--- a/LL_Team_Gantt_Heatmap.xlsx
+++ b/LL_Team_Gantt_Heatmap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lausd.sharepoint.com/teams/LinkedLearningTeam484/Shared Documents/General/Calendar for LL Team/Priorities Dashboard Ben Version/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben.gertner/Documents/LL_Team_Priorities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{AE583623-DC24-574A-AB52-1A10C056DA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADCF397D-28D5-B74A-8B2C-74C4C080981E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E46074-07A1-B142-A6B2-C4095FDF9F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activities" sheetId="1" r:id="rId1"/>
@@ -47,6 +47,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Microsoft Office User:
 1=Jul, 2=Aug, 3=Sep, 4=Oct, 5=Nov, 6=Dec, 7=Jan, 8=Feb, 9=Mar, 10=Apr, 11=May, 12=Jun. Use Start/End for continuous activities.</t>
@@ -60,6 +61,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Microsoft Office User:
 1=Jul, 2=Aug, 3=Sep, 4=Oct, 5=Nov, 6=Dec, 7=Jan, 8=Feb, 9=Mar, 10=Apr, 11=May, 12=Jun. Use Start/End for continuous activities.</t>
@@ -73,6 +75,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Microsoft Office User:
 For non-contiguous activities. Type comma-separated month numbers, e.g. "8,10,1,3" for Aug, Oct, Jan, Mar. If filled in, this OVERRIDES Start/End. Leave blank for continuous activities.</t>
@@ -86,6 +89,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Microsoft Office User:
 1=Light, 2=Moderate, 3=Heavy, 4=Peak. Used for Load row totals.</t>
@@ -99,6 +103,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Microsoft Office User:
 Yes for one-day events / hard deadlines. Milestones don't count toward Load totals.</t>
@@ -340,9 +345,6 @@
     <t>PBL/HQIM annual planning, pilot reflection &amp; improvement design</t>
   </si>
   <si>
-    <t>1,11,12</t>
-  </si>
-  <si>
     <t>Consolidates pilot reflection, theory of action, and annual instructional planning.</t>
   </si>
   <si>
@@ -596,6 +598,9 @@
   </si>
   <si>
     <t>The seven workstreams separate the major coach, coordinator, and shared bodies of work so overlaps are easier to interpret.</t>
+  </si>
+  <si>
+    <t>11,12</t>
   </si>
 </sst>
 </file>
@@ -608,7 +613,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -808,6 +813,12 @@
       <color theme="10"/>
       <name val="Poppins Regular"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="22">
     <fill>
@@ -997,15 +1008,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1036,63 +1038,31 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1113,15 +1083,6 @@
     <xf numFmtId="0" fontId="33" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1130,6 +1091,56 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1421,11 +1432,61 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94AABE50-D890-3268-C324-4791B46AC92B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14732000" cy="16256000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1573,1803 +1634,1803 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41" style="23" customWidth="1"/>
+    <col min="2" max="2" width="41" style="18" customWidth="1"/>
     <col min="3" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="5" width="16" style="1" customWidth="1"/>
     <col min="6" max="7" width="12" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="42.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="83.33203125" style="23" customWidth="1"/>
+    <col min="10" max="10" width="83.33203125" style="18" customWidth="1"/>
     <col min="11" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="29">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="38">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="57">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="25" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="21">
         <v>1</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="I5" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="27"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" ht="57">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="28" t="s">
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="24">
         <v>2</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="27"/>
+      <c r="J6" s="22"/>
     </row>
     <row r="7" spans="1:10" ht="38">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="25" t="s">
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="21">
         <v>2</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="27"/>
+      <c r="J7" s="22"/>
     </row>
     <row r="8" spans="1:10" ht="38">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="24">
         <v>2</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="24">
         <v>5</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29">
+      <c r="E8" s="23"/>
+      <c r="F8" s="24">
         <v>2</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="23" t="s">
         <v>73</v>
       </c>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="38">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="25" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="21">
+        <v>1</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="26">
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="38">
+      <c r="A10" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="24">
+        <v>3</v>
+      </c>
+      <c r="D10" s="24">
+        <v>9</v>
+      </c>
+      <c r="E10" s="23"/>
+      <c r="F10" s="24">
+        <v>3</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" spans="1:10" ht="57">
+      <c r="A11" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="21">
+        <v>2</v>
+      </c>
+      <c r="D11" s="21">
+        <v>2</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21">
+        <v>2</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" s="22"/>
+    </row>
+    <row r="12" spans="1:10" ht="38">
+      <c r="A12" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="24">
+        <v>4</v>
+      </c>
+      <c r="D12" s="24">
+        <v>4</v>
+      </c>
+      <c r="E12" s="23"/>
+      <c r="F12" s="24">
+        <v>3</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="57">
+      <c r="A13" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="21">
+        <v>2</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="57">
+      <c r="A14" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="24">
+        <v>2</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="38">
+      <c r="A15" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="21">
+        <v>2</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="57">
+      <c r="A16" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="24">
+        <v>2</v>
+      </c>
+      <c r="D16" s="24">
+        <v>10</v>
+      </c>
+      <c r="E16" s="23"/>
+      <c r="F16" s="24">
+        <v>2</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="57">
+      <c r="A17" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="21">
         <v>1</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G17" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H17" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="38">
+      <c r="A18" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="24">
+        <v>1</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="38">
+      <c r="A19" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="21">
+        <v>1</v>
+      </c>
+      <c r="D19" s="21">
+        <v>1</v>
+      </c>
+      <c r="E19" s="20"/>
+      <c r="F19" s="21">
+        <v>1</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="38">
+      <c r="A20" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="24">
+        <v>2</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" ht="38">
-      <c r="A10" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="29">
+      <c r="I20" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="57">
+      <c r="A21" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="21">
+        <v>11</v>
+      </c>
+      <c r="E21" s="20"/>
+      <c r="F21" s="21">
+        <v>1</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="38">
+      <c r="A22" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="24">
+        <v>1</v>
+      </c>
+      <c r="D22" s="24">
         <v>3</v>
       </c>
-      <c r="D10" s="29">
+      <c r="E22" s="23"/>
+      <c r="F22" s="24">
+        <v>2</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="57">
+      <c r="A23" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="21">
+        <v>2</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" ht="38">
+      <c r="A24" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="24">
+        <v>2</v>
+      </c>
+      <c r="D24" s="24">
         <v>9</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="29">
+      <c r="E24" s="23"/>
+      <c r="F24" s="24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" ht="57">
+      <c r="A25" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="21">
+        <v>2</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" ht="57">
+      <c r="A26" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="24">
+        <v>2</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" ht="57">
+      <c r="A27" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="21">
+        <v>2</v>
+      </c>
+      <c r="D27" s="21">
+        <v>12</v>
+      </c>
+      <c r="E27" s="20"/>
+      <c r="F27" s="21">
+        <v>2</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" ht="57">
+      <c r="A28" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="24">
         <v>3</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="D28" s="24">
+        <v>11</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="24">
+        <v>3</v>
+      </c>
+      <c r="G28" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H10" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="J10" s="27"/>
-    </row>
-    <row r="11" spans="1:10" ht="57">
-      <c r="A11" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="26">
+      <c r="H28" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="57">
+      <c r="A29" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="21">
+        <v>3</v>
+      </c>
+      <c r="D29" s="21">
+        <v>11</v>
+      </c>
+      <c r="E29" s="20"/>
+      <c r="F29" s="21">
         <v>2</v>
       </c>
-      <c r="D11" s="26">
+      <c r="G29" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H29" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="57">
+      <c r="A30" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="24">
+        <v>1</v>
+      </c>
+      <c r="D30" s="24">
+        <v>12</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="24">
         <v>2</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26">
+      <c r="G30" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="57">
+      <c r="A31" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F31" s="21">
         <v>2</v>
       </c>
-      <c r="G11" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" s="27"/>
-    </row>
-    <row r="12" spans="1:10" ht="38">
-      <c r="A12" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="29">
-        <v>4</v>
-      </c>
-      <c r="D12" s="29">
-        <v>4</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="29">
+      <c r="G31" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="57">
+      <c r="A32" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="24">
         <v>3</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="D32" s="24">
+        <v>9</v>
+      </c>
+      <c r="E32" s="23"/>
+      <c r="F32" s="24">
+        <v>3</v>
+      </c>
+      <c r="G32" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" ht="57">
-      <c r="A13" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="26">
+      <c r="H32" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="38">
+      <c r="A33" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="21">
+        <v>3</v>
+      </c>
+      <c r="D33" s="21">
+        <v>10</v>
+      </c>
+      <c r="E33" s="20"/>
+      <c r="F33" s="21">
         <v>2</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G33" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" ht="57">
-      <c r="A14" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" s="29">
+      <c r="H33" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="57">
+      <c r="A34" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" s="24">
+        <v>3</v>
+      </c>
+      <c r="D34" s="24">
+        <v>12</v>
+      </c>
+      <c r="E34" s="23"/>
+      <c r="F34" s="24">
+        <v>3</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="57">
+      <c r="A35" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="21">
+        <v>3</v>
+      </c>
+      <c r="D35" s="21">
+        <v>12</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="21">
+        <v>1</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="38">
+      <c r="A36" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36" s="24">
+        <v>11</v>
+      </c>
+      <c r="D36" s="24">
+        <v>12</v>
+      </c>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24">
         <v>2</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G36" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" ht="38">
-      <c r="A15" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="26">
+      <c r="H36" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" ht="57">
+      <c r="A37" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="21">
         <v>2</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="D37" s="21">
+        <v>5</v>
+      </c>
+      <c r="E37" s="20"/>
+      <c r="F37" s="21">
+        <v>1</v>
+      </c>
+      <c r="G37" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" ht="57">
-      <c r="A16" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="29">
+      <c r="H37" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" ht="57">
+      <c r="A38" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="24">
+        <v>5</v>
+      </c>
+      <c r="D38" s="24">
+        <v>5</v>
+      </c>
+      <c r="E38" s="23"/>
+      <c r="F38" s="24">
         <v>2</v>
       </c>
-      <c r="D16" s="29">
-        <v>10</v>
-      </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="29">
+      <c r="G38" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" ht="38">
+      <c r="A39" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="21">
         <v>2</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="D39" s="21">
+        <v>11</v>
+      </c>
+      <c r="E39" s="20"/>
+      <c r="F39" s="21">
+        <v>2</v>
+      </c>
+      <c r="G39" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" ht="57">
-      <c r="A17" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="26">
+      <c r="H39" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" ht="57">
+      <c r="A40" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="24">
         <v>1</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="D40" s="24">
+        <v>12</v>
+      </c>
+      <c r="E40" s="23"/>
+      <c r="F40" s="24">
+        <v>2</v>
+      </c>
+      <c r="G40" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="38">
-      <c r="A18" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="29">
+      <c r="H40" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" ht="57">
+      <c r="A41" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C41" s="21">
         <v>1</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="D41" s="21">
+        <v>12</v>
+      </c>
+      <c r="E41" s="20"/>
+      <c r="F41" s="21">
+        <v>2</v>
+      </c>
+      <c r="G41" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H18" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="38">
-      <c r="A19" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="26">
+      <c r="H41" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" ht="38">
+      <c r="A42" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="24">
+        <v>12</v>
+      </c>
+      <c r="D42" s="24">
         <v>1</v>
       </c>
-      <c r="D19" s="26">
-        <v>1</v>
-      </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="26">
-        <v>1</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" ht="38">
-      <c r="A20" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" s="29">
+      <c r="E42" s="23"/>
+      <c r="F42" s="24">
         <v>2</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G42" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H20" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="57">
-      <c r="A21" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="26">
-        <v>1</v>
-      </c>
-      <c r="D21" s="26">
-        <v>11</v>
-      </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26">
-        <v>1</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="38">
-      <c r="A22" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="29">
-        <v>1</v>
-      </c>
-      <c r="D22" s="29">
-        <v>3</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29">
-        <v>2</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" ht="57">
-      <c r="A23" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="26">
-        <v>2</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="38">
-      <c r="A24" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="29">
-        <v>2</v>
-      </c>
-      <c r="D24" s="29">
-        <v>9</v>
-      </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="29">
-        <v>1</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="57">
-      <c r="A25" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="F25" s="26">
-        <v>2</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" ht="57">
-      <c r="A26" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" s="29">
-        <v>2</v>
-      </c>
-      <c r="G26" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H26" s="29" t="s">
+      <c r="H42" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" ht="57">
-      <c r="A27" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="26">
-        <v>2</v>
-      </c>
-      <c r="D27" s="26">
-        <v>12</v>
-      </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="26">
-        <v>2</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" ht="57">
-      <c r="A28" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="29">
-        <v>3</v>
-      </c>
-      <c r="D28" s="29">
-        <v>11</v>
-      </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="29">
-        <v>3</v>
-      </c>
-      <c r="G28" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="57">
-      <c r="A29" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="26">
-        <v>3</v>
-      </c>
-      <c r="D29" s="26">
-        <v>11</v>
-      </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="26">
-        <v>2</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="57">
-      <c r="A30" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C30" s="29">
-        <v>1</v>
-      </c>
-      <c r="D30" s="29">
-        <v>12</v>
-      </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29">
-        <v>2</v>
-      </c>
-      <c r="G30" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H30" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="57">
-      <c r="A31" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" s="26">
-        <v>2</v>
-      </c>
-      <c r="G31" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" ht="57">
-      <c r="A32" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="C32" s="29">
-        <v>3</v>
-      </c>
-      <c r="D32" s="29">
-        <v>9</v>
-      </c>
-      <c r="E32" s="28"/>
-      <c r="F32" s="29">
-        <v>3</v>
-      </c>
-      <c r="G32" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" ht="38">
-      <c r="A33" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="C33" s="26">
-        <v>3</v>
-      </c>
-      <c r="D33" s="26">
-        <v>10</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="26">
-        <v>2</v>
-      </c>
-      <c r="G33" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" ht="57">
-      <c r="A34" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="29">
-        <v>3</v>
-      </c>
-      <c r="D34" s="29">
-        <v>12</v>
-      </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="29">
-        <v>3</v>
-      </c>
-      <c r="G34" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" ht="57">
-      <c r="A35" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="C35" s="26">
-        <v>3</v>
-      </c>
-      <c r="D35" s="26">
-        <v>12</v>
-      </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="26">
-        <v>1</v>
-      </c>
-      <c r="G35" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" ht="38">
-      <c r="A36" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="C36" s="29">
-        <v>11</v>
-      </c>
-      <c r="D36" s="29">
-        <v>12</v>
-      </c>
-      <c r="E36" s="28"/>
-      <c r="F36" s="29">
-        <v>2</v>
-      </c>
-      <c r="G36" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" ht="57">
-      <c r="A37" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="B37" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="C37" s="26">
-        <v>2</v>
-      </c>
-      <c r="D37" s="26">
-        <v>5</v>
-      </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="26">
-        <v>1</v>
-      </c>
-      <c r="G37" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" ht="57">
-      <c r="A38" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="29">
-        <v>5</v>
-      </c>
-      <c r="D38" s="29">
-        <v>5</v>
-      </c>
-      <c r="E38" s="28"/>
-      <c r="F38" s="29">
-        <v>2</v>
-      </c>
-      <c r="G38" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H38" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" ht="38">
-      <c r="A39" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="C39" s="26">
-        <v>2</v>
-      </c>
-      <c r="D39" s="26">
-        <v>11</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="26">
-        <v>2</v>
-      </c>
-      <c r="G39" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H39" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I39" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" ht="57">
-      <c r="A40" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="29">
-        <v>1</v>
-      </c>
-      <c r="D40" s="29">
-        <v>12</v>
-      </c>
-      <c r="E40" s="28"/>
-      <c r="F40" s="29">
-        <v>2</v>
-      </c>
-      <c r="G40" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H40" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I40" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="J40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" ht="57">
-      <c r="A41" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="C41" s="26">
-        <v>1</v>
-      </c>
-      <c r="D41" s="26">
-        <v>12</v>
-      </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="26">
-        <v>2</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H41" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I41" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="J41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" ht="38">
-      <c r="A42" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="B42" s="28" t="s">
+      <c r="I42" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="C42" s="29">
-        <v>12</v>
-      </c>
-      <c r="D42" s="29">
-        <v>1</v>
-      </c>
-      <c r="E42" s="28"/>
-      <c r="F42" s="29">
-        <v>2</v>
-      </c>
-      <c r="G42" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="H42" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I42" s="28" t="s">
-        <v>159</v>
-      </c>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="25"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="20"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="28"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="23"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="25"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="20"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="28"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="28"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="23"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="25"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="25"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="20"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="25"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="28"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="23"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="25"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="20"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="28"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="28"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="23"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="25"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="25"/>
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="20"/>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="28"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="28"/>
+      <c r="A52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="23"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="25"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="25"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="20"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="28"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="28"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="23"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="28"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="28"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="23"/>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="25"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="25"/>
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="20"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="28"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="23"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="25"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="25"/>
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="20"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="28"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="23"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="25"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="25"/>
+      <c r="A60" s="20"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="20"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="28"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="28"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="23"/>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="25"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="25"/>
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="20"/>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="28"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="28"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="23"/>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="25"/>
+      <c r="A64" s="20"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="20"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="28"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="29"/>
-      <c r="H65" s="29"/>
-      <c r="I65" s="28"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="23"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="25"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="26"/>
-      <c r="G66" s="26"/>
-      <c r="H66" s="26"/>
-      <c r="I66" s="25"/>
+      <c r="A66" s="20"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="20"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="28"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="28"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="23"/>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="25"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
-      <c r="H68" s="26"/>
-      <c r="I68" s="25"/>
+      <c r="A68" s="20"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="28"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="28"/>
+      <c r="A69" s="23"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="23"/>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="25"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="25"/>
+      <c r="A70" s="20"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="20"/>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="28"/>
-      <c r="B71" s="28"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="28"/>
+      <c r="A71" s="23"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24"/>
+      <c r="I71" s="23"/>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="25"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="25"/>
+      <c r="A72" s="20"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="20"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="28"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="28"/>
+      <c r="A73" s="23"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="23"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="25"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="25"/>
+      <c r="A74" s="20"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="20"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="28"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="28"/>
+      <c r="A75" s="23"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="23"/>
     </row>
     <row r="76" spans="1:9">
-      <c r="A76" s="25"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="26"/>
-      <c r="D76" s="26"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="25"/>
+      <c r="A76" s="20"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21"/>
+      <c r="I76" s="20"/>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" s="28"/>
-      <c r="B77" s="28"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="28"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="28"/>
+      <c r="A77" s="23"/>
+      <c r="B77" s="23"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="23"/>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" s="25"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
-      <c r="I78" s="25"/>
+      <c r="A78" s="20"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21"/>
+      <c r="I78" s="20"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="28"/>
-      <c r="B79" s="28"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="29"/>
-      <c r="G79" s="29"/>
-      <c r="H79" s="29"/>
-      <c r="I79" s="28"/>
+      <c r="A79" s="23"/>
+      <c r="B79" s="23"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24"/>
+      <c r="H79" s="24"/>
+      <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9">
-      <c r="A80" s="25"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="25"/>
+      <c r="A80" s="20"/>
+      <c r="B80" s="20"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="20"/>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="28"/>
-      <c r="B81" s="28"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="29"/>
-      <c r="G81" s="29"/>
-      <c r="H81" s="29"/>
-      <c r="I81" s="28"/>
+      <c r="A81" s="23"/>
+      <c r="B81" s="23"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="24"/>
+      <c r="H81" s="24"/>
+      <c r="I81" s="23"/>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="25"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="25"/>
-      <c r="F82" s="26"/>
-      <c r="G82" s="26"/>
-      <c r="H82" s="26"/>
-      <c r="I82" s="25"/>
+      <c r="A82" s="20"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="20"/>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="28"/>
-      <c r="B83" s="28"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="28"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="29"/>
-      <c r="H83" s="29"/>
-      <c r="I83" s="28"/>
+      <c r="A83" s="23"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="24"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="24"/>
+      <c r="G83" s="24"/>
+      <c r="H83" s="24"/>
+      <c r="I83" s="23"/>
     </row>
     <row r="84" spans="1:9">
-      <c r="A84" s="25"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="26"/>
-      <c r="G84" s="26"/>
-      <c r="H84" s="26"/>
-      <c r="I84" s="25"/>
+      <c r="A84" s="20"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="21"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="20"/>
     </row>
     <row r="85" spans="1:9">
-      <c r="A85" s="28"/>
-      <c r="B85" s="28"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="28"/>
-      <c r="F85" s="29"/>
-      <c r="G85" s="29"/>
-      <c r="H85" s="29"/>
-      <c r="I85" s="28"/>
+      <c r="A85" s="23"/>
+      <c r="B85" s="23"/>
+      <c r="C85" s="24"/>
+      <c r="D85" s="24"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="24"/>
+      <c r="H85" s="24"/>
+      <c r="I85" s="23"/>
     </row>
     <row r="86" spans="1:9">
-      <c r="A86" s="25"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="26"/>
-      <c r="E86" s="25"/>
-      <c r="F86" s="26"/>
-      <c r="G86" s="26"/>
-      <c r="H86" s="26"/>
-      <c r="I86" s="25"/>
+      <c r="A86" s="20"/>
+      <c r="B86" s="20"/>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="21"/>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+      <c r="I86" s="20"/>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" s="28"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="29"/>
-      <c r="E87" s="28"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29"/>
-      <c r="H87" s="29"/>
-      <c r="I87" s="28"/>
+      <c r="A87" s="23"/>
+      <c r="B87" s="23"/>
+      <c r="C87" s="24"/>
+      <c r="D87" s="24"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="24"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="23"/>
     </row>
     <row r="88" spans="1:9">
-      <c r="A88" s="25"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="26"/>
-      <c r="D88" s="26"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="26"/>
-      <c r="G88" s="26"/>
-      <c r="H88" s="26"/>
-      <c r="I88" s="25"/>
+      <c r="A88" s="20"/>
+      <c r="B88" s="20"/>
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="21"/>
+      <c r="G88" s="21"/>
+      <c r="H88" s="21"/>
+      <c r="I88" s="20"/>
     </row>
     <row r="89" spans="1:9">
-      <c r="A89" s="28"/>
-      <c r="B89" s="28"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="29"/>
-      <c r="E89" s="28"/>
-      <c r="F89" s="29"/>
-      <c r="G89" s="29"/>
-      <c r="H89" s="29"/>
-      <c r="I89" s="28"/>
+      <c r="A89" s="23"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="24"/>
+      <c r="D89" s="24"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="24"/>
+      <c r="G89" s="24"/>
+      <c r="H89" s="24"/>
+      <c r="I89" s="23"/>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="25"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="26"/>
-      <c r="D90" s="26"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="26"/>
-      <c r="H90" s="26"/>
-      <c r="I90" s="25"/>
+      <c r="A90" s="20"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="21"/>
+      <c r="G90" s="21"/>
+      <c r="H90" s="21"/>
+      <c r="I90" s="20"/>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="28"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
-      <c r="E91" s="28"/>
-      <c r="F91" s="29"/>
-      <c r="G91" s="29"/>
-      <c r="H91" s="29"/>
-      <c r="I91" s="28"/>
+      <c r="A91" s="23"/>
+      <c r="B91" s="23"/>
+      <c r="C91" s="24"/>
+      <c r="D91" s="24"/>
+      <c r="E91" s="23"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="24"/>
+      <c r="I91" s="23"/>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="25"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="26"/>
-      <c r="D92" s="26"/>
-      <c r="E92" s="25"/>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
-      <c r="H92" s="26"/>
-      <c r="I92" s="25"/>
+      <c r="A92" s="20"/>
+      <c r="B92" s="20"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="21"/>
+      <c r="G92" s="21"/>
+      <c r="H92" s="21"/>
+      <c r="I92" s="20"/>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="28"/>
-      <c r="B93" s="28"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="28"/>
-      <c r="F93" s="29"/>
-      <c r="G93" s="29"/>
-      <c r="H93" s="29"/>
-      <c r="I93" s="28"/>
+      <c r="A93" s="23"/>
+      <c r="B93" s="23"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="24"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="23"/>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="25"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="26"/>
-      <c r="D94" s="26"/>
-      <c r="E94" s="25"/>
-      <c r="F94" s="26"/>
-      <c r="G94" s="26"/>
-      <c r="H94" s="26"/>
-      <c r="I94" s="25"/>
+      <c r="A94" s="20"/>
+      <c r="B94" s="20"/>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="20"/>
+      <c r="F94" s="21"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="21"/>
+      <c r="I94" s="20"/>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="28"/>
-      <c r="B95" s="28"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="29"/>
-      <c r="E95" s="28"/>
-      <c r="F95" s="29"/>
-      <c r="G95" s="29"/>
-      <c r="H95" s="29"/>
-      <c r="I95" s="28"/>
+      <c r="A95" s="23"/>
+      <c r="B95" s="23"/>
+      <c r="C95" s="24"/>
+      <c r="D95" s="24"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="24"/>
+      <c r="G95" s="24"/>
+      <c r="H95" s="24"/>
+      <c r="I95" s="23"/>
     </row>
     <row r="96" spans="1:9">
-      <c r="A96" s="25"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="26"/>
-      <c r="D96" s="26"/>
-      <c r="E96" s="25"/>
-      <c r="F96" s="26"/>
-      <c r="G96" s="26"/>
-      <c r="H96" s="26"/>
-      <c r="I96" s="25"/>
+      <c r="A96" s="20"/>
+      <c r="B96" s="20"/>
+      <c r="C96" s="21"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="21"/>
+      <c r="G96" s="21"/>
+      <c r="H96" s="21"/>
+      <c r="I96" s="20"/>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="28"/>
-      <c r="B97" s="28"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="28"/>
-      <c r="F97" s="29"/>
-      <c r="G97" s="29"/>
-      <c r="H97" s="29"/>
-      <c r="I97" s="28"/>
+      <c r="A97" s="23"/>
+      <c r="B97" s="23"/>
+      <c r="C97" s="24"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="23"/>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="25"/>
-      <c r="B98" s="25"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="25"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="25"/>
+      <c r="A98" s="20"/>
+      <c r="B98" s="20"/>
+      <c r="C98" s="21"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="20"/>
+      <c r="F98" s="21"/>
+      <c r="G98" s="21"/>
+      <c r="H98" s="21"/>
+      <c r="I98" s="20"/>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="28"/>
-      <c r="B99" s="28"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="29"/>
-      <c r="E99" s="28"/>
-      <c r="F99" s="29"/>
-      <c r="G99" s="29"/>
-      <c r="H99" s="29"/>
-      <c r="I99" s="28"/>
+      <c r="A99" s="23"/>
+      <c r="B99" s="23"/>
+      <c r="C99" s="24"/>
+      <c r="D99" s="24"/>
+      <c r="E99" s="23"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="24"/>
+      <c r="H99" s="24"/>
+      <c r="I99" s="23"/>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="25"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="26"/>
-      <c r="D100" s="26"/>
-      <c r="E100" s="25"/>
-      <c r="F100" s="26"/>
-      <c r="G100" s="26"/>
-      <c r="H100" s="26"/>
-      <c r="I100" s="25"/>
+      <c r="A100" s="20"/>
+      <c r="B100" s="20"/>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="20"/>
+      <c r="F100" s="21"/>
+      <c r="G100" s="21"/>
+      <c r="H100" s="21"/>
+      <c r="I100" s="20"/>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="28"/>
-      <c r="B101" s="28"/>
-      <c r="C101" s="29"/>
-      <c r="D101" s="29"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="29"/>
-      <c r="G101" s="29"/>
-      <c r="H101" s="29"/>
-      <c r="I101" s="28"/>
+      <c r="A101" s="23"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="23"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="23"/>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="25"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="26"/>
-      <c r="D102" s="26"/>
-      <c r="E102" s="25"/>
-      <c r="F102" s="26"/>
-      <c r="G102" s="26"/>
-      <c r="H102" s="26"/>
-      <c r="I102" s="25"/>
+      <c r="A102" s="20"/>
+      <c r="B102" s="20"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="20"/>
+      <c r="F102" s="21"/>
+      <c r="G102" s="21"/>
+      <c r="H102" s="21"/>
+      <c r="I102" s="20"/>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="28"/>
-      <c r="B103" s="28"/>
-      <c r="C103" s="29"/>
-      <c r="D103" s="29"/>
-      <c r="E103" s="28"/>
-      <c r="F103" s="29"/>
-      <c r="G103" s="29"/>
-      <c r="H103" s="29"/>
-      <c r="I103" s="28"/>
+      <c r="A103" s="23"/>
+      <c r="B103" s="23"/>
+      <c r="C103" s="24"/>
+      <c r="D103" s="24"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="24"/>
+      <c r="H103" s="24"/>
+      <c r="I103" s="23"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="25"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="26"/>
-      <c r="D104" s="26"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="26"/>
-      <c r="H104" s="26"/>
-      <c r="I104" s="25"/>
+      <c r="A104" s="20"/>
+      <c r="B104" s="20"/>
+      <c r="C104" s="21"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="20"/>
+      <c r="F104" s="21"/>
+      <c r="G104" s="21"/>
+      <c r="H104" s="21"/>
+      <c r="I104" s="20"/>
       <c r="J104" s="1"/>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="28"/>
-      <c r="B105" s="28"/>
-      <c r="C105" s="29"/>
-      <c r="D105" s="29"/>
-      <c r="E105" s="28"/>
-      <c r="F105" s="29"/>
-      <c r="G105" s="29"/>
-      <c r="H105" s="29"/>
-      <c r="I105" s="28"/>
+      <c r="A105" s="23"/>
+      <c r="B105" s="23"/>
+      <c r="C105" s="24"/>
+      <c r="D105" s="24"/>
+      <c r="E105" s="23"/>
+      <c r="F105" s="24"/>
+      <c r="G105" s="24"/>
+      <c r="H105" s="24"/>
+      <c r="I105" s="23"/>
       <c r="J105" s="1"/>
     </row>
     <row r="106" spans="1:10">
@@ -3425,8 +3486,8 @@
   <dimension ref="A1:N907"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="23" customWidth="1"/>
-    <col min="2" max="2" width="32.1640625" style="23" customWidth="1"/>
+    <col min="1" max="1" width="23.5" style="18" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" style="18" customWidth="1"/>
     <col min="3" max="10" width="21.83203125" style="5" customWidth="1"/>
     <col min="11" max="14" width="21.83203125" style="6" customWidth="1"/>
     <col min="15" max="15" width="8.6640625" style="1" customWidth="1"/>
@@ -3434,40 +3495,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="29">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
     </row>
     <row r="4" spans="1:14" s="4" customFormat="1" ht="23">
       <c r="A4" s="17" t="s">
@@ -3522,12 +3583,12 @@
         <f>IF(Activities!$B5&lt;&gt;"",Activities!$B5,"")</f>
         <v>CTE master scheduling, pathway completion &amp; Elevate error review</v>
       </c>
-      <c r="C5" s="63" t="str">
+      <c r="C5" s="43" t="str">
         <f>IF(AND(Activities!$A5&lt;&gt;"",IF(Activities!$E5&lt;&gt;"",ISNUMBER(SEARCH(",1,",","&amp;Activities!$E5&amp;",")),AND(Activities!$C5&lt;=1,Activities!$D5&gt;=1))),IF(Activities!$H5="Coaches","🌱 ",IF(Activities!$H5="Coordinators","⚙️ ",IF(Activities!$H5="Both","👥 ","")))&amp;Activities!$B5&amp;CHAR(10)&amp;REPT("●",Activities!$F5),"")</f>
         <v>🌱 CTE master scheduling, pathway completion &amp; Elevate error review
 ●</v>
       </c>
-      <c r="D5" s="63" t="str">
+      <c r="D5" s="43" t="str">
         <f>IF(AND(Activities!$A5&lt;&gt;"",IF(Activities!$E5&lt;&gt;"",ISNUMBER(SEARCH(",2,",","&amp;Activities!$E5&amp;",")),AND(Activities!$C5&lt;=2,Activities!$D5&gt;=2))),IF(Activities!$H5="Coaches","🌱 ",IF(Activities!$H5="Coordinators","⚙️ ",IF(Activities!$H5="Both","👥 ","")))&amp;Activities!$B5&amp;CHAR(10)&amp;REPT("●",Activities!$F5),"")</f>
         <v>🌱 CTE master scheduling, pathway completion &amp; Elevate error review
 ●</v>
@@ -3561,7 +3622,7 @@
         <f>IF(AND(Activities!$A5&lt;&gt;"",IF(Activities!$E5&lt;&gt;"",ISNUMBER(SEARCH(",8,",","&amp;Activities!$E5&amp;",")),AND(Activities!$C5&lt;=8,Activities!$D5&gt;=8))),IF(Activities!$H5="Coaches","🌱 ",IF(Activities!$H5="Coordinators","⚙️ ",IF(Activities!$H5="Both","👥 ","")))&amp;Activities!$B5&amp;CHAR(10)&amp;REPT("●",Activities!$F5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="64" t="str">
+      <c r="K5" s="44" t="str">
         <f>IF(AND(Activities!$A5&lt;&gt;"",IF(Activities!$E5&lt;&gt;"",ISNUMBER(SEARCH(",9,",","&amp;Activities!$E5&amp;",")),AND(Activities!$C5&lt;=9,Activities!$D5&gt;=9))),IF(Activities!$H5="Coaches","🌱 ",IF(Activities!$H5="Coordinators","⚙️ ",IF(Activities!$H5="Both","👥 ","")))&amp;Activities!$B5&amp;CHAR(10)&amp;REPT("●",Activities!$F5),"")</f>
         <v>🌱 CTE master scheduling, pathway completion &amp; Elevate error review
 ●</v>
@@ -3598,12 +3659,12 @@
         <v>🌱 Unified Funding Application cycle: orientation, troubleshooting, application &amp; purchasing support
 ●●</v>
       </c>
-      <c r="E6" s="63" t="str">
+      <c r="E6" s="43" t="str">
         <f>IF(AND(Activities!$A6&lt;&gt;"",IF(Activities!$E6&lt;&gt;"",ISNUMBER(SEARCH(",3,",","&amp;Activities!$E6&amp;",")),AND(Activities!$C6&lt;=3,Activities!$D6&gt;=3))),IF(Activities!$H6="Coaches","🌱 ",IF(Activities!$H6="Coordinators","⚙️ ",IF(Activities!$H6="Both","👥 ","")))&amp;Activities!$B6&amp;CHAR(10)&amp;REPT("●",Activities!$F6),"")</f>
         <v>🌱 Unified Funding Application cycle: orientation, troubleshooting, application &amp; purchasing support
 ●●</v>
       </c>
-      <c r="F6" s="63" t="str">
+      <c r="F6" s="43" t="str">
         <f>IF(AND(Activities!$A6&lt;&gt;"",IF(Activities!$E6&lt;&gt;"",ISNUMBER(SEARCH(",4,",","&amp;Activities!$E6&amp;",")),AND(Activities!$C6&lt;=4,Activities!$D6&gt;=4))),IF(Activities!$H6="Coaches","🌱 ",IF(Activities!$H6="Coordinators","⚙️ ",IF(Activities!$H6="Both","👥 ","")))&amp;Activities!$B6&amp;CHAR(10)&amp;REPT("●",Activities!$F6),"")</f>
         <v>🌱 Unified Funding Application cycle: orientation, troubleshooting, application &amp; purchasing support
 ●●</v>
@@ -3616,7 +3677,7 @@
         <f>IF(AND(Activities!$A6&lt;&gt;"",IF(Activities!$E6&lt;&gt;"",ISNUMBER(SEARCH(",6,",","&amp;Activities!$E6&amp;",")),AND(Activities!$C6&lt;=6,Activities!$D6&gt;=6))),IF(Activities!$H6="Coaches","🌱 ",IF(Activities!$H6="Coordinators","⚙️ ",IF(Activities!$H6="Both","👥 ","")))&amp;Activities!$B6&amp;CHAR(10)&amp;REPT("●",Activities!$F6),"")</f>
         <v/>
       </c>
-      <c r="I6" s="64" t="str">
+      <c r="I6" s="44" t="str">
         <f>IF(AND(Activities!$A6&lt;&gt;"",IF(Activities!$E6&lt;&gt;"",ISNUMBER(SEARCH(",7,",","&amp;Activities!$E6&amp;",")),AND(Activities!$C6&lt;=7,Activities!$D6&gt;=7))),IF(Activities!$H6="Coaches","🌱 ",IF(Activities!$H6="Coordinators","⚙️ ",IF(Activities!$H6="Both","👥 ","")))&amp;Activities!$B6&amp;CHAR(10)&amp;REPT("●",Activities!$F6),"")</f>
         <v>🌱 Unified Funding Application cycle: orientation, troubleshooting, application &amp; purchasing support
 ●●</v>
@@ -3662,7 +3723,7 @@
         <f>IF(AND(Activities!$A7&lt;&gt;"",IF(Activities!$E7&lt;&gt;"",ISNUMBER(SEARCH(",2,",","&amp;Activities!$E7&amp;",")),AND(Activities!$C7&lt;=2,Activities!$D7&gt;=2))),IF(Activities!$H7="Coaches","🌱 ",IF(Activities!$H7="Coordinators","⚙️ ",IF(Activities!$H7="Both","👥 ","")))&amp;Activities!$B7&amp;CHAR(10)&amp;REPT("●",Activities!$F7),"")</f>
         <v/>
       </c>
-      <c r="E7" s="64" t="str">
+      <c r="E7" s="44" t="str">
         <f>IF(AND(Activities!$A7&lt;&gt;"",IF(Activities!$E7&lt;&gt;"",ISNUMBER(SEARCH(",3,",","&amp;Activities!$E7&amp;",")),AND(Activities!$C7&lt;=3,Activities!$D7&gt;=3))),IF(Activities!$H7="Coaches","🌱 ",IF(Activities!$H7="Coordinators","⚙️ ",IF(Activities!$H7="Both","👥 ","")))&amp;Activities!$B7&amp;CHAR(10)&amp;REPT("●",Activities!$F7),"")</f>
         <v>🌱 GSPP planning, implementation &amp; spending support
 ●●</v>
@@ -3681,12 +3742,12 @@
         <v>🌱 GSPP planning, implementation &amp; spending support
 ●●</v>
       </c>
-      <c r="I7" s="63" t="str">
+      <c r="I7" s="43" t="str">
         <f>IF(AND(Activities!$A7&lt;&gt;"",IF(Activities!$E7&lt;&gt;"",ISNUMBER(SEARCH(",7,",","&amp;Activities!$E7&amp;",")),AND(Activities!$C7&lt;=7,Activities!$D7&gt;=7))),IF(Activities!$H7="Coaches","🌱 ",IF(Activities!$H7="Coordinators","⚙️ ",IF(Activities!$H7="Both","👥 ","")))&amp;Activities!$B7&amp;CHAR(10)&amp;REPT("●",Activities!$F7),"")</f>
         <v>🌱 GSPP planning, implementation &amp; spending support
 ●●</v>
       </c>
-      <c r="J7" s="63" t="str">
+      <c r="J7" s="43" t="str">
         <f>IF(AND(Activities!$A7&lt;&gt;"",IF(Activities!$E7&lt;&gt;"",ISNUMBER(SEARCH(",8,",","&amp;Activities!$E7&amp;",")),AND(Activities!$C7&lt;=8,Activities!$D7&gt;=8))),IF(Activities!$H7="Coaches","🌱 ",IF(Activities!$H7="Coordinators","⚙️ ",IF(Activities!$H7="Both","👥 ","")))&amp;Activities!$B7&amp;CHAR(10)&amp;REPT("●",Activities!$F7),"")</f>
         <v>🌱 GSPP planning, implementation &amp; spending support
 ●●</v>
@@ -3705,7 +3766,7 @@
         <v>🌱 GSPP planning, implementation &amp; spending support
 ●●</v>
       </c>
-      <c r="N7" s="64" t="str">
+      <c r="N7" s="44" t="str">
         <f>IF(AND(Activities!$A7&lt;&gt;"",IF(Activities!$E7&lt;&gt;"",ISNUMBER(SEARCH(",12,",","&amp;Activities!$E7&amp;",")),AND(Activities!$C7&lt;=12,Activities!$D7&gt;=12))),IF(Activities!$H7="Coaches","🌱 ",IF(Activities!$H7="Coordinators","⚙️ ",IF(Activities!$H7="Both","👥 ","")))&amp;Activities!$B7&amp;CHAR(10)&amp;REPT("●",Activities!$F7),"")</f>
         <v>🌱 GSPP planning, implementation &amp; spending support
 ●●</v>
@@ -3784,8 +3845,7 @@
       </c>
       <c r="C9" s="7" t="str">
         <f>IF(AND(Activities!$A9&lt;&gt;"",IF(Activities!$E9&lt;&gt;"",ISNUMBER(SEARCH(",1,",","&amp;Activities!$E9&amp;",")),AND(Activities!$C9&lt;=1,Activities!$D9&gt;=1))),IF(Activities!$H9="Coaches","🌱 ",IF(Activities!$H9="Coordinators","⚙️ ",IF(Activities!$H9="Both","👥 ","")))&amp;Activities!$B9&amp;CHAR(10)&amp;REPT("●",Activities!$F9),"")</f>
-        <v>🌱 PBL/HQIM annual planning, pilot reflection &amp; improvement design
-●</v>
+        <v/>
       </c>
       <c r="D9" s="7" t="str">
         <f>IF(AND(Activities!$A9&lt;&gt;"",IF(Activities!$E9&lt;&gt;"",ISNUMBER(SEARCH(",2,",","&amp;Activities!$E9&amp;",")),AND(Activities!$C9&lt;=2,Activities!$D9&gt;=2))),IF(Activities!$H9="Coaches","🌱 ",IF(Activities!$H9="Coordinators","⚙️ ",IF(Activities!$H9="Both","👥 ","")))&amp;Activities!$B9&amp;CHAR(10)&amp;REPT("●",Activities!$F9),"")</f>
@@ -3851,12 +3911,12 @@
         <f>IF(AND(Activities!$A10&lt;&gt;"",IF(Activities!$E10&lt;&gt;"",ISNUMBER(SEARCH(",2,",","&amp;Activities!$E10&amp;",")),AND(Activities!$C10&lt;=2,Activities!$D10&gt;=2))),IF(Activities!$H10="Coaches","🌱 ",IF(Activities!$H10="Coordinators","⚙️ ",IF(Activities!$H10="Both","👥 ","")))&amp;Activities!$B10&amp;CHAR(10)&amp;REPT("●",Activities!$F10),"")</f>
         <v/>
       </c>
-      <c r="E10" s="63" t="str">
+      <c r="E10" s="43" t="str">
         <f>IF(AND(Activities!$A10&lt;&gt;"",IF(Activities!$E10&lt;&gt;"",ISNUMBER(SEARCH(",3,",","&amp;Activities!$E10&amp;",")),AND(Activities!$C10&lt;=3,Activities!$D10&gt;=3))),IF(Activities!$H10="Coaches","🌱 ",IF(Activities!$H10="Coordinators","⚙️ ",IF(Activities!$H10="Both","👥 ","")))&amp;Activities!$B10&amp;CHAR(10)&amp;REPT("●",Activities!$F10),"")</f>
         <v>🌱 PBL/HQIM school-site coaching and professional learning
 ●●●</v>
       </c>
-      <c r="F10" s="63" t="str">
+      <c r="F10" s="43" t="str">
         <f>IF(AND(Activities!$A10&lt;&gt;"",IF(Activities!$E10&lt;&gt;"",ISNUMBER(SEARCH(",4,",","&amp;Activities!$E10&amp;",")),AND(Activities!$C10&lt;=4,Activities!$D10&gt;=4))),IF(Activities!$H10="Coaches","🌱 ",IF(Activities!$H10="Coordinators","⚙️ ",IF(Activities!$H10="Both","👥 ","")))&amp;Activities!$B10&amp;CHAR(10)&amp;REPT("●",Activities!$F10),"")</f>
         <v>🌱 PBL/HQIM school-site coaching and professional learning
 ●●●</v>
@@ -3871,7 +3931,7 @@
         <v>🌱 PBL/HQIM school-site coaching and professional learning
 ●●●</v>
       </c>
-      <c r="I10" s="64" t="str">
+      <c r="I10" s="44" t="str">
         <f>IF(AND(Activities!$A10&lt;&gt;"",IF(Activities!$E10&lt;&gt;"",ISNUMBER(SEARCH(",7,",","&amp;Activities!$E10&amp;",")),AND(Activities!$C10&lt;=7,Activities!$D10&gt;=7))),IF(Activities!$H10="Coaches","🌱 ",IF(Activities!$H10="Coordinators","⚙️ ",IF(Activities!$H10="Both","👥 ","")))&amp;Activities!$B10&amp;CHAR(10)&amp;REPT("●",Activities!$F10),"")</f>
         <v>🌱 PBL/HQIM school-site coaching and professional learning
 ●●●</v>
@@ -3925,11 +3985,11 @@
         <f>IF(AND(Activities!$A11&lt;&gt;"",IF(Activities!$E11&lt;&gt;"",ISNUMBER(SEARCH(",4,",","&amp;Activities!$E11&amp;",")),AND(Activities!$C11&lt;=4,Activities!$D11&gt;=4))),IF(Activities!$H11="Coaches","🌱 ",IF(Activities!$H11="Coordinators","⚙️ ",IF(Activities!$H11="Both","👥 ","")))&amp;Activities!$B11&amp;CHAR(10)&amp;REPT("●",Activities!$F11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="63" t="str">
+      <c r="G11" s="43" t="str">
         <f>IF(AND(Activities!$A11&lt;&gt;"",IF(Activities!$E11&lt;&gt;"",ISNUMBER(SEARCH(",5,",","&amp;Activities!$E11&amp;",")),AND(Activities!$C11&lt;=5,Activities!$D11&gt;=5))),IF(Activities!$H11="Coaches","🌱 ",IF(Activities!$H11="Coordinators","⚙️ ",IF(Activities!$H11="Both","👥 ","")))&amp;Activities!$B11&amp;CHAR(10)&amp;REPT("●",Activities!$F11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="63" t="str">
+      <c r="H11" s="43" t="str">
         <f>IF(AND(Activities!$A11&lt;&gt;"",IF(Activities!$E11&lt;&gt;"",ISNUMBER(SEARCH(",6,",","&amp;Activities!$E11&amp;",")),AND(Activities!$C11&lt;=6,Activities!$D11&gt;=6))),IF(Activities!$H11="Coaches","🌱 ",IF(Activities!$H11="Coordinators","⚙️ ",IF(Activities!$H11="Both","👥 ","")))&amp;Activities!$B11&amp;CHAR(10)&amp;REPT("●",Activities!$F11),"")</f>
         <v/>
       </c>
@@ -3953,7 +4013,7 @@
         <f>IF(AND(Activities!$A11&lt;&gt;"",IF(Activities!$E11&lt;&gt;"",ISNUMBER(SEARCH(",11,",","&amp;Activities!$E11&amp;",")),AND(Activities!$C11&lt;=11,Activities!$D11&gt;=11))),IF(Activities!$H11="Coaches","🌱 ",IF(Activities!$H11="Coordinators","⚙️ ",IF(Activities!$H11="Both","👥 ","")))&amp;Activities!$B11&amp;CHAR(10)&amp;REPT("●",Activities!$F11),"")</f>
         <v/>
       </c>
-      <c r="N11" s="64" t="str">
+      <c r="N11" s="44" t="str">
         <f>IF(AND(Activities!$A11&lt;&gt;"",IF(Activities!$E11&lt;&gt;"",ISNUMBER(SEARCH(",12,",","&amp;Activities!$E11&amp;",")),AND(Activities!$C11&lt;=12,Activities!$D11&gt;=12))),IF(Activities!$H11="Coaches","🌱 ",IF(Activities!$H11="Coordinators","⚙️ ",IF(Activities!$H11="Both","👥 ","")))&amp;Activities!$B11&amp;CHAR(10)&amp;REPT("●",Activities!$F11),"")</f>
         <v/>
       </c>
@@ -9539,8 +9599,8 @@
       </c>
     </row>
     <row r="105" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A105" s="65"/>
-      <c r="B105" s="63"/>
+      <c r="A105" s="45"/>
+      <c r="B105" s="43"/>
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
@@ -9563,7 +9623,7 @@
       </c>
       <c r="C106" s="12">
         <f t="array" ref="C106">SUMPRODUCT((C$5:C$104&lt;&gt;"")*(Activities!$G$5:$G$104&lt;&gt;"Yes")*((Activities!$H$5:$H$104="Coaches")+(Activities!$H$5:$H$104="Both"))*Activities!$F$5:$F$104)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D106" s="12">
         <f t="array" ref="D106">SUMPRODUCT((D$5:D$104&lt;&gt;"")*(Activities!$G$5:$G$104&lt;&gt;"Yes")*((Activities!$H$5:$H$104="Coaches")+(Activities!$H$5:$H$104="Both"))*Activities!$F$5:$F$104)</f>
@@ -9675,7 +9735,7 @@
       </c>
       <c r="C108" s="13">
         <f>SUMPRODUCT((C$5:C$104&lt;&gt;"")*(Activities!$G$5:$G$104&lt;&gt;"Yes")*((Activities!$H$5:$H$104="Coaches")+(Activities!$H$5:$H$104="Coordinators")+(Activities!$H$5:$H$104="Both"))*Activities!$F$5:$F$104)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D108" s="13">
         <f>SUMPRODUCT((D$5:D$104&lt;&gt;"")*(Activities!$G$5:$G$104&lt;&gt;"Yes")*((Activities!$H$5:$H$104="Coaches")+(Activities!$H$5:$H$104="Coordinators")+(Activities!$H$5:$H$104="Both"))*Activities!$F$5:$F$104)</f>
@@ -9723,8 +9783,8 @@
       </c>
     </row>
     <row r="109" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A109" s="65"/>
-      <c r="B109" s="63"/>
+      <c r="A109" s="45"/>
+      <c r="B109" s="43"/>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
@@ -9739,8 +9799,8 @@
       <c r="N109" s="10"/>
     </row>
     <row r="110" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A110" s="65"/>
-      <c r="B110" s="63"/>
+      <c r="A110" s="45"/>
+      <c r="B110" s="43"/>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
@@ -9755,8 +9815,8 @@
       <c r="N110" s="10"/>
     </row>
     <row r="111" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A111" s="65"/>
-      <c r="B111" s="63"/>
+      <c r="A111" s="45"/>
+      <c r="B111" s="43"/>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -9771,8 +9831,8 @@
       <c r="N111" s="10"/>
     </row>
     <row r="112" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A112" s="65"/>
-      <c r="B112" s="63"/>
+      <c r="A112" s="45"/>
+      <c r="B112" s="43"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
@@ -9787,8 +9847,8 @@
       <c r="N112" s="10"/>
     </row>
     <row r="113" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A113" s="65"/>
-      <c r="B113" s="63"/>
+      <c r="A113" s="45"/>
+      <c r="B113" s="43"/>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
@@ -9803,8 +9863,8 @@
       <c r="N113" s="10"/>
     </row>
     <row r="114" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A114" s="65"/>
-      <c r="B114" s="63"/>
+      <c r="A114" s="45"/>
+      <c r="B114" s="43"/>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
@@ -9819,8 +9879,8 @@
       <c r="N114" s="10"/>
     </row>
     <row r="115" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A115" s="65"/>
-      <c r="B115" s="63"/>
+      <c r="A115" s="45"/>
+      <c r="B115" s="43"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
@@ -9835,8 +9895,8 @@
       <c r="N115" s="10"/>
     </row>
     <row r="116" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A116" s="65"/>
-      <c r="B116" s="63"/>
+      <c r="A116" s="45"/>
+      <c r="B116" s="43"/>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -9851,8 +9911,8 @@
       <c r="N116" s="10"/>
     </row>
     <row r="117" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A117" s="65"/>
-      <c r="B117" s="63"/>
+      <c r="A117" s="45"/>
+      <c r="B117" s="43"/>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -9867,8 +9927,8 @@
       <c r="N117" s="10"/>
     </row>
     <row r="118" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A118" s="65"/>
-      <c r="B118" s="63"/>
+      <c r="A118" s="45"/>
+      <c r="B118" s="43"/>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -9883,8 +9943,8 @@
       <c r="N118" s="10"/>
     </row>
     <row r="119" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A119" s="65"/>
-      <c r="B119" s="63"/>
+      <c r="A119" s="45"/>
+      <c r="B119" s="43"/>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -9899,8 +9959,8 @@
       <c r="N119" s="10"/>
     </row>
     <row r="120" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A120" s="65"/>
-      <c r="B120" s="63"/>
+      <c r="A120" s="45"/>
+      <c r="B120" s="43"/>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -9915,8 +9975,8 @@
       <c r="N120" s="10"/>
     </row>
     <row r="121" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A121" s="65"/>
-      <c r="B121" s="63"/>
+      <c r="A121" s="45"/>
+      <c r="B121" s="43"/>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -9931,8 +9991,8 @@
       <c r="N121" s="10"/>
     </row>
     <row r="122" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A122" s="65"/>
-      <c r="B122" s="63"/>
+      <c r="A122" s="45"/>
+      <c r="B122" s="43"/>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -9947,8 +10007,8 @@
       <c r="N122" s="10"/>
     </row>
     <row r="123" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A123" s="65"/>
-      <c r="B123" s="63"/>
+      <c r="A123" s="45"/>
+      <c r="B123" s="43"/>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
@@ -9963,8 +10023,8 @@
       <c r="N123" s="10"/>
     </row>
     <row r="124" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A124" s="65"/>
-      <c r="B124" s="63"/>
+      <c r="A124" s="45"/>
+      <c r="B124" s="43"/>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
@@ -9979,8 +10039,8 @@
       <c r="N124" s="10"/>
     </row>
     <row r="125" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A125" s="65"/>
-      <c r="B125" s="63"/>
+      <c r="A125" s="45"/>
+      <c r="B125" s="43"/>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
@@ -9995,8 +10055,8 @@
       <c r="N125" s="10"/>
     </row>
     <row r="126" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A126" s="65"/>
-      <c r="B126" s="63"/>
+      <c r="A126" s="45"/>
+      <c r="B126" s="43"/>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
@@ -10011,8 +10071,8 @@
       <c r="N126" s="10"/>
     </row>
     <row r="127" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A127" s="65"/>
-      <c r="B127" s="63"/>
+      <c r="A127" s="45"/>
+      <c r="B127" s="43"/>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
@@ -10027,8 +10087,8 @@
       <c r="N127" s="10"/>
     </row>
     <row r="128" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A128" s="65"/>
-      <c r="B128" s="63"/>
+      <c r="A128" s="45"/>
+      <c r="B128" s="43"/>
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
@@ -10043,8 +10103,8 @@
       <c r="N128" s="10"/>
     </row>
     <row r="129" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A129" s="65"/>
-      <c r="B129" s="63"/>
+      <c r="A129" s="45"/>
+      <c r="B129" s="43"/>
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
@@ -10059,8 +10119,8 @@
       <c r="N129" s="10"/>
     </row>
     <row r="130" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A130" s="65"/>
-      <c r="B130" s="63"/>
+      <c r="A130" s="45"/>
+      <c r="B130" s="43"/>
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
@@ -10075,8 +10135,8 @@
       <c r="N130" s="10"/>
     </row>
     <row r="131" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A131" s="65"/>
-      <c r="B131" s="63"/>
+      <c r="A131" s="45"/>
+      <c r="B131" s="43"/>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
@@ -10091,8 +10151,8 @@
       <c r="N131" s="10"/>
     </row>
     <row r="132" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A132" s="65"/>
-      <c r="B132" s="63"/>
+      <c r="A132" s="45"/>
+      <c r="B132" s="43"/>
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
@@ -10107,8 +10167,8 @@
       <c r="N132" s="10"/>
     </row>
     <row r="133" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A133" s="65"/>
-      <c r="B133" s="63"/>
+      <c r="A133" s="45"/>
+      <c r="B133" s="43"/>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
@@ -10123,8 +10183,8 @@
       <c r="N133" s="10"/>
     </row>
     <row r="134" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A134" s="65"/>
-      <c r="B134" s="63"/>
+      <c r="A134" s="45"/>
+      <c r="B134" s="43"/>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
@@ -10139,8 +10199,8 @@
       <c r="N134" s="10"/>
     </row>
     <row r="135" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A135" s="65"/>
-      <c r="B135" s="63"/>
+      <c r="A135" s="45"/>
+      <c r="B135" s="43"/>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
@@ -10155,8 +10215,8 @@
       <c r="N135" s="10"/>
     </row>
     <row r="136" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A136" s="65"/>
-      <c r="B136" s="63"/>
+      <c r="A136" s="45"/>
+      <c r="B136" s="43"/>
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
@@ -10171,8 +10231,8 @@
       <c r="N136" s="10"/>
     </row>
     <row r="137" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A137" s="65"/>
-      <c r="B137" s="63"/>
+      <c r="A137" s="45"/>
+      <c r="B137" s="43"/>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
@@ -10187,8 +10247,8 @@
       <c r="N137" s="10"/>
     </row>
     <row r="138" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A138" s="65"/>
-      <c r="B138" s="63"/>
+      <c r="A138" s="45"/>
+      <c r="B138" s="43"/>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
@@ -10203,8 +10263,8 @@
       <c r="N138" s="10"/>
     </row>
     <row r="139" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A139" s="65"/>
-      <c r="B139" s="63"/>
+      <c r="A139" s="45"/>
+      <c r="B139" s="43"/>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
@@ -10219,8 +10279,8 @@
       <c r="N139" s="10"/>
     </row>
     <row r="140" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A140" s="65"/>
-      <c r="B140" s="63"/>
+      <c r="A140" s="45"/>
+      <c r="B140" s="43"/>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
@@ -10235,8 +10295,8 @@
       <c r="N140" s="10"/>
     </row>
     <row r="141" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A141" s="65"/>
-      <c r="B141" s="63"/>
+      <c r="A141" s="45"/>
+      <c r="B141" s="43"/>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
@@ -10251,8 +10311,8 @@
       <c r="N141" s="10"/>
     </row>
     <row r="142" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A142" s="65"/>
-      <c r="B142" s="63"/>
+      <c r="A142" s="45"/>
+      <c r="B142" s="43"/>
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
@@ -10267,8 +10327,8 @@
       <c r="N142" s="10"/>
     </row>
     <row r="143" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A143" s="65"/>
-      <c r="B143" s="63"/>
+      <c r="A143" s="45"/>
+      <c r="B143" s="43"/>
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
@@ -10283,8 +10343,8 @@
       <c r="N143" s="10"/>
     </row>
     <row r="144" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A144" s="65"/>
-      <c r="B144" s="63"/>
+      <c r="A144" s="45"/>
+      <c r="B144" s="43"/>
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
@@ -10299,8 +10359,8 @@
       <c r="N144" s="10"/>
     </row>
     <row r="145" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A145" s="65"/>
-      <c r="B145" s="63"/>
+      <c r="A145" s="45"/>
+      <c r="B145" s="43"/>
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
@@ -10315,8 +10375,8 @@
       <c r="N145" s="10"/>
     </row>
     <row r="146" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A146" s="65"/>
-      <c r="B146" s="63"/>
+      <c r="A146" s="45"/>
+      <c r="B146" s="43"/>
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
@@ -10331,8 +10391,8 @@
       <c r="N146" s="10"/>
     </row>
     <row r="147" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A147" s="65"/>
-      <c r="B147" s="63"/>
+      <c r="A147" s="45"/>
+      <c r="B147" s="43"/>
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
@@ -10347,8 +10407,8 @@
       <c r="N147" s="10"/>
     </row>
     <row r="148" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A148" s="65"/>
-      <c r="B148" s="63"/>
+      <c r="A148" s="45"/>
+      <c r="B148" s="43"/>
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
@@ -10363,8 +10423,8 @@
       <c r="N148" s="10"/>
     </row>
     <row r="149" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A149" s="65"/>
-      <c r="B149" s="63"/>
+      <c r="A149" s="45"/>
+      <c r="B149" s="43"/>
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
@@ -10379,8 +10439,8 @@
       <c r="N149" s="10"/>
     </row>
     <row r="150" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A150" s="65"/>
-      <c r="B150" s="63"/>
+      <c r="A150" s="45"/>
+      <c r="B150" s="43"/>
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
@@ -10395,8 +10455,8 @@
       <c r="N150" s="10"/>
     </row>
     <row r="151" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A151" s="65"/>
-      <c r="B151" s="63"/>
+      <c r="A151" s="45"/>
+      <c r="B151" s="43"/>
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
@@ -10411,8 +10471,8 @@
       <c r="N151" s="10"/>
     </row>
     <row r="152" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A152" s="65"/>
-      <c r="B152" s="63"/>
+      <c r="A152" s="45"/>
+      <c r="B152" s="43"/>
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -10427,8 +10487,8 @@
       <c r="N152" s="10"/>
     </row>
     <row r="153" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A153" s="65"/>
-      <c r="B153" s="63"/>
+      <c r="A153" s="45"/>
+      <c r="B153" s="43"/>
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
@@ -10443,8 +10503,8 @@
       <c r="N153" s="10"/>
     </row>
     <row r="154" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A154" s="65"/>
-      <c r="B154" s="63"/>
+      <c r="A154" s="45"/>
+      <c r="B154" s="43"/>
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
@@ -10459,8 +10519,8 @@
       <c r="N154" s="10"/>
     </row>
     <row r="155" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A155" s="65"/>
-      <c r="B155" s="63"/>
+      <c r="A155" s="45"/>
+      <c r="B155" s="43"/>
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
@@ -10475,8 +10535,8 @@
       <c r="N155" s="10"/>
     </row>
     <row r="156" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A156" s="65"/>
-      <c r="B156" s="63"/>
+      <c r="A156" s="45"/>
+      <c r="B156" s="43"/>
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
@@ -10491,8 +10551,8 @@
       <c r="N156" s="10"/>
     </row>
     <row r="157" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A157" s="65"/>
-      <c r="B157" s="63"/>
+      <c r="A157" s="45"/>
+      <c r="B157" s="43"/>
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
@@ -10507,8 +10567,8 @@
       <c r="N157" s="10"/>
     </row>
     <row r="158" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A158" s="65"/>
-      <c r="B158" s="63"/>
+      <c r="A158" s="45"/>
+      <c r="B158" s="43"/>
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
@@ -10523,8 +10583,8 @@
       <c r="N158" s="10"/>
     </row>
     <row r="159" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A159" s="65"/>
-      <c r="B159" s="63"/>
+      <c r="A159" s="45"/>
+      <c r="B159" s="43"/>
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
@@ -10539,8 +10599,8 @@
       <c r="N159" s="10"/>
     </row>
     <row r="160" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A160" s="65"/>
-      <c r="B160" s="63"/>
+      <c r="A160" s="45"/>
+      <c r="B160" s="43"/>
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -10555,8 +10615,8 @@
       <c r="N160" s="10"/>
     </row>
     <row r="161" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A161" s="65"/>
-      <c r="B161" s="63"/>
+      <c r="A161" s="45"/>
+      <c r="B161" s="43"/>
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
@@ -10571,8 +10631,8 @@
       <c r="N161" s="10"/>
     </row>
     <row r="162" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A162" s="65"/>
-      <c r="B162" s="63"/>
+      <c r="A162" s="45"/>
+      <c r="B162" s="43"/>
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -10587,8 +10647,8 @@
       <c r="N162" s="10"/>
     </row>
     <row r="163" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A163" s="65"/>
-      <c r="B163" s="63"/>
+      <c r="A163" s="45"/>
+      <c r="B163" s="43"/>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -10603,8 +10663,8 @@
       <c r="N163" s="10"/>
     </row>
     <row r="164" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A164" s="65"/>
-      <c r="B164" s="63"/>
+      <c r="A164" s="45"/>
+      <c r="B164" s="43"/>
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
@@ -10619,8 +10679,8 @@
       <c r="N164" s="10"/>
     </row>
     <row r="165" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A165" s="65"/>
-      <c r="B165" s="63"/>
+      <c r="A165" s="45"/>
+      <c r="B165" s="43"/>
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
@@ -10635,8 +10695,8 @@
       <c r="N165" s="10"/>
     </row>
     <row r="166" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A166" s="65"/>
-      <c r="B166" s="63"/>
+      <c r="A166" s="45"/>
+      <c r="B166" s="43"/>
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
@@ -10651,8 +10711,8 @@
       <c r="N166" s="10"/>
     </row>
     <row r="167" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A167" s="65"/>
-      <c r="B167" s="63"/>
+      <c r="A167" s="45"/>
+      <c r="B167" s="43"/>
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
@@ -10667,8 +10727,8 @@
       <c r="N167" s="10"/>
     </row>
     <row r="168" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A168" s="65"/>
-      <c r="B168" s="63"/>
+      <c r="A168" s="45"/>
+      <c r="B168" s="43"/>
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
@@ -10683,8 +10743,8 @@
       <c r="N168" s="10"/>
     </row>
     <row r="169" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A169" s="65"/>
-      <c r="B169" s="63"/>
+      <c r="A169" s="45"/>
+      <c r="B169" s="43"/>
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
@@ -10699,8 +10759,8 @@
       <c r="N169" s="10"/>
     </row>
     <row r="170" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A170" s="65"/>
-      <c r="B170" s="63"/>
+      <c r="A170" s="45"/>
+      <c r="B170" s="43"/>
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -10715,8 +10775,8 @@
       <c r="N170" s="10"/>
     </row>
     <row r="171" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A171" s="65"/>
-      <c r="B171" s="63"/>
+      <c r="A171" s="45"/>
+      <c r="B171" s="43"/>
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
@@ -10731,8 +10791,8 @@
       <c r="N171" s="10"/>
     </row>
     <row r="172" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A172" s="65"/>
-      <c r="B172" s="63"/>
+      <c r="A172" s="45"/>
+      <c r="B172" s="43"/>
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
@@ -10747,8 +10807,8 @@
       <c r="N172" s="10"/>
     </row>
     <row r="173" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A173" s="65"/>
-      <c r="B173" s="63"/>
+      <c r="A173" s="45"/>
+      <c r="B173" s="43"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
@@ -10763,8 +10823,8 @@
       <c r="N173" s="10"/>
     </row>
     <row r="174" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A174" s="65"/>
-      <c r="B174" s="63"/>
+      <c r="A174" s="45"/>
+      <c r="B174" s="43"/>
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
@@ -10779,8 +10839,8 @@
       <c r="N174" s="10"/>
     </row>
     <row r="175" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A175" s="65"/>
-      <c r="B175" s="63"/>
+      <c r="A175" s="45"/>
+      <c r="B175" s="43"/>
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
@@ -10795,8 +10855,8 @@
       <c r="N175" s="10"/>
     </row>
     <row r="176" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A176" s="65"/>
-      <c r="B176" s="63"/>
+      <c r="A176" s="45"/>
+      <c r="B176" s="43"/>
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
@@ -10811,8 +10871,8 @@
       <c r="N176" s="10"/>
     </row>
     <row r="177" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A177" s="65"/>
-      <c r="B177" s="63"/>
+      <c r="A177" s="45"/>
+      <c r="B177" s="43"/>
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
@@ -10827,8 +10887,8 @@
       <c r="N177" s="10"/>
     </row>
     <row r="178" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A178" s="65"/>
-      <c r="B178" s="63"/>
+      <c r="A178" s="45"/>
+      <c r="B178" s="43"/>
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
       <c r="E178" s="9"/>
@@ -10843,8 +10903,8 @@
       <c r="N178" s="10"/>
     </row>
     <row r="179" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A179" s="65"/>
-      <c r="B179" s="63"/>
+      <c r="A179" s="45"/>
+      <c r="B179" s="43"/>
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
       <c r="E179" s="9"/>
@@ -10859,8 +10919,8 @@
       <c r="N179" s="10"/>
     </row>
     <row r="180" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A180" s="65"/>
-      <c r="B180" s="63"/>
+      <c r="A180" s="45"/>
+      <c r="B180" s="43"/>
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
       <c r="E180" s="9"/>
@@ -10875,8 +10935,8 @@
       <c r="N180" s="10"/>
     </row>
     <row r="181" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A181" s="65"/>
-      <c r="B181" s="63"/>
+      <c r="A181" s="45"/>
+      <c r="B181" s="43"/>
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
       <c r="E181" s="9"/>
@@ -10891,8 +10951,8 @@
       <c r="N181" s="10"/>
     </row>
     <row r="182" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A182" s="65"/>
-      <c r="B182" s="63"/>
+      <c r="A182" s="45"/>
+      <c r="B182" s="43"/>
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
@@ -10907,8 +10967,8 @@
       <c r="N182" s="10"/>
     </row>
     <row r="183" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A183" s="65"/>
-      <c r="B183" s="63"/>
+      <c r="A183" s="45"/>
+      <c r="B183" s="43"/>
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
       <c r="E183" s="9"/>
@@ -10923,8 +10983,8 @@
       <c r="N183" s="10"/>
     </row>
     <row r="184" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A184" s="65"/>
-      <c r="B184" s="63"/>
+      <c r="A184" s="45"/>
+      <c r="B184" s="43"/>
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
       <c r="E184" s="9"/>
@@ -10939,8 +10999,8 @@
       <c r="N184" s="10"/>
     </row>
     <row r="185" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A185" s="65"/>
-      <c r="B185" s="63"/>
+      <c r="A185" s="45"/>
+      <c r="B185" s="43"/>
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
       <c r="E185" s="9"/>
@@ -10955,8 +11015,8 @@
       <c r="N185" s="10"/>
     </row>
     <row r="186" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A186" s="65"/>
-      <c r="B186" s="63"/>
+      <c r="A186" s="45"/>
+      <c r="B186" s="43"/>
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
       <c r="E186" s="9"/>
@@ -10971,8 +11031,8 @@
       <c r="N186" s="10"/>
     </row>
     <row r="187" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A187" s="65"/>
-      <c r="B187" s="63"/>
+      <c r="A187" s="45"/>
+      <c r="B187" s="43"/>
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
       <c r="E187" s="9"/>
@@ -10987,8 +11047,8 @@
       <c r="N187" s="10"/>
     </row>
     <row r="188" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A188" s="65"/>
-      <c r="B188" s="63"/>
+      <c r="A188" s="45"/>
+      <c r="B188" s="43"/>
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
       <c r="E188" s="9"/>
@@ -11003,8 +11063,8 @@
       <c r="N188" s="10"/>
     </row>
     <row r="189" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A189" s="65"/>
-      <c r="B189" s="63"/>
+      <c r="A189" s="45"/>
+      <c r="B189" s="43"/>
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -11019,8 +11079,8 @@
       <c r="N189" s="10"/>
     </row>
     <row r="190" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A190" s="65"/>
-      <c r="B190" s="63"/>
+      <c r="A190" s="45"/>
+      <c r="B190" s="43"/>
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
       <c r="E190" s="9"/>
@@ -11035,8 +11095,8 @@
       <c r="N190" s="10"/>
     </row>
     <row r="191" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A191" s="65"/>
-      <c r="B191" s="63"/>
+      <c r="A191" s="45"/>
+      <c r="B191" s="43"/>
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
       <c r="E191" s="9"/>
@@ -11051,8 +11111,8 @@
       <c r="N191" s="10"/>
     </row>
     <row r="192" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A192" s="65"/>
-      <c r="B192" s="63"/>
+      <c r="A192" s="45"/>
+      <c r="B192" s="43"/>
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
       <c r="E192" s="9"/>
@@ -11067,8 +11127,8 @@
       <c r="N192" s="10"/>
     </row>
     <row r="193" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A193" s="65"/>
-      <c r="B193" s="63"/>
+      <c r="A193" s="45"/>
+      <c r="B193" s="43"/>
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
       <c r="E193" s="9"/>
@@ -11083,8 +11143,8 @@
       <c r="N193" s="10"/>
     </row>
     <row r="194" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A194" s="65"/>
-      <c r="B194" s="63"/>
+      <c r="A194" s="45"/>
+      <c r="B194" s="43"/>
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
       <c r="E194" s="9"/>
@@ -11099,8 +11159,8 @@
       <c r="N194" s="10"/>
     </row>
     <row r="195" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A195" s="65"/>
-      <c r="B195" s="63"/>
+      <c r="A195" s="45"/>
+      <c r="B195" s="43"/>
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
       <c r="E195" s="9"/>
@@ -11115,8 +11175,8 @@
       <c r="N195" s="10"/>
     </row>
     <row r="196" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A196" s="65"/>
-      <c r="B196" s="63"/>
+      <c r="A196" s="45"/>
+      <c r="B196" s="43"/>
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
       <c r="E196" s="9"/>
@@ -11131,8 +11191,8 @@
       <c r="N196" s="10"/>
     </row>
     <row r="197" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A197" s="65"/>
-      <c r="B197" s="63"/>
+      <c r="A197" s="45"/>
+      <c r="B197" s="43"/>
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
       <c r="E197" s="9"/>
@@ -11147,8 +11207,8 @@
       <c r="N197" s="10"/>
     </row>
     <row r="198" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A198" s="65"/>
-      <c r="B198" s="63"/>
+      <c r="A198" s="45"/>
+      <c r="B198" s="43"/>
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
       <c r="E198" s="9"/>
@@ -11163,8 +11223,8 @@
       <c r="N198" s="10"/>
     </row>
     <row r="199" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A199" s="65"/>
-      <c r="B199" s="63"/>
+      <c r="A199" s="45"/>
+      <c r="B199" s="43"/>
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
       <c r="E199" s="9"/>
@@ -11179,8 +11239,8 @@
       <c r="N199" s="10"/>
     </row>
     <row r="200" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A200" s="65"/>
-      <c r="B200" s="63"/>
+      <c r="A200" s="45"/>
+      <c r="B200" s="43"/>
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
       <c r="E200" s="9"/>
@@ -11195,8 +11255,8 @@
       <c r="N200" s="10"/>
     </row>
     <row r="201" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A201" s="65"/>
-      <c r="B201" s="63"/>
+      <c r="A201" s="45"/>
+      <c r="B201" s="43"/>
       <c r="C201" s="9"/>
       <c r="D201" s="9"/>
       <c r="E201" s="9"/>
@@ -11211,8 +11271,8 @@
       <c r="N201" s="10"/>
     </row>
     <row r="202" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A202" s="65"/>
-      <c r="B202" s="63"/>
+      <c r="A202" s="45"/>
+      <c r="B202" s="43"/>
       <c r="C202" s="9"/>
       <c r="D202" s="9"/>
       <c r="E202" s="9"/>
@@ -11227,8 +11287,8 @@
       <c r="N202" s="10"/>
     </row>
     <row r="203" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A203" s="65"/>
-      <c r="B203" s="63"/>
+      <c r="A203" s="45"/>
+      <c r="B203" s="43"/>
       <c r="C203" s="9"/>
       <c r="D203" s="9"/>
       <c r="E203" s="9"/>
@@ -11243,8 +11303,8 @@
       <c r="N203" s="10"/>
     </row>
     <row r="204" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A204" s="65"/>
-      <c r="B204" s="63"/>
+      <c r="A204" s="45"/>
+      <c r="B204" s="43"/>
       <c r="C204" s="9"/>
       <c r="D204" s="9"/>
       <c r="E204" s="9"/>
@@ -11259,8 +11319,8 @@
       <c r="N204" s="10"/>
     </row>
     <row r="205" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A205" s="65"/>
-      <c r="B205" s="63"/>
+      <c r="A205" s="45"/>
+      <c r="B205" s="43"/>
       <c r="C205" s="9"/>
       <c r="D205" s="9"/>
       <c r="E205" s="9"/>
@@ -11275,8 +11335,8 @@
       <c r="N205" s="10"/>
     </row>
     <row r="206" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A206" s="65"/>
-      <c r="B206" s="63"/>
+      <c r="A206" s="45"/>
+      <c r="B206" s="43"/>
       <c r="C206" s="9"/>
       <c r="D206" s="9"/>
       <c r="E206" s="9"/>
@@ -11291,8 +11351,8 @@
       <c r="N206" s="10"/>
     </row>
     <row r="207" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A207" s="65"/>
-      <c r="B207" s="63"/>
+      <c r="A207" s="45"/>
+      <c r="B207" s="43"/>
       <c r="C207" s="9"/>
       <c r="D207" s="9"/>
       <c r="E207" s="9"/>
@@ -11307,8 +11367,8 @@
       <c r="N207" s="10"/>
     </row>
     <row r="208" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A208" s="65"/>
-      <c r="B208" s="63"/>
+      <c r="A208" s="45"/>
+      <c r="B208" s="43"/>
       <c r="C208" s="9"/>
       <c r="D208" s="9"/>
       <c r="E208" s="9"/>
@@ -11323,8 +11383,8 @@
       <c r="N208" s="10"/>
     </row>
     <row r="209" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A209" s="65"/>
-      <c r="B209" s="63"/>
+      <c r="A209" s="45"/>
+      <c r="B209" s="43"/>
       <c r="C209" s="9"/>
       <c r="D209" s="9"/>
       <c r="E209" s="9"/>
@@ -11339,8 +11399,8 @@
       <c r="N209" s="10"/>
     </row>
     <row r="210" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A210" s="65"/>
-      <c r="B210" s="63"/>
+      <c r="A210" s="45"/>
+      <c r="B210" s="43"/>
       <c r="C210" s="9"/>
       <c r="D210" s="9"/>
       <c r="E210" s="9"/>
@@ -11355,8 +11415,8 @@
       <c r="N210" s="10"/>
     </row>
     <row r="211" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A211" s="65"/>
-      <c r="B211" s="63"/>
+      <c r="A211" s="45"/>
+      <c r="B211" s="43"/>
       <c r="C211" s="9"/>
       <c r="D211" s="9"/>
       <c r="E211" s="9"/>
@@ -11371,8 +11431,8 @@
       <c r="N211" s="10"/>
     </row>
     <row r="212" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A212" s="65"/>
-      <c r="B212" s="63"/>
+      <c r="A212" s="45"/>
+      <c r="B212" s="43"/>
       <c r="C212" s="9"/>
       <c r="D212" s="9"/>
       <c r="E212" s="9"/>
@@ -11387,8 +11447,8 @@
       <c r="N212" s="10"/>
     </row>
     <row r="213" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A213" s="65"/>
-      <c r="B213" s="63"/>
+      <c r="A213" s="45"/>
+      <c r="B213" s="43"/>
       <c r="C213" s="9"/>
       <c r="D213" s="9"/>
       <c r="E213" s="9"/>
@@ -11403,8 +11463,8 @@
       <c r="N213" s="10"/>
     </row>
     <row r="214" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A214" s="65"/>
-      <c r="B214" s="63"/>
+      <c r="A214" s="45"/>
+      <c r="B214" s="43"/>
       <c r="C214" s="9"/>
       <c r="D214" s="9"/>
       <c r="E214" s="9"/>
@@ -11419,8 +11479,8 @@
       <c r="N214" s="10"/>
     </row>
     <row r="215" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A215" s="65"/>
-      <c r="B215" s="63"/>
+      <c r="A215" s="45"/>
+      <c r="B215" s="43"/>
       <c r="C215" s="9"/>
       <c r="D215" s="9"/>
       <c r="E215" s="9"/>
@@ -11435,8 +11495,8 @@
       <c r="N215" s="10"/>
     </row>
     <row r="216" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A216" s="65"/>
-      <c r="B216" s="63"/>
+      <c r="A216" s="45"/>
+      <c r="B216" s="43"/>
       <c r="C216" s="9"/>
       <c r="D216" s="9"/>
       <c r="E216" s="9"/>
@@ -11451,8 +11511,8 @@
       <c r="N216" s="10"/>
     </row>
     <row r="217" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A217" s="65"/>
-      <c r="B217" s="63"/>
+      <c r="A217" s="45"/>
+      <c r="B217" s="43"/>
       <c r="C217" s="9"/>
       <c r="D217" s="9"/>
       <c r="E217" s="9"/>
@@ -11467,8 +11527,8 @@
       <c r="N217" s="10"/>
     </row>
     <row r="218" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A218" s="65"/>
-      <c r="B218" s="63"/>
+      <c r="A218" s="45"/>
+      <c r="B218" s="43"/>
       <c r="C218" s="9"/>
       <c r="D218" s="9"/>
       <c r="E218" s="9"/>
@@ -11483,8 +11543,8 @@
       <c r="N218" s="10"/>
     </row>
     <row r="219" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A219" s="65"/>
-      <c r="B219" s="63"/>
+      <c r="A219" s="45"/>
+      <c r="B219" s="43"/>
       <c r="C219" s="9"/>
       <c r="D219" s="9"/>
       <c r="E219" s="9"/>
@@ -11499,8 +11559,8 @@
       <c r="N219" s="10"/>
     </row>
     <row r="220" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A220" s="65"/>
-      <c r="B220" s="63"/>
+      <c r="A220" s="45"/>
+      <c r="B220" s="43"/>
       <c r="C220" s="9"/>
       <c r="D220" s="9"/>
       <c r="E220" s="9"/>
@@ -11515,8 +11575,8 @@
       <c r="N220" s="10"/>
     </row>
     <row r="221" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A221" s="65"/>
-      <c r="B221" s="63"/>
+      <c r="A221" s="45"/>
+      <c r="B221" s="43"/>
       <c r="C221" s="9"/>
       <c r="D221" s="9"/>
       <c r="E221" s="9"/>
@@ -11531,8 +11591,8 @@
       <c r="N221" s="10"/>
     </row>
     <row r="222" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A222" s="65"/>
-      <c r="B222" s="63"/>
+      <c r="A222" s="45"/>
+      <c r="B222" s="43"/>
       <c r="C222" s="9"/>
       <c r="D222" s="9"/>
       <c r="E222" s="9"/>
@@ -11547,8 +11607,8 @@
       <c r="N222" s="10"/>
     </row>
     <row r="223" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A223" s="65"/>
-      <c r="B223" s="63"/>
+      <c r="A223" s="45"/>
+      <c r="B223" s="43"/>
       <c r="C223" s="9"/>
       <c r="D223" s="9"/>
       <c r="E223" s="9"/>
@@ -11563,8 +11623,8 @@
       <c r="N223" s="10"/>
     </row>
     <row r="224" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A224" s="65"/>
-      <c r="B224" s="63"/>
+      <c r="A224" s="45"/>
+      <c r="B224" s="43"/>
       <c r="C224" s="9"/>
       <c r="D224" s="9"/>
       <c r="E224" s="9"/>
@@ -11579,8 +11639,8 @@
       <c r="N224" s="10"/>
     </row>
     <row r="225" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A225" s="65"/>
-      <c r="B225" s="63"/>
+      <c r="A225" s="45"/>
+      <c r="B225" s="43"/>
       <c r="C225" s="9"/>
       <c r="D225" s="9"/>
       <c r="E225" s="9"/>
@@ -11595,8 +11655,8 @@
       <c r="N225" s="10"/>
     </row>
     <row r="226" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A226" s="65"/>
-      <c r="B226" s="63"/>
+      <c r="A226" s="45"/>
+      <c r="B226" s="43"/>
       <c r="C226" s="9"/>
       <c r="D226" s="9"/>
       <c r="E226" s="9"/>
@@ -11611,8 +11671,8 @@
       <c r="N226" s="10"/>
     </row>
     <row r="227" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A227" s="65"/>
-      <c r="B227" s="63"/>
+      <c r="A227" s="45"/>
+      <c r="B227" s="43"/>
       <c r="C227" s="9"/>
       <c r="D227" s="9"/>
       <c r="E227" s="9"/>
@@ -11627,8 +11687,8 @@
       <c r="N227" s="10"/>
     </row>
     <row r="228" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A228" s="65"/>
-      <c r="B228" s="63"/>
+      <c r="A228" s="45"/>
+      <c r="B228" s="43"/>
       <c r="C228" s="9"/>
       <c r="D228" s="9"/>
       <c r="E228" s="9"/>
@@ -11643,8 +11703,8 @@
       <c r="N228" s="10"/>
     </row>
     <row r="229" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A229" s="65"/>
-      <c r="B229" s="63"/>
+      <c r="A229" s="45"/>
+      <c r="B229" s="43"/>
       <c r="C229" s="9"/>
       <c r="D229" s="9"/>
       <c r="E229" s="9"/>
@@ -11659,8 +11719,8 @@
       <c r="N229" s="10"/>
     </row>
     <row r="230" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A230" s="65"/>
-      <c r="B230" s="63"/>
+      <c r="A230" s="45"/>
+      <c r="B230" s="43"/>
       <c r="C230" s="9"/>
       <c r="D230" s="9"/>
       <c r="E230" s="9"/>
@@ -11675,8 +11735,8 @@
       <c r="N230" s="10"/>
     </row>
     <row r="231" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A231" s="65"/>
-      <c r="B231" s="63"/>
+      <c r="A231" s="45"/>
+      <c r="B231" s="43"/>
       <c r="C231" s="9"/>
       <c r="D231" s="9"/>
       <c r="E231" s="9"/>
@@ -11691,8 +11751,8 @@
       <c r="N231" s="10"/>
     </row>
     <row r="232" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A232" s="65"/>
-      <c r="B232" s="63"/>
+      <c r="A232" s="45"/>
+      <c r="B232" s="43"/>
       <c r="C232" s="9"/>
       <c r="D232" s="9"/>
       <c r="E232" s="9"/>
@@ -11707,8 +11767,8 @@
       <c r="N232" s="10"/>
     </row>
     <row r="233" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A233" s="65"/>
-      <c r="B233" s="63"/>
+      <c r="A233" s="45"/>
+      <c r="B233" s="43"/>
       <c r="C233" s="9"/>
       <c r="D233" s="9"/>
       <c r="E233" s="9"/>
@@ -11723,8 +11783,8 @@
       <c r="N233" s="10"/>
     </row>
     <row r="234" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A234" s="65"/>
-      <c r="B234" s="63"/>
+      <c r="A234" s="45"/>
+      <c r="B234" s="43"/>
       <c r="C234" s="9"/>
       <c r="D234" s="9"/>
       <c r="E234" s="9"/>
@@ -11739,8 +11799,8 @@
       <c r="N234" s="10"/>
     </row>
     <row r="235" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A235" s="65"/>
-      <c r="B235" s="63"/>
+      <c r="A235" s="45"/>
+      <c r="B235" s="43"/>
       <c r="C235" s="9"/>
       <c r="D235" s="9"/>
       <c r="E235" s="9"/>
@@ -11755,8 +11815,8 @@
       <c r="N235" s="10"/>
     </row>
     <row r="236" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A236" s="65"/>
-      <c r="B236" s="63"/>
+      <c r="A236" s="45"/>
+      <c r="B236" s="43"/>
       <c r="C236" s="9"/>
       <c r="D236" s="9"/>
       <c r="E236" s="9"/>
@@ -11771,8 +11831,8 @@
       <c r="N236" s="10"/>
     </row>
     <row r="237" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A237" s="65"/>
-      <c r="B237" s="63"/>
+      <c r="A237" s="45"/>
+      <c r="B237" s="43"/>
       <c r="C237" s="9"/>
       <c r="D237" s="9"/>
       <c r="E237" s="9"/>
@@ -11787,8 +11847,8 @@
       <c r="N237" s="10"/>
     </row>
     <row r="238" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A238" s="65"/>
-      <c r="B238" s="63"/>
+      <c r="A238" s="45"/>
+      <c r="B238" s="43"/>
       <c r="C238" s="9"/>
       <c r="D238" s="9"/>
       <c r="E238" s="9"/>
@@ -11803,8 +11863,8 @@
       <c r="N238" s="10"/>
     </row>
     <row r="239" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A239" s="65"/>
-      <c r="B239" s="63"/>
+      <c r="A239" s="45"/>
+      <c r="B239" s="43"/>
       <c r="C239" s="9"/>
       <c r="D239" s="9"/>
       <c r="E239" s="9"/>
@@ -11819,8 +11879,8 @@
       <c r="N239" s="10"/>
     </row>
     <row r="240" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A240" s="65"/>
-      <c r="B240" s="63"/>
+      <c r="A240" s="45"/>
+      <c r="B240" s="43"/>
       <c r="C240" s="9"/>
       <c r="D240" s="9"/>
       <c r="E240" s="9"/>
@@ -11835,8 +11895,8 @@
       <c r="N240" s="10"/>
     </row>
     <row r="241" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A241" s="65"/>
-      <c r="B241" s="63"/>
+      <c r="A241" s="45"/>
+      <c r="B241" s="43"/>
       <c r="C241" s="9"/>
       <c r="D241" s="9"/>
       <c r="E241" s="9"/>
@@ -11851,8 +11911,8 @@
       <c r="N241" s="10"/>
     </row>
     <row r="242" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A242" s="65"/>
-      <c r="B242" s="63"/>
+      <c r="A242" s="45"/>
+      <c r="B242" s="43"/>
       <c r="C242" s="9"/>
       <c r="D242" s="9"/>
       <c r="E242" s="9"/>
@@ -11867,8 +11927,8 @@
       <c r="N242" s="10"/>
     </row>
     <row r="243" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A243" s="65"/>
-      <c r="B243" s="63"/>
+      <c r="A243" s="45"/>
+      <c r="B243" s="43"/>
       <c r="C243" s="9"/>
       <c r="D243" s="9"/>
       <c r="E243" s="9"/>
@@ -11883,8 +11943,8 @@
       <c r="N243" s="10"/>
     </row>
     <row r="244" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A244" s="65"/>
-      <c r="B244" s="63"/>
+      <c r="A244" s="45"/>
+      <c r="B244" s="43"/>
       <c r="C244" s="9"/>
       <c r="D244" s="9"/>
       <c r="E244" s="9"/>
@@ -11899,8 +11959,8 @@
       <c r="N244" s="10"/>
     </row>
     <row r="245" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A245" s="65"/>
-      <c r="B245" s="63"/>
+      <c r="A245" s="45"/>
+      <c r="B245" s="43"/>
       <c r="C245" s="9"/>
       <c r="D245" s="9"/>
       <c r="E245" s="9"/>
@@ -11915,8 +11975,8 @@
       <c r="N245" s="10"/>
     </row>
     <row r="246" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A246" s="65"/>
-      <c r="B246" s="63"/>
+      <c r="A246" s="45"/>
+      <c r="B246" s="43"/>
       <c r="C246" s="9"/>
       <c r="D246" s="9"/>
       <c r="E246" s="9"/>
@@ -11931,8 +11991,8 @@
       <c r="N246" s="10"/>
     </row>
     <row r="247" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A247" s="65"/>
-      <c r="B247" s="63"/>
+      <c r="A247" s="45"/>
+      <c r="B247" s="43"/>
       <c r="C247" s="9"/>
       <c r="D247" s="9"/>
       <c r="E247" s="9"/>
@@ -11947,8 +12007,8 @@
       <c r="N247" s="10"/>
     </row>
     <row r="248" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A248" s="65"/>
-      <c r="B248" s="63"/>
+      <c r="A248" s="45"/>
+      <c r="B248" s="43"/>
       <c r="C248" s="9"/>
       <c r="D248" s="9"/>
       <c r="E248" s="9"/>
@@ -11963,8 +12023,8 @@
       <c r="N248" s="10"/>
     </row>
     <row r="249" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A249" s="65"/>
-      <c r="B249" s="63"/>
+      <c r="A249" s="45"/>
+      <c r="B249" s="43"/>
       <c r="C249" s="9"/>
       <c r="D249" s="9"/>
       <c r="E249" s="9"/>
@@ -11979,8 +12039,8 @@
       <c r="N249" s="10"/>
     </row>
     <row r="250" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A250" s="65"/>
-      <c r="B250" s="63"/>
+      <c r="A250" s="45"/>
+      <c r="B250" s="43"/>
       <c r="C250" s="9"/>
       <c r="D250" s="9"/>
       <c r="E250" s="9"/>
@@ -11995,8 +12055,8 @@
       <c r="N250" s="10"/>
     </row>
     <row r="251" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A251" s="65"/>
-      <c r="B251" s="63"/>
+      <c r="A251" s="45"/>
+      <c r="B251" s="43"/>
       <c r="C251" s="9"/>
       <c r="D251" s="9"/>
       <c r="E251" s="9"/>
@@ -12011,8 +12071,8 @@
       <c r="N251" s="10"/>
     </row>
     <row r="252" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A252" s="65"/>
-      <c r="B252" s="63"/>
+      <c r="A252" s="45"/>
+      <c r="B252" s="43"/>
       <c r="C252" s="9"/>
       <c r="D252" s="9"/>
       <c r="E252" s="9"/>
@@ -12027,8 +12087,8 @@
       <c r="N252" s="10"/>
     </row>
     <row r="253" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A253" s="65"/>
-      <c r="B253" s="63"/>
+      <c r="A253" s="45"/>
+      <c r="B253" s="43"/>
       <c r="C253" s="9"/>
       <c r="D253" s="9"/>
       <c r="E253" s="9"/>
@@ -12043,8 +12103,8 @@
       <c r="N253" s="10"/>
     </row>
     <row r="254" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A254" s="65"/>
-      <c r="B254" s="63"/>
+      <c r="A254" s="45"/>
+      <c r="B254" s="43"/>
       <c r="C254" s="9"/>
       <c r="D254" s="9"/>
       <c r="E254" s="9"/>
@@ -12059,8 +12119,8 @@
       <c r="N254" s="10"/>
     </row>
     <row r="255" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A255" s="65"/>
-      <c r="B255" s="63"/>
+      <c r="A255" s="45"/>
+      <c r="B255" s="43"/>
       <c r="C255" s="9"/>
       <c r="D255" s="9"/>
       <c r="E255" s="9"/>
@@ -12075,8 +12135,8 @@
       <c r="N255" s="10"/>
     </row>
     <row r="256" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A256" s="65"/>
-      <c r="B256" s="63"/>
+      <c r="A256" s="45"/>
+      <c r="B256" s="43"/>
       <c r="C256" s="9"/>
       <c r="D256" s="9"/>
       <c r="E256" s="9"/>
@@ -12091,8 +12151,8 @@
       <c r="N256" s="10"/>
     </row>
     <row r="257" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A257" s="65"/>
-      <c r="B257" s="63"/>
+      <c r="A257" s="45"/>
+      <c r="B257" s="43"/>
       <c r="C257" s="9"/>
       <c r="D257" s="9"/>
       <c r="E257" s="9"/>
@@ -12107,8 +12167,8 @@
       <c r="N257" s="10"/>
     </row>
     <row r="258" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A258" s="65"/>
-      <c r="B258" s="63"/>
+      <c r="A258" s="45"/>
+      <c r="B258" s="43"/>
       <c r="C258" s="9"/>
       <c r="D258" s="9"/>
       <c r="E258" s="9"/>
@@ -12123,8 +12183,8 @@
       <c r="N258" s="10"/>
     </row>
     <row r="259" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A259" s="65"/>
-      <c r="B259" s="63"/>
+      <c r="A259" s="45"/>
+      <c r="B259" s="43"/>
       <c r="C259" s="9"/>
       <c r="D259" s="9"/>
       <c r="E259" s="9"/>
@@ -12139,8 +12199,8 @@
       <c r="N259" s="10"/>
     </row>
     <row r="260" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A260" s="65"/>
-      <c r="B260" s="63"/>
+      <c r="A260" s="45"/>
+      <c r="B260" s="43"/>
       <c r="C260" s="9"/>
       <c r="D260" s="9"/>
       <c r="E260" s="9"/>
@@ -12155,8 +12215,8 @@
       <c r="N260" s="10"/>
     </row>
     <row r="261" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A261" s="65"/>
-      <c r="B261" s="63"/>
+      <c r="A261" s="45"/>
+      <c r="B261" s="43"/>
       <c r="C261" s="9"/>
       <c r="D261" s="9"/>
       <c r="E261" s="9"/>
@@ -12171,8 +12231,8 @@
       <c r="N261" s="10"/>
     </row>
     <row r="262" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A262" s="65"/>
-      <c r="B262" s="63"/>
+      <c r="A262" s="45"/>
+      <c r="B262" s="43"/>
       <c r="C262" s="9"/>
       <c r="D262" s="9"/>
       <c r="E262" s="9"/>
@@ -12187,8 +12247,8 @@
       <c r="N262" s="10"/>
     </row>
     <row r="263" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A263" s="65"/>
-      <c r="B263" s="63"/>
+      <c r="A263" s="45"/>
+      <c r="B263" s="43"/>
       <c r="C263" s="9"/>
       <c r="D263" s="9"/>
       <c r="E263" s="9"/>
@@ -12203,8 +12263,8 @@
       <c r="N263" s="10"/>
     </row>
     <row r="264" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A264" s="65"/>
-      <c r="B264" s="63"/>
+      <c r="A264" s="45"/>
+      <c r="B264" s="43"/>
       <c r="C264" s="9"/>
       <c r="D264" s="9"/>
       <c r="E264" s="9"/>
@@ -12219,8 +12279,8 @@
       <c r="N264" s="10"/>
     </row>
     <row r="265" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A265" s="65"/>
-      <c r="B265" s="63"/>
+      <c r="A265" s="45"/>
+      <c r="B265" s="43"/>
       <c r="C265" s="9"/>
       <c r="D265" s="9"/>
       <c r="E265" s="9"/>
@@ -12235,8 +12295,8 @@
       <c r="N265" s="10"/>
     </row>
     <row r="266" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A266" s="65"/>
-      <c r="B266" s="63"/>
+      <c r="A266" s="45"/>
+      <c r="B266" s="43"/>
       <c r="C266" s="9"/>
       <c r="D266" s="9"/>
       <c r="E266" s="9"/>
@@ -12251,8 +12311,8 @@
       <c r="N266" s="10"/>
     </row>
     <row r="267" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A267" s="65"/>
-      <c r="B267" s="63"/>
+      <c r="A267" s="45"/>
+      <c r="B267" s="43"/>
       <c r="C267" s="9"/>
       <c r="D267" s="9"/>
       <c r="E267" s="9"/>
@@ -12267,8 +12327,8 @@
       <c r="N267" s="10"/>
     </row>
     <row r="268" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A268" s="65"/>
-      <c r="B268" s="63"/>
+      <c r="A268" s="45"/>
+      <c r="B268" s="43"/>
       <c r="C268" s="9"/>
       <c r="D268" s="9"/>
       <c r="E268" s="9"/>
@@ -12283,8 +12343,8 @@
       <c r="N268" s="10"/>
     </row>
     <row r="269" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A269" s="65"/>
-      <c r="B269" s="63"/>
+      <c r="A269" s="45"/>
+      <c r="B269" s="43"/>
       <c r="C269" s="9"/>
       <c r="D269" s="9"/>
       <c r="E269" s="9"/>
@@ -12299,8 +12359,8 @@
       <c r="N269" s="10"/>
     </row>
     <row r="270" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A270" s="65"/>
-      <c r="B270" s="63"/>
+      <c r="A270" s="45"/>
+      <c r="B270" s="43"/>
       <c r="C270" s="9"/>
       <c r="D270" s="9"/>
       <c r="E270" s="9"/>
@@ -12315,8 +12375,8 @@
       <c r="N270" s="10"/>
     </row>
     <row r="271" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A271" s="65"/>
-      <c r="B271" s="63"/>
+      <c r="A271" s="45"/>
+      <c r="B271" s="43"/>
       <c r="C271" s="9"/>
       <c r="D271" s="9"/>
       <c r="E271" s="9"/>
@@ -12331,8 +12391,8 @@
       <c r="N271" s="10"/>
     </row>
     <row r="272" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A272" s="65"/>
-      <c r="B272" s="63"/>
+      <c r="A272" s="45"/>
+      <c r="B272" s="43"/>
       <c r="C272" s="9"/>
       <c r="D272" s="9"/>
       <c r="E272" s="9"/>
@@ -12347,8 +12407,8 @@
       <c r="N272" s="10"/>
     </row>
     <row r="273" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A273" s="65"/>
-      <c r="B273" s="63"/>
+      <c r="A273" s="45"/>
+      <c r="B273" s="43"/>
       <c r="C273" s="9"/>
       <c r="D273" s="9"/>
       <c r="E273" s="9"/>
@@ -12363,8 +12423,8 @@
       <c r="N273" s="10"/>
     </row>
     <row r="274" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A274" s="65"/>
-      <c r="B274" s="63"/>
+      <c r="A274" s="45"/>
+      <c r="B274" s="43"/>
       <c r="C274" s="9"/>
       <c r="D274" s="9"/>
       <c r="E274" s="9"/>
@@ -12379,8 +12439,8 @@
       <c r="N274" s="10"/>
     </row>
     <row r="275" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A275" s="65"/>
-      <c r="B275" s="63"/>
+      <c r="A275" s="45"/>
+      <c r="B275" s="43"/>
       <c r="C275" s="9"/>
       <c r="D275" s="9"/>
       <c r="E275" s="9"/>
@@ -12395,8 +12455,8 @@
       <c r="N275" s="10"/>
     </row>
     <row r="276" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A276" s="65"/>
-      <c r="B276" s="63"/>
+      <c r="A276" s="45"/>
+      <c r="B276" s="43"/>
       <c r="C276" s="9"/>
       <c r="D276" s="9"/>
       <c r="E276" s="9"/>
@@ -12411,8 +12471,8 @@
       <c r="N276" s="10"/>
     </row>
     <row r="277" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A277" s="65"/>
-      <c r="B277" s="63"/>
+      <c r="A277" s="45"/>
+      <c r="B277" s="43"/>
       <c r="C277" s="9"/>
       <c r="D277" s="9"/>
       <c r="E277" s="9"/>
@@ -12427,8 +12487,8 @@
       <c r="N277" s="10"/>
     </row>
     <row r="278" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A278" s="65"/>
-      <c r="B278" s="63"/>
+      <c r="A278" s="45"/>
+      <c r="B278" s="43"/>
       <c r="C278" s="9"/>
       <c r="D278" s="9"/>
       <c r="E278" s="9"/>
@@ -12443,8 +12503,8 @@
       <c r="N278" s="10"/>
     </row>
     <row r="279" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A279" s="65"/>
-      <c r="B279" s="63"/>
+      <c r="A279" s="45"/>
+      <c r="B279" s="43"/>
       <c r="C279" s="9"/>
       <c r="D279" s="9"/>
       <c r="E279" s="9"/>
@@ -12459,8 +12519,8 @@
       <c r="N279" s="10"/>
     </row>
     <row r="280" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A280" s="65"/>
-      <c r="B280" s="63"/>
+      <c r="A280" s="45"/>
+      <c r="B280" s="43"/>
       <c r="C280" s="9"/>
       <c r="D280" s="9"/>
       <c r="E280" s="9"/>
@@ -12475,8 +12535,8 @@
       <c r="N280" s="10"/>
     </row>
     <row r="281" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A281" s="65"/>
-      <c r="B281" s="63"/>
+      <c r="A281" s="45"/>
+      <c r="B281" s="43"/>
       <c r="C281" s="9"/>
       <c r="D281" s="9"/>
       <c r="E281" s="9"/>
@@ -12491,8 +12551,8 @@
       <c r="N281" s="10"/>
     </row>
     <row r="282" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A282" s="65"/>
-      <c r="B282" s="63"/>
+      <c r="A282" s="45"/>
+      <c r="B282" s="43"/>
       <c r="C282" s="9"/>
       <c r="D282" s="9"/>
       <c r="E282" s="9"/>
@@ -12507,8 +12567,8 @@
       <c r="N282" s="10"/>
     </row>
     <row r="283" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A283" s="65"/>
-      <c r="B283" s="63"/>
+      <c r="A283" s="45"/>
+      <c r="B283" s="43"/>
       <c r="C283" s="9"/>
       <c r="D283" s="9"/>
       <c r="E283" s="9"/>
@@ -12523,8 +12583,8 @@
       <c r="N283" s="10"/>
     </row>
     <row r="284" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A284" s="65"/>
-      <c r="B284" s="63"/>
+      <c r="A284" s="45"/>
+      <c r="B284" s="43"/>
       <c r="C284" s="9"/>
       <c r="D284" s="9"/>
       <c r="E284" s="9"/>
@@ -12539,8 +12599,8 @@
       <c r="N284" s="10"/>
     </row>
     <row r="285" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A285" s="65"/>
-      <c r="B285" s="63"/>
+      <c r="A285" s="45"/>
+      <c r="B285" s="43"/>
       <c r="C285" s="9"/>
       <c r="D285" s="9"/>
       <c r="E285" s="9"/>
@@ -12555,8 +12615,8 @@
       <c r="N285" s="10"/>
     </row>
     <row r="286" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A286" s="65"/>
-      <c r="B286" s="63"/>
+      <c r="A286" s="45"/>
+      <c r="B286" s="43"/>
       <c r="C286" s="9"/>
       <c r="D286" s="9"/>
       <c r="E286" s="9"/>
@@ -12571,8 +12631,8 @@
       <c r="N286" s="10"/>
     </row>
     <row r="287" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A287" s="65"/>
-      <c r="B287" s="63"/>
+      <c r="A287" s="45"/>
+      <c r="B287" s="43"/>
       <c r="C287" s="9"/>
       <c r="D287" s="9"/>
       <c r="E287" s="9"/>
@@ -12587,8 +12647,8 @@
       <c r="N287" s="10"/>
     </row>
     <row r="288" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A288" s="65"/>
-      <c r="B288" s="63"/>
+      <c r="A288" s="45"/>
+      <c r="B288" s="43"/>
       <c r="C288" s="9"/>
       <c r="D288" s="9"/>
       <c r="E288" s="9"/>
@@ -12603,8 +12663,8 @@
       <c r="N288" s="10"/>
     </row>
     <row r="289" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A289" s="65"/>
-      <c r="B289" s="63"/>
+      <c r="A289" s="45"/>
+      <c r="B289" s="43"/>
       <c r="C289" s="9"/>
       <c r="D289" s="9"/>
       <c r="E289" s="9"/>
@@ -12619,8 +12679,8 @@
       <c r="N289" s="10"/>
     </row>
     <row r="290" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A290" s="65"/>
-      <c r="B290" s="63"/>
+      <c r="A290" s="45"/>
+      <c r="B290" s="43"/>
       <c r="C290" s="9"/>
       <c r="D290" s="9"/>
       <c r="E290" s="9"/>
@@ -12635,8 +12695,8 @@
       <c r="N290" s="10"/>
     </row>
     <row r="291" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A291" s="65"/>
-      <c r="B291" s="63"/>
+      <c r="A291" s="45"/>
+      <c r="B291" s="43"/>
       <c r="C291" s="9"/>
       <c r="D291" s="9"/>
       <c r="E291" s="9"/>
@@ -12651,8 +12711,8 @@
       <c r="N291" s="10"/>
     </row>
     <row r="292" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A292" s="65"/>
-      <c r="B292" s="63"/>
+      <c r="A292" s="45"/>
+      <c r="B292" s="43"/>
       <c r="C292" s="9"/>
       <c r="D292" s="9"/>
       <c r="E292" s="9"/>
@@ -12667,8 +12727,8 @@
       <c r="N292" s="10"/>
     </row>
     <row r="293" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A293" s="65"/>
-      <c r="B293" s="63"/>
+      <c r="A293" s="45"/>
+      <c r="B293" s="43"/>
       <c r="C293" s="9"/>
       <c r="D293" s="9"/>
       <c r="E293" s="9"/>
@@ -12683,8 +12743,8 @@
       <c r="N293" s="10"/>
     </row>
     <row r="294" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A294" s="65"/>
-      <c r="B294" s="63"/>
+      <c r="A294" s="45"/>
+      <c r="B294" s="43"/>
       <c r="C294" s="9"/>
       <c r="D294" s="9"/>
       <c r="E294" s="9"/>
@@ -12699,8 +12759,8 @@
       <c r="N294" s="10"/>
     </row>
     <row r="295" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A295" s="65"/>
-      <c r="B295" s="63"/>
+      <c r="A295" s="45"/>
+      <c r="B295" s="43"/>
       <c r="C295" s="9"/>
       <c r="D295" s="9"/>
       <c r="E295" s="9"/>
@@ -12715,8 +12775,8 @@
       <c r="N295" s="10"/>
     </row>
     <row r="296" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A296" s="65"/>
-      <c r="B296" s="63"/>
+      <c r="A296" s="45"/>
+      <c r="B296" s="43"/>
       <c r="C296" s="9"/>
       <c r="D296" s="9"/>
       <c r="E296" s="9"/>
@@ -12731,8 +12791,8 @@
       <c r="N296" s="10"/>
     </row>
     <row r="297" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A297" s="65"/>
-      <c r="B297" s="63"/>
+      <c r="A297" s="45"/>
+      <c r="B297" s="43"/>
       <c r="C297" s="9"/>
       <c r="D297" s="9"/>
       <c r="E297" s="9"/>
@@ -12747,8 +12807,8 @@
       <c r="N297" s="10"/>
     </row>
     <row r="298" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A298" s="65"/>
-      <c r="B298" s="63"/>
+      <c r="A298" s="45"/>
+      <c r="B298" s="43"/>
       <c r="C298" s="9"/>
       <c r="D298" s="9"/>
       <c r="E298" s="9"/>
@@ -12763,8 +12823,8 @@
       <c r="N298" s="10"/>
     </row>
     <row r="299" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A299" s="65"/>
-      <c r="B299" s="63"/>
+      <c r="A299" s="45"/>
+      <c r="B299" s="43"/>
       <c r="C299" s="9"/>
       <c r="D299" s="9"/>
       <c r="E299" s="9"/>
@@ -12779,8 +12839,8 @@
       <c r="N299" s="10"/>
     </row>
     <row r="300" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A300" s="65"/>
-      <c r="B300" s="63"/>
+      <c r="A300" s="45"/>
+      <c r="B300" s="43"/>
       <c r="C300" s="9"/>
       <c r="D300" s="9"/>
       <c r="E300" s="9"/>
@@ -12795,8 +12855,8 @@
       <c r="N300" s="10"/>
     </row>
     <row r="301" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A301" s="65"/>
-      <c r="B301" s="63"/>
+      <c r="A301" s="45"/>
+      <c r="B301" s="43"/>
       <c r="C301" s="9"/>
       <c r="D301" s="9"/>
       <c r="E301" s="9"/>
@@ -12811,8 +12871,8 @@
       <c r="N301" s="10"/>
     </row>
     <row r="302" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A302" s="65"/>
-      <c r="B302" s="63"/>
+      <c r="A302" s="45"/>
+      <c r="B302" s="43"/>
       <c r="C302" s="9"/>
       <c r="D302" s="9"/>
       <c r="E302" s="9"/>
@@ -12827,8 +12887,8 @@
       <c r="N302" s="10"/>
     </row>
     <row r="303" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A303" s="65"/>
-      <c r="B303" s="63"/>
+      <c r="A303" s="45"/>
+      <c r="B303" s="43"/>
       <c r="C303" s="9"/>
       <c r="D303" s="9"/>
       <c r="E303" s="9"/>
@@ -12843,8 +12903,8 @@
       <c r="N303" s="10"/>
     </row>
     <row r="304" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A304" s="65"/>
-      <c r="B304" s="63"/>
+      <c r="A304" s="45"/>
+      <c r="B304" s="43"/>
       <c r="C304" s="9"/>
       <c r="D304" s="9"/>
       <c r="E304" s="9"/>
@@ -12859,8 +12919,8 @@
       <c r="N304" s="10"/>
     </row>
     <row r="305" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A305" s="65"/>
-      <c r="B305" s="63"/>
+      <c r="A305" s="45"/>
+      <c r="B305" s="43"/>
       <c r="C305" s="9"/>
       <c r="D305" s="9"/>
       <c r="E305" s="9"/>
@@ -12875,8 +12935,8 @@
       <c r="N305" s="10"/>
     </row>
     <row r="306" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A306" s="65"/>
-      <c r="B306" s="63"/>
+      <c r="A306" s="45"/>
+      <c r="B306" s="43"/>
       <c r="C306" s="9"/>
       <c r="D306" s="9"/>
       <c r="E306" s="9"/>
@@ -12891,8 +12951,8 @@
       <c r="N306" s="10"/>
     </row>
     <row r="307" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A307" s="65"/>
-      <c r="B307" s="63"/>
+      <c r="A307" s="45"/>
+      <c r="B307" s="43"/>
       <c r="C307" s="9"/>
       <c r="D307" s="9"/>
       <c r="E307" s="9"/>
@@ -12907,8 +12967,8 @@
       <c r="N307" s="10"/>
     </row>
     <row r="308" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A308" s="65"/>
-      <c r="B308" s="63"/>
+      <c r="A308" s="45"/>
+      <c r="B308" s="43"/>
       <c r="C308" s="9"/>
       <c r="D308" s="9"/>
       <c r="E308" s="9"/>
@@ -12923,8 +12983,8 @@
       <c r="N308" s="10"/>
     </row>
     <row r="309" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A309" s="65"/>
-      <c r="B309" s="63"/>
+      <c r="A309" s="45"/>
+      <c r="B309" s="43"/>
       <c r="C309" s="9"/>
       <c r="D309" s="9"/>
       <c r="E309" s="9"/>
@@ -12939,8 +12999,8 @@
       <c r="N309" s="10"/>
     </row>
     <row r="310" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A310" s="65"/>
-      <c r="B310" s="63"/>
+      <c r="A310" s="45"/>
+      <c r="B310" s="43"/>
       <c r="C310" s="9"/>
       <c r="D310" s="9"/>
       <c r="E310" s="9"/>
@@ -12955,8 +13015,8 @@
       <c r="N310" s="10"/>
     </row>
     <row r="311" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A311" s="65"/>
-      <c r="B311" s="63"/>
+      <c r="A311" s="45"/>
+      <c r="B311" s="43"/>
       <c r="C311" s="9"/>
       <c r="D311" s="9"/>
       <c r="E311" s="9"/>
@@ -12971,8 +13031,8 @@
       <c r="N311" s="10"/>
     </row>
     <row r="312" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A312" s="65"/>
-      <c r="B312" s="63"/>
+      <c r="A312" s="45"/>
+      <c r="B312" s="43"/>
       <c r="C312" s="9"/>
       <c r="D312" s="9"/>
       <c r="E312" s="9"/>
@@ -12987,8 +13047,8 @@
       <c r="N312" s="10"/>
     </row>
     <row r="313" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A313" s="65"/>
-      <c r="B313" s="63"/>
+      <c r="A313" s="45"/>
+      <c r="B313" s="43"/>
       <c r="C313" s="9"/>
       <c r="D313" s="9"/>
       <c r="E313" s="9"/>
@@ -13003,8 +13063,8 @@
       <c r="N313" s="10"/>
     </row>
     <row r="314" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A314" s="65"/>
-      <c r="B314" s="63"/>
+      <c r="A314" s="45"/>
+      <c r="B314" s="43"/>
       <c r="C314" s="9"/>
       <c r="D314" s="9"/>
       <c r="E314" s="9"/>
@@ -13019,8 +13079,8 @@
       <c r="N314" s="10"/>
     </row>
     <row r="315" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A315" s="65"/>
-      <c r="B315" s="63"/>
+      <c r="A315" s="45"/>
+      <c r="B315" s="43"/>
       <c r="C315" s="9"/>
       <c r="D315" s="9"/>
       <c r="E315" s="9"/>
@@ -13035,8 +13095,8 @@
       <c r="N315" s="10"/>
     </row>
     <row r="316" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A316" s="65"/>
-      <c r="B316" s="63"/>
+      <c r="A316" s="45"/>
+      <c r="B316" s="43"/>
       <c r="C316" s="9"/>
       <c r="D316" s="9"/>
       <c r="E316" s="9"/>
@@ -13051,8 +13111,8 @@
       <c r="N316" s="10"/>
     </row>
     <row r="317" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A317" s="65"/>
-      <c r="B317" s="63"/>
+      <c r="A317" s="45"/>
+      <c r="B317" s="43"/>
       <c r="C317" s="9"/>
       <c r="D317" s="9"/>
       <c r="E317" s="9"/>
@@ -13067,8 +13127,8 @@
       <c r="N317" s="10"/>
     </row>
     <row r="318" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A318" s="65"/>
-      <c r="B318" s="63"/>
+      <c r="A318" s="45"/>
+      <c r="B318" s="43"/>
       <c r="C318" s="9"/>
       <c r="D318" s="9"/>
       <c r="E318" s="9"/>
@@ -13083,8 +13143,8 @@
       <c r="N318" s="10"/>
     </row>
     <row r="319" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A319" s="65"/>
-      <c r="B319" s="63"/>
+      <c r="A319" s="45"/>
+      <c r="B319" s="43"/>
       <c r="C319" s="9"/>
       <c r="D319" s="9"/>
       <c r="E319" s="9"/>
@@ -13099,8 +13159,8 @@
       <c r="N319" s="10"/>
     </row>
     <row r="320" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A320" s="65"/>
-      <c r="B320" s="63"/>
+      <c r="A320" s="45"/>
+      <c r="B320" s="43"/>
       <c r="C320" s="9"/>
       <c r="D320" s="9"/>
       <c r="E320" s="9"/>
@@ -13115,8 +13175,8 @@
       <c r="N320" s="10"/>
     </row>
     <row r="321" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A321" s="65"/>
-      <c r="B321" s="63"/>
+      <c r="A321" s="45"/>
+      <c r="B321" s="43"/>
       <c r="C321" s="9"/>
       <c r="D321" s="9"/>
       <c r="E321" s="9"/>
@@ -13131,8 +13191,8 @@
       <c r="N321" s="10"/>
     </row>
     <row r="322" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A322" s="65"/>
-      <c r="B322" s="63"/>
+      <c r="A322" s="45"/>
+      <c r="B322" s="43"/>
       <c r="C322" s="9"/>
       <c r="D322" s="9"/>
       <c r="E322" s="9"/>
@@ -13147,8 +13207,8 @@
       <c r="N322" s="10"/>
     </row>
     <row r="323" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A323" s="65"/>
-      <c r="B323" s="63"/>
+      <c r="A323" s="45"/>
+      <c r="B323" s="43"/>
       <c r="C323" s="9"/>
       <c r="D323" s="9"/>
       <c r="E323" s="9"/>
@@ -13163,8 +13223,8 @@
       <c r="N323" s="10"/>
     </row>
     <row r="324" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A324" s="65"/>
-      <c r="B324" s="63"/>
+      <c r="A324" s="45"/>
+      <c r="B324" s="43"/>
       <c r="C324" s="9"/>
       <c r="D324" s="9"/>
       <c r="E324" s="9"/>
@@ -13179,8 +13239,8 @@
       <c r="N324" s="10"/>
     </row>
     <row r="325" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A325" s="65"/>
-      <c r="B325" s="63"/>
+      <c r="A325" s="45"/>
+      <c r="B325" s="43"/>
       <c r="C325" s="9"/>
       <c r="D325" s="9"/>
       <c r="E325" s="9"/>
@@ -13195,8 +13255,8 @@
       <c r="N325" s="10"/>
     </row>
     <row r="326" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A326" s="65"/>
-      <c r="B326" s="63"/>
+      <c r="A326" s="45"/>
+      <c r="B326" s="43"/>
       <c r="C326" s="9"/>
       <c r="D326" s="9"/>
       <c r="E326" s="9"/>
@@ -13211,8 +13271,8 @@
       <c r="N326" s="10"/>
     </row>
     <row r="327" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A327" s="65"/>
-      <c r="B327" s="63"/>
+      <c r="A327" s="45"/>
+      <c r="B327" s="43"/>
       <c r="C327" s="9"/>
       <c r="D327" s="9"/>
       <c r="E327" s="9"/>
@@ -13227,8 +13287,8 @@
       <c r="N327" s="10"/>
     </row>
     <row r="328" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A328" s="65"/>
-      <c r="B328" s="63"/>
+      <c r="A328" s="45"/>
+      <c r="B328" s="43"/>
       <c r="C328" s="9"/>
       <c r="D328" s="9"/>
       <c r="E328" s="9"/>
@@ -13243,8 +13303,8 @@
       <c r="N328" s="10"/>
     </row>
     <row r="329" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A329" s="65"/>
-      <c r="B329" s="63"/>
+      <c r="A329" s="45"/>
+      <c r="B329" s="43"/>
       <c r="C329" s="9"/>
       <c r="D329" s="9"/>
       <c r="E329" s="9"/>
@@ -13259,8 +13319,8 @@
       <c r="N329" s="10"/>
     </row>
     <row r="330" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A330" s="65"/>
-      <c r="B330" s="63"/>
+      <c r="A330" s="45"/>
+      <c r="B330" s="43"/>
       <c r="C330" s="9"/>
       <c r="D330" s="9"/>
       <c r="E330" s="9"/>
@@ -13275,8 +13335,8 @@
       <c r="N330" s="10"/>
     </row>
     <row r="331" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A331" s="65"/>
-      <c r="B331" s="63"/>
+      <c r="A331" s="45"/>
+      <c r="B331" s="43"/>
       <c r="C331" s="9"/>
       <c r="D331" s="9"/>
       <c r="E331" s="9"/>
@@ -13291,8 +13351,8 @@
       <c r="N331" s="10"/>
     </row>
     <row r="332" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A332" s="65"/>
-      <c r="B332" s="63"/>
+      <c r="A332" s="45"/>
+      <c r="B332" s="43"/>
       <c r="C332" s="9"/>
       <c r="D332" s="9"/>
       <c r="E332" s="9"/>
@@ -13307,8 +13367,8 @@
       <c r="N332" s="10"/>
     </row>
     <row r="333" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A333" s="65"/>
-      <c r="B333" s="63"/>
+      <c r="A333" s="45"/>
+      <c r="B333" s="43"/>
       <c r="C333" s="9"/>
       <c r="D333" s="9"/>
       <c r="E333" s="9"/>
@@ -13323,8 +13383,8 @@
       <c r="N333" s="10"/>
     </row>
     <row r="334" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A334" s="65"/>
-      <c r="B334" s="63"/>
+      <c r="A334" s="45"/>
+      <c r="B334" s="43"/>
       <c r="C334" s="9"/>
       <c r="D334" s="9"/>
       <c r="E334" s="9"/>
@@ -13339,8 +13399,8 @@
       <c r="N334" s="10"/>
     </row>
     <row r="335" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A335" s="65"/>
-      <c r="B335" s="63"/>
+      <c r="A335" s="45"/>
+      <c r="B335" s="43"/>
       <c r="C335" s="9"/>
       <c r="D335" s="9"/>
       <c r="E335" s="9"/>
@@ -13355,8 +13415,8 @@
       <c r="N335" s="10"/>
     </row>
     <row r="336" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A336" s="65"/>
-      <c r="B336" s="63"/>
+      <c r="A336" s="45"/>
+      <c r="B336" s="43"/>
       <c r="C336" s="9"/>
       <c r="D336" s="9"/>
       <c r="E336" s="9"/>
@@ -13371,8 +13431,8 @@
       <c r="N336" s="10"/>
     </row>
     <row r="337" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A337" s="65"/>
-      <c r="B337" s="63"/>
+      <c r="A337" s="45"/>
+      <c r="B337" s="43"/>
       <c r="C337" s="9"/>
       <c r="D337" s="9"/>
       <c r="E337" s="9"/>
@@ -13387,8 +13447,8 @@
       <c r="N337" s="10"/>
     </row>
     <row r="338" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A338" s="65"/>
-      <c r="B338" s="63"/>
+      <c r="A338" s="45"/>
+      <c r="B338" s="43"/>
       <c r="C338" s="9"/>
       <c r="D338" s="9"/>
       <c r="E338" s="9"/>
@@ -13403,8 +13463,8 @@
       <c r="N338" s="10"/>
     </row>
     <row r="339" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A339" s="65"/>
-      <c r="B339" s="63"/>
+      <c r="A339" s="45"/>
+      <c r="B339" s="43"/>
       <c r="C339" s="9"/>
       <c r="D339" s="9"/>
       <c r="E339" s="9"/>
@@ -13419,8 +13479,8 @@
       <c r="N339" s="10"/>
     </row>
     <row r="340" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A340" s="65"/>
-      <c r="B340" s="63"/>
+      <c r="A340" s="45"/>
+      <c r="B340" s="43"/>
       <c r="C340" s="9"/>
       <c r="D340" s="9"/>
       <c r="E340" s="9"/>
@@ -13435,8 +13495,8 @@
       <c r="N340" s="10"/>
     </row>
     <row r="341" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A341" s="65"/>
-      <c r="B341" s="63"/>
+      <c r="A341" s="45"/>
+      <c r="B341" s="43"/>
       <c r="C341" s="9"/>
       <c r="D341" s="9"/>
       <c r="E341" s="9"/>
@@ -13451,8 +13511,8 @@
       <c r="N341" s="10"/>
     </row>
     <row r="342" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A342" s="65"/>
-      <c r="B342" s="63"/>
+      <c r="A342" s="45"/>
+      <c r="B342" s="43"/>
       <c r="C342" s="9"/>
       <c r="D342" s="9"/>
       <c r="E342" s="9"/>
@@ -13467,8 +13527,8 @@
       <c r="N342" s="10"/>
     </row>
     <row r="343" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A343" s="65"/>
-      <c r="B343" s="63"/>
+      <c r="A343" s="45"/>
+      <c r="B343" s="43"/>
       <c r="C343" s="9"/>
       <c r="D343" s="9"/>
       <c r="E343" s="9"/>
@@ -13483,8 +13543,8 @@
       <c r="N343" s="10"/>
     </row>
     <row r="344" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A344" s="65"/>
-      <c r="B344" s="63"/>
+      <c r="A344" s="45"/>
+      <c r="B344" s="43"/>
       <c r="C344" s="9"/>
       <c r="D344" s="9"/>
       <c r="E344" s="9"/>
@@ -13499,8 +13559,8 @@
       <c r="N344" s="10"/>
     </row>
     <row r="345" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A345" s="65"/>
-      <c r="B345" s="63"/>
+      <c r="A345" s="45"/>
+      <c r="B345" s="43"/>
       <c r="C345" s="9"/>
       <c r="D345" s="9"/>
       <c r="E345" s="9"/>
@@ -13515,8 +13575,8 @@
       <c r="N345" s="10"/>
     </row>
     <row r="346" spans="1:14" s="8" customFormat="1" ht="19">
-      <c r="A346" s="65"/>
-      <c r="B346" s="63"/>
+      <c r="A346" s="45"/>
+      <c r="B346" s="43"/>
       <c r="C346" s="9"/>
       <c r="D346" s="9"/>
       <c r="E346" s="9"/>
@@ -13531,1687 +13591,1687 @@
       <c r="N346" s="10"/>
     </row>
     <row r="347" spans="1:14" ht="19">
-      <c r="A347" s="65"/>
+      <c r="A347" s="45"/>
     </row>
     <row r="348" spans="1:14" ht="19">
-      <c r="A348" s="65"/>
+      <c r="A348" s="45"/>
     </row>
     <row r="349" spans="1:14" ht="19">
-      <c r="A349" s="65"/>
+      <c r="A349" s="45"/>
     </row>
     <row r="350" spans="1:14" ht="19">
-      <c r="A350" s="65"/>
+      <c r="A350" s="45"/>
     </row>
     <row r="351" spans="1:14" ht="19">
-      <c r="A351" s="65"/>
+      <c r="A351" s="45"/>
     </row>
     <row r="352" spans="1:14" ht="19">
-      <c r="A352" s="65"/>
+      <c r="A352" s="45"/>
     </row>
     <row r="353" spans="1:1" ht="19">
-      <c r="A353" s="65"/>
+      <c r="A353" s="45"/>
     </row>
     <row r="354" spans="1:1" ht="19">
-      <c r="A354" s="65"/>
+      <c r="A354" s="45"/>
     </row>
     <row r="355" spans="1:1" ht="19">
-      <c r="A355" s="65"/>
+      <c r="A355" s="45"/>
     </row>
     <row r="356" spans="1:1" ht="19">
-      <c r="A356" s="65"/>
+      <c r="A356" s="45"/>
     </row>
     <row r="357" spans="1:1" ht="19">
-      <c r="A357" s="65"/>
+      <c r="A357" s="45"/>
     </row>
     <row r="358" spans="1:1" ht="19">
-      <c r="A358" s="65"/>
+      <c r="A358" s="45"/>
     </row>
     <row r="359" spans="1:1" ht="19">
-      <c r="A359" s="65"/>
+      <c r="A359" s="45"/>
     </row>
     <row r="360" spans="1:1" ht="19">
-      <c r="A360" s="65"/>
+      <c r="A360" s="45"/>
     </row>
     <row r="361" spans="1:1" ht="19">
-      <c r="A361" s="65"/>
+      <c r="A361" s="45"/>
     </row>
     <row r="362" spans="1:1" ht="19">
-      <c r="A362" s="65"/>
+      <c r="A362" s="45"/>
     </row>
     <row r="363" spans="1:1" ht="19">
-      <c r="A363" s="65"/>
+      <c r="A363" s="45"/>
     </row>
     <row r="364" spans="1:1" ht="19">
-      <c r="A364" s="65"/>
+      <c r="A364" s="45"/>
     </row>
     <row r="365" spans="1:1" ht="19">
-      <c r="A365" s="65"/>
+      <c r="A365" s="45"/>
     </row>
     <row r="366" spans="1:1" ht="19">
-      <c r="A366" s="65"/>
+      <c r="A366" s="45"/>
     </row>
     <row r="367" spans="1:1" ht="19">
-      <c r="A367" s="65"/>
+      <c r="A367" s="45"/>
     </row>
     <row r="368" spans="1:1" ht="19">
-      <c r="A368" s="65"/>
+      <c r="A368" s="45"/>
     </row>
     <row r="369" spans="1:1" ht="19">
-      <c r="A369" s="65"/>
+      <c r="A369" s="45"/>
     </row>
     <row r="370" spans="1:1" ht="19">
-      <c r="A370" s="65"/>
+      <c r="A370" s="45"/>
     </row>
     <row r="371" spans="1:1" ht="19">
-      <c r="A371" s="65"/>
+      <c r="A371" s="45"/>
     </row>
     <row r="372" spans="1:1" ht="19">
-      <c r="A372" s="65"/>
+      <c r="A372" s="45"/>
     </row>
     <row r="373" spans="1:1" ht="19">
-      <c r="A373" s="65"/>
+      <c r="A373" s="45"/>
     </row>
     <row r="374" spans="1:1" ht="19">
-      <c r="A374" s="65"/>
+      <c r="A374" s="45"/>
     </row>
     <row r="375" spans="1:1" ht="19">
-      <c r="A375" s="65"/>
+      <c r="A375" s="45"/>
     </row>
     <row r="376" spans="1:1" ht="19">
-      <c r="A376" s="65"/>
+      <c r="A376" s="45"/>
     </row>
     <row r="377" spans="1:1" ht="19">
-      <c r="A377" s="65"/>
+      <c r="A377" s="45"/>
     </row>
     <row r="378" spans="1:1" ht="19">
-      <c r="A378" s="65"/>
+      <c r="A378" s="45"/>
     </row>
     <row r="379" spans="1:1" ht="19">
-      <c r="A379" s="65"/>
+      <c r="A379" s="45"/>
     </row>
     <row r="380" spans="1:1" ht="19">
-      <c r="A380" s="65"/>
+      <c r="A380" s="45"/>
     </row>
     <row r="381" spans="1:1" ht="19">
-      <c r="A381" s="65"/>
+      <c r="A381" s="45"/>
     </row>
     <row r="382" spans="1:1" ht="19">
-      <c r="A382" s="65"/>
+      <c r="A382" s="45"/>
     </row>
     <row r="383" spans="1:1" ht="19">
-      <c r="A383" s="65"/>
+      <c r="A383" s="45"/>
     </row>
     <row r="384" spans="1:1" ht="19">
-      <c r="A384" s="65"/>
+      <c r="A384" s="45"/>
     </row>
     <row r="385" spans="1:1" ht="19">
-      <c r="A385" s="65"/>
+      <c r="A385" s="45"/>
     </row>
     <row r="386" spans="1:1" ht="19">
-      <c r="A386" s="65"/>
+      <c r="A386" s="45"/>
     </row>
     <row r="387" spans="1:1" ht="19">
-      <c r="A387" s="65"/>
+      <c r="A387" s="45"/>
     </row>
     <row r="388" spans="1:1" ht="19">
-      <c r="A388" s="65"/>
+      <c r="A388" s="45"/>
     </row>
     <row r="389" spans="1:1" ht="19">
-      <c r="A389" s="65"/>
+      <c r="A389" s="45"/>
     </row>
     <row r="390" spans="1:1" ht="19">
-      <c r="A390" s="65"/>
+      <c r="A390" s="45"/>
     </row>
     <row r="391" spans="1:1" ht="19">
-      <c r="A391" s="65"/>
+      <c r="A391" s="45"/>
     </row>
     <row r="392" spans="1:1" ht="19">
-      <c r="A392" s="65"/>
+      <c r="A392" s="45"/>
     </row>
     <row r="393" spans="1:1" ht="19">
-      <c r="A393" s="65"/>
+      <c r="A393" s="45"/>
     </row>
     <row r="394" spans="1:1" ht="19">
-      <c r="A394" s="65"/>
+      <c r="A394" s="45"/>
     </row>
     <row r="395" spans="1:1" ht="19">
-      <c r="A395" s="65"/>
+      <c r="A395" s="45"/>
     </row>
     <row r="396" spans="1:1" ht="19">
-      <c r="A396" s="65"/>
+      <c r="A396" s="45"/>
     </row>
     <row r="397" spans="1:1" ht="19">
-      <c r="A397" s="65"/>
+      <c r="A397" s="45"/>
     </row>
     <row r="398" spans="1:1" ht="19">
-      <c r="A398" s="65"/>
+      <c r="A398" s="45"/>
     </row>
     <row r="399" spans="1:1" ht="19">
-      <c r="A399" s="65"/>
+      <c r="A399" s="45"/>
     </row>
     <row r="400" spans="1:1" ht="19">
-      <c r="A400" s="65"/>
+      <c r="A400" s="45"/>
     </row>
     <row r="401" spans="1:1" ht="19">
-      <c r="A401" s="65"/>
+      <c r="A401" s="45"/>
     </row>
     <row r="402" spans="1:1" ht="19">
-      <c r="A402" s="65"/>
+      <c r="A402" s="45"/>
     </row>
     <row r="403" spans="1:1" ht="19">
-      <c r="A403" s="65"/>
+      <c r="A403" s="45"/>
     </row>
     <row r="404" spans="1:1" ht="19">
-      <c r="A404" s="65"/>
+      <c r="A404" s="45"/>
     </row>
     <row r="405" spans="1:1" ht="19">
-      <c r="A405" s="65"/>
+      <c r="A405" s="45"/>
     </row>
     <row r="406" spans="1:1" ht="19">
-      <c r="A406" s="65"/>
+      <c r="A406" s="45"/>
     </row>
     <row r="407" spans="1:1" ht="19">
-      <c r="A407" s="65"/>
+      <c r="A407" s="45"/>
     </row>
     <row r="408" spans="1:1" ht="19">
-      <c r="A408" s="65"/>
+      <c r="A408" s="45"/>
     </row>
     <row r="409" spans="1:1" ht="19">
-      <c r="A409" s="65"/>
+      <c r="A409" s="45"/>
     </row>
     <row r="410" spans="1:1" ht="19">
-      <c r="A410" s="65"/>
+      <c r="A410" s="45"/>
     </row>
     <row r="411" spans="1:1" ht="19">
-      <c r="A411" s="65"/>
+      <c r="A411" s="45"/>
     </row>
     <row r="412" spans="1:1" ht="19">
-      <c r="A412" s="65"/>
+      <c r="A412" s="45"/>
     </row>
     <row r="413" spans="1:1" ht="19">
-      <c r="A413" s="65"/>
+      <c r="A413" s="45"/>
     </row>
     <row r="414" spans="1:1" ht="19">
-      <c r="A414" s="65"/>
+      <c r="A414" s="45"/>
     </row>
     <row r="415" spans="1:1" ht="19">
-      <c r="A415" s="65"/>
+      <c r="A415" s="45"/>
     </row>
     <row r="416" spans="1:1" ht="19">
-      <c r="A416" s="65"/>
+      <c r="A416" s="45"/>
     </row>
     <row r="417" spans="1:1" ht="19">
-      <c r="A417" s="65"/>
+      <c r="A417" s="45"/>
     </row>
     <row r="418" spans="1:1" ht="19">
-      <c r="A418" s="65"/>
+      <c r="A418" s="45"/>
     </row>
     <row r="419" spans="1:1" ht="19">
-      <c r="A419" s="65"/>
+      <c r="A419" s="45"/>
     </row>
     <row r="420" spans="1:1" ht="19">
-      <c r="A420" s="65"/>
+      <c r="A420" s="45"/>
     </row>
     <row r="421" spans="1:1" ht="19">
-      <c r="A421" s="65"/>
+      <c r="A421" s="45"/>
     </row>
     <row r="422" spans="1:1" ht="19">
-      <c r="A422" s="65"/>
+      <c r="A422" s="45"/>
     </row>
     <row r="423" spans="1:1" ht="19">
-      <c r="A423" s="65"/>
+      <c r="A423" s="45"/>
     </row>
     <row r="424" spans="1:1" ht="19">
-      <c r="A424" s="65"/>
+      <c r="A424" s="45"/>
     </row>
     <row r="425" spans="1:1" ht="19">
-      <c r="A425" s="65"/>
+      <c r="A425" s="45"/>
     </row>
     <row r="426" spans="1:1" ht="19">
-      <c r="A426" s="65"/>
+      <c r="A426" s="45"/>
     </row>
     <row r="427" spans="1:1" ht="19">
-      <c r="A427" s="65"/>
+      <c r="A427" s="45"/>
     </row>
     <row r="428" spans="1:1" ht="19">
-      <c r="A428" s="65"/>
+      <c r="A428" s="45"/>
     </row>
     <row r="429" spans="1:1" ht="19">
-      <c r="A429" s="65"/>
+      <c r="A429" s="45"/>
     </row>
     <row r="430" spans="1:1" ht="19">
-      <c r="A430" s="65"/>
+      <c r="A430" s="45"/>
     </row>
     <row r="431" spans="1:1" ht="19">
-      <c r="A431" s="65"/>
+      <c r="A431" s="45"/>
     </row>
     <row r="432" spans="1:1" ht="19">
-      <c r="A432" s="65"/>
+      <c r="A432" s="45"/>
     </row>
     <row r="433" spans="1:1" ht="19">
-      <c r="A433" s="65"/>
+      <c r="A433" s="45"/>
     </row>
     <row r="434" spans="1:1" ht="19">
-      <c r="A434" s="65"/>
+      <c r="A434" s="45"/>
     </row>
     <row r="435" spans="1:1" ht="19">
-      <c r="A435" s="65"/>
+      <c r="A435" s="45"/>
     </row>
     <row r="436" spans="1:1" ht="19">
-      <c r="A436" s="65"/>
+      <c r="A436" s="45"/>
     </row>
     <row r="437" spans="1:1" ht="19">
-      <c r="A437" s="65"/>
+      <c r="A437" s="45"/>
     </row>
     <row r="438" spans="1:1" ht="19">
-      <c r="A438" s="65"/>
+      <c r="A438" s="45"/>
     </row>
     <row r="439" spans="1:1" ht="19">
-      <c r="A439" s="65"/>
+      <c r="A439" s="45"/>
     </row>
     <row r="440" spans="1:1" ht="19">
-      <c r="A440" s="65"/>
+      <c r="A440" s="45"/>
     </row>
     <row r="441" spans="1:1" ht="19">
-      <c r="A441" s="65"/>
+      <c r="A441" s="45"/>
     </row>
     <row r="442" spans="1:1" ht="19">
-      <c r="A442" s="65"/>
+      <c r="A442" s="45"/>
     </row>
     <row r="443" spans="1:1" ht="19">
-      <c r="A443" s="65"/>
+      <c r="A443" s="45"/>
     </row>
     <row r="444" spans="1:1" ht="19">
-      <c r="A444" s="65"/>
+      <c r="A444" s="45"/>
     </row>
     <row r="445" spans="1:1" ht="19">
-      <c r="A445" s="65"/>
+      <c r="A445" s="45"/>
     </row>
     <row r="446" spans="1:1" ht="19">
-      <c r="A446" s="65"/>
+      <c r="A446" s="45"/>
     </row>
     <row r="447" spans="1:1" ht="19">
-      <c r="A447" s="65"/>
+      <c r="A447" s="45"/>
     </row>
     <row r="448" spans="1:1" ht="19">
-      <c r="A448" s="65"/>
+      <c r="A448" s="45"/>
     </row>
     <row r="449" spans="1:1" ht="19">
-      <c r="A449" s="65"/>
+      <c r="A449" s="45"/>
     </row>
     <row r="450" spans="1:1" ht="19">
-      <c r="A450" s="65"/>
+      <c r="A450" s="45"/>
     </row>
     <row r="451" spans="1:1" ht="19">
-      <c r="A451" s="65"/>
+      <c r="A451" s="45"/>
     </row>
     <row r="452" spans="1:1" ht="19">
-      <c r="A452" s="65"/>
+      <c r="A452" s="45"/>
     </row>
     <row r="453" spans="1:1" ht="19">
-      <c r="A453" s="65"/>
+      <c r="A453" s="45"/>
     </row>
     <row r="454" spans="1:1" ht="19">
-      <c r="A454" s="65"/>
+      <c r="A454" s="45"/>
     </row>
     <row r="455" spans="1:1" ht="19">
-      <c r="A455" s="65"/>
+      <c r="A455" s="45"/>
     </row>
     <row r="456" spans="1:1" ht="19">
-      <c r="A456" s="65"/>
+      <c r="A456" s="45"/>
     </row>
     <row r="457" spans="1:1" ht="19">
-      <c r="A457" s="65"/>
+      <c r="A457" s="45"/>
     </row>
     <row r="458" spans="1:1" ht="19">
-      <c r="A458" s="65"/>
+      <c r="A458" s="45"/>
     </row>
     <row r="459" spans="1:1" ht="19">
-      <c r="A459" s="65"/>
+      <c r="A459" s="45"/>
     </row>
     <row r="460" spans="1:1" ht="19">
-      <c r="A460" s="65"/>
+      <c r="A460" s="45"/>
     </row>
     <row r="461" spans="1:1" ht="19">
-      <c r="A461" s="65"/>
+      <c r="A461" s="45"/>
     </row>
     <row r="462" spans="1:1" ht="19">
-      <c r="A462" s="65"/>
+      <c r="A462" s="45"/>
     </row>
     <row r="463" spans="1:1" ht="19">
-      <c r="A463" s="65"/>
+      <c r="A463" s="45"/>
     </row>
     <row r="464" spans="1:1" ht="19">
-      <c r="A464" s="65"/>
+      <c r="A464" s="45"/>
     </row>
     <row r="465" spans="1:1" ht="19">
-      <c r="A465" s="65"/>
+      <c r="A465" s="45"/>
     </row>
     <row r="466" spans="1:1" ht="19">
-      <c r="A466" s="65"/>
+      <c r="A466" s="45"/>
     </row>
     <row r="467" spans="1:1" ht="19">
-      <c r="A467" s="65"/>
+      <c r="A467" s="45"/>
     </row>
     <row r="468" spans="1:1" ht="19">
-      <c r="A468" s="65"/>
+      <c r="A468" s="45"/>
     </row>
     <row r="469" spans="1:1" ht="19">
-      <c r="A469" s="65"/>
+      <c r="A469" s="45"/>
     </row>
     <row r="470" spans="1:1" ht="19">
-      <c r="A470" s="65"/>
+      <c r="A470" s="45"/>
     </row>
     <row r="471" spans="1:1" ht="19">
-      <c r="A471" s="65"/>
+      <c r="A471" s="45"/>
     </row>
     <row r="472" spans="1:1" ht="19">
-      <c r="A472" s="65"/>
+      <c r="A472" s="45"/>
     </row>
     <row r="473" spans="1:1" ht="19">
-      <c r="A473" s="65"/>
+      <c r="A473" s="45"/>
     </row>
     <row r="474" spans="1:1" ht="19">
-      <c r="A474" s="65"/>
+      <c r="A474" s="45"/>
     </row>
     <row r="475" spans="1:1" ht="19">
-      <c r="A475" s="65"/>
+      <c r="A475" s="45"/>
     </row>
     <row r="476" spans="1:1" ht="19">
-      <c r="A476" s="65"/>
+      <c r="A476" s="45"/>
     </row>
     <row r="477" spans="1:1" ht="19">
-      <c r="A477" s="65"/>
+      <c r="A477" s="45"/>
     </row>
     <row r="478" spans="1:1" ht="19">
-      <c r="A478" s="65"/>
+      <c r="A478" s="45"/>
     </row>
     <row r="479" spans="1:1" ht="19">
-      <c r="A479" s="65"/>
+      <c r="A479" s="45"/>
     </row>
     <row r="480" spans="1:1" ht="19">
-      <c r="A480" s="65"/>
+      <c r="A480" s="45"/>
     </row>
     <row r="481" spans="1:1" ht="19">
-      <c r="A481" s="65"/>
+      <c r="A481" s="45"/>
     </row>
     <row r="482" spans="1:1" ht="19">
-      <c r="A482" s="65"/>
+      <c r="A482" s="45"/>
     </row>
     <row r="483" spans="1:1" ht="19">
-      <c r="A483" s="65"/>
+      <c r="A483" s="45"/>
     </row>
     <row r="484" spans="1:1" ht="19">
-      <c r="A484" s="65"/>
+      <c r="A484" s="45"/>
     </row>
     <row r="485" spans="1:1" ht="19">
-      <c r="A485" s="65"/>
+      <c r="A485" s="45"/>
     </row>
     <row r="486" spans="1:1" ht="19">
-      <c r="A486" s="65"/>
+      <c r="A486" s="45"/>
     </row>
     <row r="487" spans="1:1" ht="19">
-      <c r="A487" s="65"/>
+      <c r="A487" s="45"/>
     </row>
     <row r="488" spans="1:1" ht="19">
-      <c r="A488" s="65"/>
+      <c r="A488" s="45"/>
     </row>
     <row r="489" spans="1:1" ht="19">
-      <c r="A489" s="65"/>
+      <c r="A489" s="45"/>
     </row>
     <row r="490" spans="1:1" ht="19">
-      <c r="A490" s="65"/>
+      <c r="A490" s="45"/>
     </row>
     <row r="491" spans="1:1" ht="19">
-      <c r="A491" s="65"/>
+      <c r="A491" s="45"/>
     </row>
     <row r="492" spans="1:1" ht="19">
-      <c r="A492" s="65"/>
+      <c r="A492" s="45"/>
     </row>
     <row r="493" spans="1:1" ht="19">
-      <c r="A493" s="65"/>
+      <c r="A493" s="45"/>
     </row>
     <row r="494" spans="1:1" ht="19">
-      <c r="A494" s="65"/>
+      <c r="A494" s="45"/>
     </row>
     <row r="495" spans="1:1" ht="19">
-      <c r="A495" s="65"/>
+      <c r="A495" s="45"/>
     </row>
     <row r="496" spans="1:1" ht="19">
-      <c r="A496" s="65"/>
+      <c r="A496" s="45"/>
     </row>
     <row r="497" spans="1:1" ht="19">
-      <c r="A497" s="65"/>
+      <c r="A497" s="45"/>
     </row>
     <row r="498" spans="1:1" ht="19">
-      <c r="A498" s="65"/>
+      <c r="A498" s="45"/>
     </row>
     <row r="499" spans="1:1" ht="19">
-      <c r="A499" s="65"/>
+      <c r="A499" s="45"/>
     </row>
     <row r="500" spans="1:1" ht="19">
-      <c r="A500" s="65"/>
+      <c r="A500" s="45"/>
     </row>
     <row r="501" spans="1:1" ht="19">
-      <c r="A501" s="65"/>
+      <c r="A501" s="45"/>
     </row>
     <row r="502" spans="1:1" ht="19">
-      <c r="A502" s="65"/>
+      <c r="A502" s="45"/>
     </row>
     <row r="503" spans="1:1" ht="19">
-      <c r="A503" s="65"/>
+      <c r="A503" s="45"/>
     </row>
     <row r="504" spans="1:1" ht="19">
-      <c r="A504" s="65"/>
+      <c r="A504" s="45"/>
     </row>
     <row r="505" spans="1:1" ht="19">
-      <c r="A505" s="65"/>
+      <c r="A505" s="45"/>
     </row>
     <row r="506" spans="1:1" ht="19">
-      <c r="A506" s="65"/>
+      <c r="A506" s="45"/>
     </row>
     <row r="507" spans="1:1" ht="19">
-      <c r="A507" s="65"/>
+      <c r="A507" s="45"/>
     </row>
     <row r="508" spans="1:1" ht="19">
-      <c r="A508" s="65"/>
+      <c r="A508" s="45"/>
     </row>
     <row r="509" spans="1:1" ht="19">
-      <c r="A509" s="65"/>
+      <c r="A509" s="45"/>
     </row>
     <row r="510" spans="1:1" ht="19">
-      <c r="A510" s="65"/>
+      <c r="A510" s="45"/>
     </row>
     <row r="511" spans="1:1" ht="19">
-      <c r="A511" s="65"/>
+      <c r="A511" s="45"/>
     </row>
     <row r="512" spans="1:1" ht="19">
-      <c r="A512" s="65"/>
+      <c r="A512" s="45"/>
     </row>
     <row r="513" spans="1:1" ht="19">
-      <c r="A513" s="65"/>
+      <c r="A513" s="45"/>
     </row>
     <row r="514" spans="1:1" ht="19">
-      <c r="A514" s="65"/>
+      <c r="A514" s="45"/>
     </row>
     <row r="515" spans="1:1" ht="19">
-      <c r="A515" s="65"/>
+      <c r="A515" s="45"/>
     </row>
     <row r="516" spans="1:1" ht="19">
-      <c r="A516" s="65"/>
+      <c r="A516" s="45"/>
     </row>
     <row r="517" spans="1:1" ht="19">
-      <c r="A517" s="65"/>
+      <c r="A517" s="45"/>
     </row>
     <row r="518" spans="1:1" ht="19">
-      <c r="A518" s="65"/>
+      <c r="A518" s="45"/>
     </row>
     <row r="519" spans="1:1" ht="19">
-      <c r="A519" s="65"/>
+      <c r="A519" s="45"/>
     </row>
     <row r="520" spans="1:1" ht="19">
-      <c r="A520" s="65"/>
+      <c r="A520" s="45"/>
     </row>
     <row r="521" spans="1:1" ht="19">
-      <c r="A521" s="65"/>
+      <c r="A521" s="45"/>
     </row>
     <row r="522" spans="1:1" ht="19">
-      <c r="A522" s="65"/>
+      <c r="A522" s="45"/>
     </row>
     <row r="523" spans="1:1" ht="19">
-      <c r="A523" s="65"/>
+      <c r="A523" s="45"/>
     </row>
     <row r="524" spans="1:1" ht="19">
-      <c r="A524" s="65"/>
+      <c r="A524" s="45"/>
     </row>
     <row r="525" spans="1:1" ht="19">
-      <c r="A525" s="65"/>
+      <c r="A525" s="45"/>
     </row>
     <row r="526" spans="1:1" ht="19">
-      <c r="A526" s="65"/>
+      <c r="A526" s="45"/>
     </row>
     <row r="527" spans="1:1" ht="19">
-      <c r="A527" s="65"/>
+      <c r="A527" s="45"/>
     </row>
     <row r="528" spans="1:1" ht="19">
-      <c r="A528" s="65"/>
+      <c r="A528" s="45"/>
     </row>
     <row r="529" spans="1:1" ht="19">
-      <c r="A529" s="65"/>
+      <c r="A529" s="45"/>
     </row>
     <row r="530" spans="1:1" ht="19">
-      <c r="A530" s="65"/>
+      <c r="A530" s="45"/>
     </row>
     <row r="531" spans="1:1" ht="19">
-      <c r="A531" s="65"/>
+      <c r="A531" s="45"/>
     </row>
     <row r="532" spans="1:1" ht="19">
-      <c r="A532" s="65"/>
+      <c r="A532" s="45"/>
     </row>
     <row r="533" spans="1:1" ht="19">
-      <c r="A533" s="65"/>
+      <c r="A533" s="45"/>
     </row>
     <row r="534" spans="1:1" ht="19">
-      <c r="A534" s="65"/>
+      <c r="A534" s="45"/>
     </row>
     <row r="535" spans="1:1" ht="19">
-      <c r="A535" s="65"/>
+      <c r="A535" s="45"/>
     </row>
     <row r="536" spans="1:1" ht="19">
-      <c r="A536" s="65"/>
+      <c r="A536" s="45"/>
     </row>
     <row r="537" spans="1:1" ht="19">
-      <c r="A537" s="65"/>
+      <c r="A537" s="45"/>
     </row>
     <row r="538" spans="1:1" ht="19">
-      <c r="A538" s="65"/>
+      <c r="A538" s="45"/>
     </row>
     <row r="539" spans="1:1" ht="19">
-      <c r="A539" s="65"/>
+      <c r="A539" s="45"/>
     </row>
     <row r="540" spans="1:1" ht="19">
-      <c r="A540" s="65"/>
+      <c r="A540" s="45"/>
     </row>
     <row r="541" spans="1:1" ht="19">
-      <c r="A541" s="65"/>
+      <c r="A541" s="45"/>
     </row>
     <row r="542" spans="1:1" ht="19">
-      <c r="A542" s="65"/>
+      <c r="A542" s="45"/>
     </row>
     <row r="543" spans="1:1" ht="19">
-      <c r="A543" s="65"/>
+      <c r="A543" s="45"/>
     </row>
     <row r="544" spans="1:1" ht="19">
-      <c r="A544" s="65"/>
+      <c r="A544" s="45"/>
     </row>
     <row r="545" spans="1:1" ht="19">
-      <c r="A545" s="65"/>
+      <c r="A545" s="45"/>
     </row>
     <row r="546" spans="1:1" ht="19">
-      <c r="A546" s="65"/>
+      <c r="A546" s="45"/>
     </row>
     <row r="547" spans="1:1" ht="19">
-      <c r="A547" s="65"/>
+      <c r="A547" s="45"/>
     </row>
     <row r="548" spans="1:1" ht="19">
-      <c r="A548" s="65"/>
+      <c r="A548" s="45"/>
     </row>
     <row r="549" spans="1:1" ht="19">
-      <c r="A549" s="65"/>
+      <c r="A549" s="45"/>
     </row>
     <row r="550" spans="1:1" ht="19">
-      <c r="A550" s="65"/>
+      <c r="A550" s="45"/>
     </row>
     <row r="551" spans="1:1" ht="19">
-      <c r="A551" s="65"/>
+      <c r="A551" s="45"/>
     </row>
     <row r="552" spans="1:1" ht="19">
-      <c r="A552" s="65"/>
+      <c r="A552" s="45"/>
     </row>
     <row r="553" spans="1:1" ht="19">
-      <c r="A553" s="65"/>
+      <c r="A553" s="45"/>
     </row>
     <row r="554" spans="1:1" ht="19">
-      <c r="A554" s="65"/>
+      <c r="A554" s="45"/>
     </row>
     <row r="555" spans="1:1" ht="19">
-      <c r="A555" s="65"/>
+      <c r="A555" s="45"/>
     </row>
     <row r="556" spans="1:1" ht="19">
-      <c r="A556" s="65"/>
+      <c r="A556" s="45"/>
     </row>
     <row r="557" spans="1:1" ht="19">
-      <c r="A557" s="65"/>
+      <c r="A557" s="45"/>
     </row>
     <row r="558" spans="1:1" ht="19">
-      <c r="A558" s="65"/>
+      <c r="A558" s="45"/>
     </row>
     <row r="559" spans="1:1" ht="19">
-      <c r="A559" s="65"/>
+      <c r="A559" s="45"/>
     </row>
     <row r="560" spans="1:1" ht="19">
-      <c r="A560" s="65"/>
+      <c r="A560" s="45"/>
     </row>
     <row r="561" spans="1:1" ht="19">
-      <c r="A561" s="65"/>
+      <c r="A561" s="45"/>
     </row>
     <row r="562" spans="1:1" ht="19">
-      <c r="A562" s="65"/>
+      <c r="A562" s="45"/>
     </row>
     <row r="563" spans="1:1" ht="19">
-      <c r="A563" s="65"/>
+      <c r="A563" s="45"/>
     </row>
     <row r="564" spans="1:1" ht="19">
-      <c r="A564" s="65"/>
+      <c r="A564" s="45"/>
     </row>
     <row r="565" spans="1:1" ht="19">
-      <c r="A565" s="65"/>
+      <c r="A565" s="45"/>
     </row>
     <row r="566" spans="1:1" ht="19">
-      <c r="A566" s="65"/>
+      <c r="A566" s="45"/>
     </row>
     <row r="567" spans="1:1" ht="19">
-      <c r="A567" s="65"/>
+      <c r="A567" s="45"/>
     </row>
     <row r="568" spans="1:1" ht="19">
-      <c r="A568" s="65"/>
+      <c r="A568" s="45"/>
     </row>
     <row r="569" spans="1:1" ht="19">
-      <c r="A569" s="65"/>
+      <c r="A569" s="45"/>
     </row>
     <row r="570" spans="1:1" ht="19">
-      <c r="A570" s="65"/>
+      <c r="A570" s="45"/>
     </row>
     <row r="571" spans="1:1" ht="19">
-      <c r="A571" s="65"/>
+      <c r="A571" s="45"/>
     </row>
     <row r="572" spans="1:1" ht="19">
-      <c r="A572" s="65"/>
+      <c r="A572" s="45"/>
     </row>
     <row r="573" spans="1:1" ht="19">
-      <c r="A573" s="65"/>
+      <c r="A573" s="45"/>
     </row>
     <row r="574" spans="1:1" ht="19">
-      <c r="A574" s="65"/>
+      <c r="A574" s="45"/>
     </row>
     <row r="575" spans="1:1" ht="19">
-      <c r="A575" s="65"/>
+      <c r="A575" s="45"/>
     </row>
     <row r="576" spans="1:1" ht="19">
-      <c r="A576" s="65"/>
+      <c r="A576" s="45"/>
     </row>
     <row r="577" spans="1:1" ht="19">
-      <c r="A577" s="65"/>
+      <c r="A577" s="45"/>
     </row>
     <row r="578" spans="1:1" ht="19">
-      <c r="A578" s="65"/>
+      <c r="A578" s="45"/>
     </row>
     <row r="579" spans="1:1" ht="19">
-      <c r="A579" s="65"/>
+      <c r="A579" s="45"/>
     </row>
     <row r="580" spans="1:1" ht="19">
-      <c r="A580" s="65"/>
+      <c r="A580" s="45"/>
     </row>
     <row r="581" spans="1:1" ht="19">
-      <c r="A581" s="65"/>
+      <c r="A581" s="45"/>
     </row>
     <row r="582" spans="1:1" ht="19">
-      <c r="A582" s="65"/>
+      <c r="A582" s="45"/>
     </row>
     <row r="583" spans="1:1" ht="19">
-      <c r="A583" s="65"/>
+      <c r="A583" s="45"/>
     </row>
     <row r="584" spans="1:1" ht="19">
-      <c r="A584" s="65"/>
+      <c r="A584" s="45"/>
     </row>
     <row r="585" spans="1:1" ht="19">
-      <c r="A585" s="65"/>
+      <c r="A585" s="45"/>
     </row>
     <row r="586" spans="1:1" ht="19">
-      <c r="A586" s="65"/>
+      <c r="A586" s="45"/>
     </row>
     <row r="587" spans="1:1" ht="19">
-      <c r="A587" s="65"/>
+      <c r="A587" s="45"/>
     </row>
     <row r="588" spans="1:1" ht="19">
-      <c r="A588" s="65"/>
+      <c r="A588" s="45"/>
     </row>
     <row r="589" spans="1:1" ht="19">
-      <c r="A589" s="65"/>
+      <c r="A589" s="45"/>
     </row>
     <row r="590" spans="1:1" ht="19">
-      <c r="A590" s="65"/>
+      <c r="A590" s="45"/>
     </row>
     <row r="591" spans="1:1" ht="19">
-      <c r="A591" s="65"/>
+      <c r="A591" s="45"/>
     </row>
     <row r="592" spans="1:1" ht="19">
-      <c r="A592" s="65"/>
+      <c r="A592" s="45"/>
     </row>
     <row r="593" spans="1:1" ht="19">
-      <c r="A593" s="65"/>
+      <c r="A593" s="45"/>
     </row>
     <row r="594" spans="1:1" ht="19">
-      <c r="A594" s="65"/>
+      <c r="A594" s="45"/>
     </row>
     <row r="595" spans="1:1" ht="19">
-      <c r="A595" s="65"/>
+      <c r="A595" s="45"/>
     </row>
     <row r="596" spans="1:1" ht="19">
-      <c r="A596" s="65"/>
+      <c r="A596" s="45"/>
     </row>
     <row r="597" spans="1:1" ht="19">
-      <c r="A597" s="65"/>
+      <c r="A597" s="45"/>
     </row>
     <row r="598" spans="1:1" ht="19">
-      <c r="A598" s="65"/>
+      <c r="A598" s="45"/>
     </row>
     <row r="599" spans="1:1" ht="19">
-      <c r="A599" s="65"/>
+      <c r="A599" s="45"/>
     </row>
     <row r="600" spans="1:1" ht="19">
-      <c r="A600" s="65"/>
+      <c r="A600" s="45"/>
     </row>
     <row r="601" spans="1:1" ht="19">
-      <c r="A601" s="65"/>
+      <c r="A601" s="45"/>
     </row>
     <row r="602" spans="1:1" ht="19">
-      <c r="A602" s="65"/>
+      <c r="A602" s="45"/>
     </row>
     <row r="603" spans="1:1" ht="19">
-      <c r="A603" s="65"/>
+      <c r="A603" s="45"/>
     </row>
     <row r="604" spans="1:1" ht="19">
-      <c r="A604" s="65"/>
+      <c r="A604" s="45"/>
     </row>
     <row r="605" spans="1:1" ht="19">
-      <c r="A605" s="65"/>
+      <c r="A605" s="45"/>
     </row>
     <row r="606" spans="1:1" ht="19">
-      <c r="A606" s="65"/>
+      <c r="A606" s="45"/>
     </row>
     <row r="607" spans="1:1" ht="19">
-      <c r="A607" s="65"/>
+      <c r="A607" s="45"/>
     </row>
     <row r="608" spans="1:1" ht="19">
-      <c r="A608" s="65"/>
+      <c r="A608" s="45"/>
     </row>
     <row r="609" spans="1:1" ht="19">
-      <c r="A609" s="65"/>
+      <c r="A609" s="45"/>
     </row>
     <row r="610" spans="1:1" ht="19">
-      <c r="A610" s="65"/>
+      <c r="A610" s="45"/>
     </row>
     <row r="611" spans="1:1" ht="19">
-      <c r="A611" s="65"/>
+      <c r="A611" s="45"/>
     </row>
     <row r="612" spans="1:1" ht="19">
-      <c r="A612" s="65"/>
+      <c r="A612" s="45"/>
     </row>
     <row r="613" spans="1:1" ht="19">
-      <c r="A613" s="65"/>
+      <c r="A613" s="45"/>
     </row>
     <row r="614" spans="1:1" ht="19">
-      <c r="A614" s="65"/>
+      <c r="A614" s="45"/>
     </row>
     <row r="615" spans="1:1" ht="19">
-      <c r="A615" s="65"/>
+      <c r="A615" s="45"/>
     </row>
     <row r="616" spans="1:1" ht="19">
-      <c r="A616" s="65"/>
+      <c r="A616" s="45"/>
     </row>
     <row r="617" spans="1:1" ht="19">
-      <c r="A617" s="65"/>
+      <c r="A617" s="45"/>
     </row>
     <row r="618" spans="1:1" ht="19">
-      <c r="A618" s="65"/>
+      <c r="A618" s="45"/>
     </row>
     <row r="619" spans="1:1" ht="19">
-      <c r="A619" s="65"/>
+      <c r="A619" s="45"/>
     </row>
     <row r="620" spans="1:1" ht="19">
-      <c r="A620" s="65"/>
+      <c r="A620" s="45"/>
     </row>
     <row r="621" spans="1:1" ht="19">
-      <c r="A621" s="65"/>
+      <c r="A621" s="45"/>
     </row>
     <row r="622" spans="1:1" ht="19">
-      <c r="A622" s="65"/>
+      <c r="A622" s="45"/>
     </row>
     <row r="623" spans="1:1" ht="19">
-      <c r="A623" s="65"/>
+      <c r="A623" s="45"/>
     </row>
     <row r="624" spans="1:1" ht="19">
-      <c r="A624" s="65"/>
+      <c r="A624" s="45"/>
     </row>
     <row r="625" spans="1:1" ht="19">
-      <c r="A625" s="65"/>
+      <c r="A625" s="45"/>
     </row>
     <row r="626" spans="1:1" ht="19">
-      <c r="A626" s="65"/>
+      <c r="A626" s="45"/>
     </row>
     <row r="627" spans="1:1" ht="19">
-      <c r="A627" s="65"/>
+      <c r="A627" s="45"/>
     </row>
     <row r="628" spans="1:1" ht="19">
-      <c r="A628" s="65"/>
+      <c r="A628" s="45"/>
     </row>
     <row r="629" spans="1:1" ht="19">
-      <c r="A629" s="65"/>
+      <c r="A629" s="45"/>
     </row>
     <row r="630" spans="1:1" ht="19">
-      <c r="A630" s="65"/>
+      <c r="A630" s="45"/>
     </row>
     <row r="631" spans="1:1" ht="19">
-      <c r="A631" s="65"/>
+      <c r="A631" s="45"/>
     </row>
     <row r="632" spans="1:1" ht="19">
-      <c r="A632" s="65"/>
+      <c r="A632" s="45"/>
     </row>
     <row r="633" spans="1:1" ht="19">
-      <c r="A633" s="65"/>
+      <c r="A633" s="45"/>
     </row>
     <row r="634" spans="1:1" ht="19">
-      <c r="A634" s="65"/>
+      <c r="A634" s="45"/>
     </row>
     <row r="635" spans="1:1" ht="19">
-      <c r="A635" s="65"/>
+      <c r="A635" s="45"/>
     </row>
     <row r="636" spans="1:1" ht="19">
-      <c r="A636" s="65"/>
+      <c r="A636" s="45"/>
     </row>
     <row r="637" spans="1:1" ht="19">
-      <c r="A637" s="65"/>
+      <c r="A637" s="45"/>
     </row>
     <row r="638" spans="1:1" ht="19">
-      <c r="A638" s="65"/>
+      <c r="A638" s="45"/>
     </row>
     <row r="639" spans="1:1" ht="19">
-      <c r="A639" s="65"/>
+      <c r="A639" s="45"/>
     </row>
     <row r="640" spans="1:1" ht="19">
-      <c r="A640" s="65"/>
+      <c r="A640" s="45"/>
     </row>
     <row r="641" spans="1:1" ht="19">
-      <c r="A641" s="65"/>
+      <c r="A641" s="45"/>
     </row>
     <row r="642" spans="1:1" ht="19">
-      <c r="A642" s="65"/>
+      <c r="A642" s="45"/>
     </row>
     <row r="643" spans="1:1" ht="19">
-      <c r="A643" s="65"/>
+      <c r="A643" s="45"/>
     </row>
     <row r="644" spans="1:1" ht="19">
-      <c r="A644" s="65"/>
+      <c r="A644" s="45"/>
     </row>
     <row r="645" spans="1:1" ht="19">
-      <c r="A645" s="65"/>
+      <c r="A645" s="45"/>
     </row>
     <row r="646" spans="1:1" ht="19">
-      <c r="A646" s="65"/>
+      <c r="A646" s="45"/>
     </row>
     <row r="647" spans="1:1" ht="19">
-      <c r="A647" s="65"/>
+      <c r="A647" s="45"/>
     </row>
     <row r="648" spans="1:1" ht="19">
-      <c r="A648" s="65"/>
+      <c r="A648" s="45"/>
     </row>
     <row r="649" spans="1:1" ht="19">
-      <c r="A649" s="65"/>
+      <c r="A649" s="45"/>
     </row>
     <row r="650" spans="1:1" ht="19">
-      <c r="A650" s="65"/>
+      <c r="A650" s="45"/>
     </row>
     <row r="651" spans="1:1" ht="19">
-      <c r="A651" s="65"/>
+      <c r="A651" s="45"/>
     </row>
     <row r="652" spans="1:1" ht="19">
-      <c r="A652" s="65"/>
+      <c r="A652" s="45"/>
     </row>
     <row r="653" spans="1:1" ht="19">
-      <c r="A653" s="65"/>
+      <c r="A653" s="45"/>
     </row>
     <row r="654" spans="1:1" ht="19">
-      <c r="A654" s="65"/>
+      <c r="A654" s="45"/>
     </row>
     <row r="655" spans="1:1" ht="19">
-      <c r="A655" s="65"/>
+      <c r="A655" s="45"/>
     </row>
     <row r="656" spans="1:1" ht="19">
-      <c r="A656" s="65"/>
+      <c r="A656" s="45"/>
     </row>
     <row r="657" spans="1:1" ht="19">
-      <c r="A657" s="65"/>
+      <c r="A657" s="45"/>
     </row>
     <row r="658" spans="1:1" ht="19">
-      <c r="A658" s="65"/>
+      <c r="A658" s="45"/>
     </row>
     <row r="659" spans="1:1" ht="19">
-      <c r="A659" s="65"/>
+      <c r="A659" s="45"/>
     </row>
     <row r="660" spans="1:1" ht="19">
-      <c r="A660" s="65"/>
+      <c r="A660" s="45"/>
     </row>
     <row r="661" spans="1:1" ht="19">
-      <c r="A661" s="65"/>
+      <c r="A661" s="45"/>
     </row>
     <row r="662" spans="1:1" ht="19">
-      <c r="A662" s="65"/>
+      <c r="A662" s="45"/>
     </row>
     <row r="663" spans="1:1" ht="19">
-      <c r="A663" s="65"/>
+      <c r="A663" s="45"/>
     </row>
     <row r="664" spans="1:1" ht="19">
-      <c r="A664" s="65"/>
+      <c r="A664" s="45"/>
     </row>
     <row r="665" spans="1:1" ht="19">
-      <c r="A665" s="65"/>
+      <c r="A665" s="45"/>
     </row>
     <row r="666" spans="1:1" ht="19">
-      <c r="A666" s="65"/>
+      <c r="A666" s="45"/>
     </row>
     <row r="667" spans="1:1" ht="19">
-      <c r="A667" s="65"/>
+      <c r="A667" s="45"/>
     </row>
     <row r="668" spans="1:1" ht="19">
-      <c r="A668" s="65"/>
+      <c r="A668" s="45"/>
     </row>
     <row r="669" spans="1:1" ht="19">
-      <c r="A669" s="65"/>
+      <c r="A669" s="45"/>
     </row>
     <row r="670" spans="1:1" ht="19">
-      <c r="A670" s="65"/>
+      <c r="A670" s="45"/>
     </row>
     <row r="671" spans="1:1" ht="19">
-      <c r="A671" s="65"/>
+      <c r="A671" s="45"/>
     </row>
     <row r="672" spans="1:1" ht="19">
-      <c r="A672" s="65"/>
+      <c r="A672" s="45"/>
     </row>
     <row r="673" spans="1:1" ht="19">
-      <c r="A673" s="65"/>
+      <c r="A673" s="45"/>
     </row>
     <row r="674" spans="1:1" ht="19">
-      <c r="A674" s="65"/>
+      <c r="A674" s="45"/>
     </row>
     <row r="675" spans="1:1" ht="19">
-      <c r="A675" s="65"/>
+      <c r="A675" s="45"/>
     </row>
     <row r="676" spans="1:1" ht="19">
-      <c r="A676" s="65"/>
+      <c r="A676" s="45"/>
     </row>
     <row r="677" spans="1:1" ht="19">
-      <c r="A677" s="65"/>
+      <c r="A677" s="45"/>
     </row>
     <row r="678" spans="1:1" ht="19">
-      <c r="A678" s="65"/>
+      <c r="A678" s="45"/>
     </row>
     <row r="679" spans="1:1" ht="19">
-      <c r="A679" s="65"/>
+      <c r="A679" s="45"/>
     </row>
     <row r="680" spans="1:1" ht="19">
-      <c r="A680" s="65"/>
+      <c r="A680" s="45"/>
     </row>
     <row r="681" spans="1:1" ht="19">
-      <c r="A681" s="65"/>
+      <c r="A681" s="45"/>
     </row>
     <row r="682" spans="1:1" ht="19">
-      <c r="A682" s="65"/>
+      <c r="A682" s="45"/>
     </row>
     <row r="683" spans="1:1" ht="19">
-      <c r="A683" s="65"/>
+      <c r="A683" s="45"/>
     </row>
     <row r="684" spans="1:1" ht="19">
-      <c r="A684" s="65"/>
+      <c r="A684" s="45"/>
     </row>
     <row r="685" spans="1:1" ht="19">
-      <c r="A685" s="65"/>
+      <c r="A685" s="45"/>
     </row>
     <row r="686" spans="1:1" ht="19">
-      <c r="A686" s="65"/>
+      <c r="A686" s="45"/>
     </row>
     <row r="687" spans="1:1" ht="19">
-      <c r="A687" s="65"/>
+      <c r="A687" s="45"/>
     </row>
     <row r="688" spans="1:1" ht="19">
-      <c r="A688" s="65"/>
+      <c r="A688" s="45"/>
     </row>
     <row r="689" spans="1:1" ht="19">
-      <c r="A689" s="65"/>
+      <c r="A689" s="45"/>
     </row>
     <row r="690" spans="1:1" ht="19">
-      <c r="A690" s="65"/>
+      <c r="A690" s="45"/>
     </row>
     <row r="691" spans="1:1" ht="19">
-      <c r="A691" s="65"/>
+      <c r="A691" s="45"/>
     </row>
     <row r="692" spans="1:1" ht="19">
-      <c r="A692" s="65"/>
+      <c r="A692" s="45"/>
     </row>
     <row r="693" spans="1:1" ht="19">
-      <c r="A693" s="65"/>
+      <c r="A693" s="45"/>
     </row>
     <row r="694" spans="1:1" ht="19">
-      <c r="A694" s="65"/>
+      <c r="A694" s="45"/>
     </row>
     <row r="695" spans="1:1" ht="19">
-      <c r="A695" s="65"/>
+      <c r="A695" s="45"/>
     </row>
     <row r="696" spans="1:1" ht="19">
-      <c r="A696" s="65"/>
+      <c r="A696" s="45"/>
     </row>
     <row r="697" spans="1:1" ht="19">
-      <c r="A697" s="65"/>
+      <c r="A697" s="45"/>
     </row>
     <row r="698" spans="1:1" ht="19">
-      <c r="A698" s="65"/>
+      <c r="A698" s="45"/>
     </row>
     <row r="699" spans="1:1" ht="19">
-      <c r="A699" s="65"/>
+      <c r="A699" s="45"/>
     </row>
     <row r="700" spans="1:1" ht="19">
-      <c r="A700" s="65"/>
+      <c r="A700" s="45"/>
     </row>
     <row r="701" spans="1:1" ht="19">
-      <c r="A701" s="65"/>
+      <c r="A701" s="45"/>
     </row>
     <row r="702" spans="1:1" ht="19">
-      <c r="A702" s="65"/>
+      <c r="A702" s="45"/>
     </row>
     <row r="703" spans="1:1" ht="19">
-      <c r="A703" s="65"/>
+      <c r="A703" s="45"/>
     </row>
     <row r="704" spans="1:1" ht="19">
-      <c r="A704" s="65"/>
+      <c r="A704" s="45"/>
     </row>
     <row r="705" spans="1:1" ht="19">
-      <c r="A705" s="65"/>
+      <c r="A705" s="45"/>
     </row>
     <row r="706" spans="1:1" ht="19">
-      <c r="A706" s="65"/>
+      <c r="A706" s="45"/>
     </row>
     <row r="707" spans="1:1" ht="19">
-      <c r="A707" s="65"/>
+      <c r="A707" s="45"/>
     </row>
     <row r="708" spans="1:1" ht="19">
-      <c r="A708" s="65"/>
+      <c r="A708" s="45"/>
     </row>
     <row r="709" spans="1:1" ht="19">
-      <c r="A709" s="65"/>
+      <c r="A709" s="45"/>
     </row>
     <row r="710" spans="1:1" ht="19">
-      <c r="A710" s="65"/>
+      <c r="A710" s="45"/>
     </row>
     <row r="711" spans="1:1" ht="19">
-      <c r="A711" s="65"/>
+      <c r="A711" s="45"/>
     </row>
     <row r="712" spans="1:1" ht="19">
-      <c r="A712" s="65"/>
+      <c r="A712" s="45"/>
     </row>
     <row r="713" spans="1:1" ht="19">
-      <c r="A713" s="65"/>
+      <c r="A713" s="45"/>
     </row>
     <row r="714" spans="1:1" ht="19">
-      <c r="A714" s="65"/>
+      <c r="A714" s="45"/>
     </row>
     <row r="715" spans="1:1" ht="19">
-      <c r="A715" s="65"/>
+      <c r="A715" s="45"/>
     </row>
     <row r="716" spans="1:1" ht="19">
-      <c r="A716" s="65"/>
+      <c r="A716" s="45"/>
     </row>
     <row r="717" spans="1:1" ht="19">
-      <c r="A717" s="65"/>
+      <c r="A717" s="45"/>
     </row>
     <row r="718" spans="1:1" ht="19">
-      <c r="A718" s="65"/>
+      <c r="A718" s="45"/>
     </row>
     <row r="719" spans="1:1" ht="19">
-      <c r="A719" s="65"/>
+      <c r="A719" s="45"/>
     </row>
     <row r="720" spans="1:1" ht="19">
-      <c r="A720" s="65"/>
+      <c r="A720" s="45"/>
     </row>
     <row r="721" spans="1:1" ht="19">
-      <c r="A721" s="65"/>
+      <c r="A721" s="45"/>
     </row>
     <row r="722" spans="1:1" ht="19">
-      <c r="A722" s="65"/>
+      <c r="A722" s="45"/>
     </row>
     <row r="723" spans="1:1" ht="19">
-      <c r="A723" s="65"/>
+      <c r="A723" s="45"/>
     </row>
     <row r="724" spans="1:1" ht="19">
-      <c r="A724" s="65"/>
+      <c r="A724" s="45"/>
     </row>
     <row r="725" spans="1:1" ht="19">
-      <c r="A725" s="65"/>
+      <c r="A725" s="45"/>
     </row>
     <row r="726" spans="1:1" ht="19">
-      <c r="A726" s="65"/>
+      <c r="A726" s="45"/>
     </row>
     <row r="727" spans="1:1" ht="19">
-      <c r="A727" s="65"/>
+      <c r="A727" s="45"/>
     </row>
     <row r="728" spans="1:1" ht="19">
-      <c r="A728" s="65"/>
+      <c r="A728" s="45"/>
     </row>
     <row r="729" spans="1:1" ht="19">
-      <c r="A729" s="65"/>
+      <c r="A729" s="45"/>
     </row>
     <row r="730" spans="1:1" ht="19">
-      <c r="A730" s="65"/>
+      <c r="A730" s="45"/>
     </row>
     <row r="731" spans="1:1" ht="19">
-      <c r="A731" s="65"/>
+      <c r="A731" s="45"/>
     </row>
     <row r="732" spans="1:1" ht="19">
-      <c r="A732" s="65"/>
+      <c r="A732" s="45"/>
     </row>
     <row r="733" spans="1:1" ht="19">
-      <c r="A733" s="65"/>
+      <c r="A733" s="45"/>
     </row>
     <row r="734" spans="1:1" ht="19">
-      <c r="A734" s="65"/>
+      <c r="A734" s="45"/>
     </row>
     <row r="735" spans="1:1" ht="19">
-      <c r="A735" s="65"/>
+      <c r="A735" s="45"/>
     </row>
     <row r="736" spans="1:1" ht="19">
-      <c r="A736" s="65"/>
+      <c r="A736" s="45"/>
     </row>
     <row r="737" spans="1:1" ht="19">
-      <c r="A737" s="65"/>
+      <c r="A737" s="45"/>
     </row>
     <row r="738" spans="1:1" ht="19">
-      <c r="A738" s="65"/>
+      <c r="A738" s="45"/>
     </row>
     <row r="739" spans="1:1" ht="19">
-      <c r="A739" s="65"/>
+      <c r="A739" s="45"/>
     </row>
     <row r="740" spans="1:1" ht="19">
-      <c r="A740" s="65"/>
+      <c r="A740" s="45"/>
     </row>
     <row r="741" spans="1:1" ht="19">
-      <c r="A741" s="65"/>
+      <c r="A741" s="45"/>
     </row>
     <row r="742" spans="1:1" ht="19">
-      <c r="A742" s="65"/>
+      <c r="A742" s="45"/>
     </row>
     <row r="743" spans="1:1" ht="19">
-      <c r="A743" s="65"/>
+      <c r="A743" s="45"/>
     </row>
     <row r="744" spans="1:1" ht="19">
-      <c r="A744" s="65"/>
+      <c r="A744" s="45"/>
     </row>
     <row r="745" spans="1:1" ht="19">
-      <c r="A745" s="65"/>
+      <c r="A745" s="45"/>
     </row>
     <row r="746" spans="1:1" ht="19">
-      <c r="A746" s="65"/>
+      <c r="A746" s="45"/>
     </row>
     <row r="747" spans="1:1" ht="19">
-      <c r="A747" s="65"/>
+      <c r="A747" s="45"/>
     </row>
     <row r="748" spans="1:1" ht="19">
-      <c r="A748" s="65"/>
+      <c r="A748" s="45"/>
     </row>
     <row r="749" spans="1:1" ht="19">
-      <c r="A749" s="65"/>
+      <c r="A749" s="45"/>
     </row>
     <row r="750" spans="1:1" ht="19">
-      <c r="A750" s="65"/>
+      <c r="A750" s="45"/>
     </row>
     <row r="751" spans="1:1" ht="19">
-      <c r="A751" s="65"/>
+      <c r="A751" s="45"/>
     </row>
     <row r="752" spans="1:1" ht="19">
-      <c r="A752" s="65"/>
+      <c r="A752" s="45"/>
     </row>
     <row r="753" spans="1:1" ht="19">
-      <c r="A753" s="65"/>
+      <c r="A753" s="45"/>
     </row>
     <row r="754" spans="1:1" ht="19">
-      <c r="A754" s="65"/>
+      <c r="A754" s="45"/>
     </row>
     <row r="755" spans="1:1" ht="19">
-      <c r="A755" s="65"/>
+      <c r="A755" s="45"/>
     </row>
     <row r="756" spans="1:1" ht="19">
-      <c r="A756" s="65"/>
+      <c r="A756" s="45"/>
     </row>
     <row r="757" spans="1:1" ht="19">
-      <c r="A757" s="65"/>
+      <c r="A757" s="45"/>
     </row>
     <row r="758" spans="1:1" ht="19">
-      <c r="A758" s="65"/>
+      <c r="A758" s="45"/>
     </row>
     <row r="759" spans="1:1" ht="19">
-      <c r="A759" s="65"/>
+      <c r="A759" s="45"/>
     </row>
     <row r="760" spans="1:1" ht="19">
-      <c r="A760" s="65"/>
+      <c r="A760" s="45"/>
     </row>
     <row r="761" spans="1:1" ht="19">
-      <c r="A761" s="65"/>
+      <c r="A761" s="45"/>
     </row>
     <row r="762" spans="1:1" ht="19">
-      <c r="A762" s="65"/>
+      <c r="A762" s="45"/>
     </row>
     <row r="763" spans="1:1" ht="19">
-      <c r="A763" s="65"/>
+      <c r="A763" s="45"/>
     </row>
     <row r="764" spans="1:1" ht="19">
-      <c r="A764" s="65"/>
+      <c r="A764" s="45"/>
     </row>
     <row r="765" spans="1:1" ht="19">
-      <c r="A765" s="65"/>
+      <c r="A765" s="45"/>
     </row>
     <row r="766" spans="1:1" ht="19">
-      <c r="A766" s="65"/>
+      <c r="A766" s="45"/>
     </row>
     <row r="767" spans="1:1" ht="19">
-      <c r="A767" s="65"/>
+      <c r="A767" s="45"/>
     </row>
     <row r="768" spans="1:1" ht="19">
-      <c r="A768" s="65"/>
+      <c r="A768" s="45"/>
     </row>
     <row r="769" spans="1:1" ht="19">
-      <c r="A769" s="65"/>
+      <c r="A769" s="45"/>
     </row>
     <row r="770" spans="1:1" ht="19">
-      <c r="A770" s="65"/>
+      <c r="A770" s="45"/>
     </row>
     <row r="771" spans="1:1" ht="19">
-      <c r="A771" s="65"/>
+      <c r="A771" s="45"/>
     </row>
     <row r="772" spans="1:1" ht="19">
-      <c r="A772" s="65"/>
+      <c r="A772" s="45"/>
     </row>
     <row r="773" spans="1:1" ht="19">
-      <c r="A773" s="65"/>
+      <c r="A773" s="45"/>
     </row>
     <row r="774" spans="1:1" ht="19">
-      <c r="A774" s="65"/>
+      <c r="A774" s="45"/>
     </row>
     <row r="775" spans="1:1" ht="19">
-      <c r="A775" s="65"/>
+      <c r="A775" s="45"/>
     </row>
     <row r="776" spans="1:1" ht="19">
-      <c r="A776" s="65"/>
+      <c r="A776" s="45"/>
     </row>
     <row r="777" spans="1:1" ht="19">
-      <c r="A777" s="65"/>
+      <c r="A777" s="45"/>
     </row>
     <row r="778" spans="1:1" ht="19">
-      <c r="A778" s="65"/>
+      <c r="A778" s="45"/>
     </row>
     <row r="779" spans="1:1" ht="19">
-      <c r="A779" s="65"/>
+      <c r="A779" s="45"/>
     </row>
     <row r="780" spans="1:1" ht="19">
-      <c r="A780" s="65"/>
+      <c r="A780" s="45"/>
     </row>
     <row r="781" spans="1:1" ht="19">
-      <c r="A781" s="65"/>
+      <c r="A781" s="45"/>
     </row>
     <row r="782" spans="1:1" ht="19">
-      <c r="A782" s="65"/>
+      <c r="A782" s="45"/>
     </row>
     <row r="783" spans="1:1" ht="19">
-      <c r="A783" s="65"/>
+      <c r="A783" s="45"/>
     </row>
     <row r="784" spans="1:1" ht="19">
-      <c r="A784" s="65"/>
+      <c r="A784" s="45"/>
     </row>
     <row r="785" spans="1:1" ht="19">
-      <c r="A785" s="65"/>
+      <c r="A785" s="45"/>
     </row>
     <row r="786" spans="1:1" ht="19">
-      <c r="A786" s="65"/>
+      <c r="A786" s="45"/>
     </row>
     <row r="787" spans="1:1" ht="19">
-      <c r="A787" s="65"/>
+      <c r="A787" s="45"/>
     </row>
     <row r="788" spans="1:1" ht="19">
-      <c r="A788" s="65"/>
+      <c r="A788" s="45"/>
     </row>
     <row r="789" spans="1:1" ht="19">
-      <c r="A789" s="65"/>
+      <c r="A789" s="45"/>
     </row>
     <row r="790" spans="1:1" ht="19">
-      <c r="A790" s="65"/>
+      <c r="A790" s="45"/>
     </row>
     <row r="791" spans="1:1" ht="19">
-      <c r="A791" s="65"/>
+      <c r="A791" s="45"/>
     </row>
     <row r="792" spans="1:1" ht="19">
-      <c r="A792" s="65"/>
+      <c r="A792" s="45"/>
     </row>
     <row r="793" spans="1:1" ht="19">
-      <c r="A793" s="65"/>
+      <c r="A793" s="45"/>
     </row>
     <row r="794" spans="1:1" ht="19">
-      <c r="A794" s="65"/>
+      <c r="A794" s="45"/>
     </row>
     <row r="795" spans="1:1" ht="19">
-      <c r="A795" s="65"/>
+      <c r="A795" s="45"/>
     </row>
     <row r="796" spans="1:1" ht="19">
-      <c r="A796" s="65"/>
+      <c r="A796" s="45"/>
     </row>
     <row r="797" spans="1:1" ht="19">
-      <c r="A797" s="65"/>
+      <c r="A797" s="45"/>
     </row>
     <row r="798" spans="1:1" ht="19">
-      <c r="A798" s="65"/>
+      <c r="A798" s="45"/>
     </row>
     <row r="799" spans="1:1" ht="19">
-      <c r="A799" s="65"/>
+      <c r="A799" s="45"/>
     </row>
     <row r="800" spans="1:1" ht="19">
-      <c r="A800" s="65"/>
+      <c r="A800" s="45"/>
     </row>
     <row r="801" spans="1:1" ht="19">
-      <c r="A801" s="65"/>
+      <c r="A801" s="45"/>
     </row>
     <row r="802" spans="1:1" ht="19">
-      <c r="A802" s="65"/>
+      <c r="A802" s="45"/>
     </row>
     <row r="803" spans="1:1" ht="19">
-      <c r="A803" s="65"/>
+      <c r="A803" s="45"/>
     </row>
     <row r="804" spans="1:1" ht="19">
-      <c r="A804" s="65"/>
+      <c r="A804" s="45"/>
     </row>
     <row r="805" spans="1:1" ht="19">
-      <c r="A805" s="65"/>
+      <c r="A805" s="45"/>
     </row>
     <row r="806" spans="1:1" ht="19">
-      <c r="A806" s="65"/>
+      <c r="A806" s="45"/>
     </row>
     <row r="807" spans="1:1" ht="19">
-      <c r="A807" s="65"/>
+      <c r="A807" s="45"/>
     </row>
     <row r="808" spans="1:1" ht="19">
-      <c r="A808" s="65"/>
+      <c r="A808" s="45"/>
     </row>
     <row r="809" spans="1:1" ht="19">
-      <c r="A809" s="65"/>
+      <c r="A809" s="45"/>
     </row>
     <row r="810" spans="1:1" ht="19">
-      <c r="A810" s="65"/>
+      <c r="A810" s="45"/>
     </row>
     <row r="811" spans="1:1" ht="19">
-      <c r="A811" s="65"/>
+      <c r="A811" s="45"/>
     </row>
     <row r="812" spans="1:1" ht="19">
-      <c r="A812" s="65"/>
+      <c r="A812" s="45"/>
     </row>
     <row r="813" spans="1:1" ht="19">
-      <c r="A813" s="65"/>
+      <c r="A813" s="45"/>
     </row>
     <row r="814" spans="1:1" ht="19">
-      <c r="A814" s="65"/>
+      <c r="A814" s="45"/>
     </row>
     <row r="815" spans="1:1" ht="19">
-      <c r="A815" s="65"/>
+      <c r="A815" s="45"/>
     </row>
     <row r="816" spans="1:1" ht="19">
-      <c r="A816" s="65"/>
+      <c r="A816" s="45"/>
     </row>
     <row r="817" spans="1:1" ht="19">
-      <c r="A817" s="65"/>
+      <c r="A817" s="45"/>
     </row>
     <row r="818" spans="1:1" ht="19">
-      <c r="A818" s="65"/>
+      <c r="A818" s="45"/>
     </row>
     <row r="819" spans="1:1" ht="19">
-      <c r="A819" s="65"/>
+      <c r="A819" s="45"/>
     </row>
     <row r="820" spans="1:1" ht="19">
-      <c r="A820" s="65"/>
+      <c r="A820" s="45"/>
     </row>
     <row r="821" spans="1:1" ht="19">
-      <c r="A821" s="65"/>
+      <c r="A821" s="45"/>
     </row>
     <row r="822" spans="1:1" ht="19">
-      <c r="A822" s="65"/>
+      <c r="A822" s="45"/>
     </row>
     <row r="823" spans="1:1" ht="19">
-      <c r="A823" s="65"/>
+      <c r="A823" s="45"/>
     </row>
     <row r="824" spans="1:1" ht="19">
-      <c r="A824" s="65"/>
+      <c r="A824" s="45"/>
     </row>
     <row r="825" spans="1:1" ht="19">
-      <c r="A825" s="65"/>
+      <c r="A825" s="45"/>
     </row>
     <row r="826" spans="1:1" ht="19">
-      <c r="A826" s="65"/>
+      <c r="A826" s="45"/>
     </row>
     <row r="827" spans="1:1" ht="19">
-      <c r="A827" s="65"/>
+      <c r="A827" s="45"/>
     </row>
     <row r="828" spans="1:1" ht="19">
-      <c r="A828" s="65"/>
+      <c r="A828" s="45"/>
     </row>
     <row r="829" spans="1:1" ht="19">
-      <c r="A829" s="65"/>
+      <c r="A829" s="45"/>
     </row>
     <row r="830" spans="1:1" ht="19">
-      <c r="A830" s="65"/>
+      <c r="A830" s="45"/>
     </row>
     <row r="831" spans="1:1" ht="19">
-      <c r="A831" s="65"/>
+      <c r="A831" s="45"/>
     </row>
     <row r="832" spans="1:1" ht="19">
-      <c r="A832" s="65"/>
+      <c r="A832" s="45"/>
     </row>
     <row r="833" spans="1:1" ht="19">
-      <c r="A833" s="65"/>
+      <c r="A833" s="45"/>
     </row>
     <row r="834" spans="1:1" ht="19">
-      <c r="A834" s="65"/>
+      <c r="A834" s="45"/>
     </row>
     <row r="835" spans="1:1" ht="19">
-      <c r="A835" s="65"/>
+      <c r="A835" s="45"/>
     </row>
     <row r="836" spans="1:1" ht="19">
-      <c r="A836" s="65"/>
+      <c r="A836" s="45"/>
     </row>
     <row r="837" spans="1:1" ht="19">
-      <c r="A837" s="65"/>
+      <c r="A837" s="45"/>
     </row>
     <row r="838" spans="1:1" ht="19">
-      <c r="A838" s="65"/>
+      <c r="A838" s="45"/>
     </row>
     <row r="839" spans="1:1" ht="19">
-      <c r="A839" s="65"/>
+      <c r="A839" s="45"/>
     </row>
     <row r="840" spans="1:1" ht="19">
-      <c r="A840" s="65"/>
+      <c r="A840" s="45"/>
     </row>
     <row r="841" spans="1:1" ht="19">
-      <c r="A841" s="65"/>
+      <c r="A841" s="45"/>
     </row>
     <row r="842" spans="1:1" ht="19">
-      <c r="A842" s="65"/>
+      <c r="A842" s="45"/>
     </row>
     <row r="843" spans="1:1" ht="19">
-      <c r="A843" s="65"/>
+      <c r="A843" s="45"/>
     </row>
     <row r="844" spans="1:1" ht="19">
-      <c r="A844" s="65"/>
+      <c r="A844" s="45"/>
     </row>
     <row r="845" spans="1:1" ht="19">
-      <c r="A845" s="65"/>
+      <c r="A845" s="45"/>
     </row>
     <row r="846" spans="1:1" ht="19">
-      <c r="A846" s="65"/>
+      <c r="A846" s="45"/>
     </row>
     <row r="847" spans="1:1" ht="19">
-      <c r="A847" s="65"/>
+      <c r="A847" s="45"/>
     </row>
     <row r="848" spans="1:1" ht="19">
-      <c r="A848" s="65"/>
+      <c r="A848" s="45"/>
     </row>
     <row r="849" spans="1:1" ht="19">
-      <c r="A849" s="65"/>
+      <c r="A849" s="45"/>
     </row>
     <row r="850" spans="1:1" ht="19">
-      <c r="A850" s="65"/>
+      <c r="A850" s="45"/>
     </row>
     <row r="851" spans="1:1" ht="19">
-      <c r="A851" s="65"/>
+      <c r="A851" s="45"/>
     </row>
     <row r="852" spans="1:1" ht="19">
-      <c r="A852" s="65"/>
+      <c r="A852" s="45"/>
     </row>
     <row r="853" spans="1:1" ht="19">
-      <c r="A853" s="65"/>
+      <c r="A853" s="45"/>
     </row>
     <row r="854" spans="1:1" ht="19">
-      <c r="A854" s="65"/>
+      <c r="A854" s="45"/>
     </row>
     <row r="855" spans="1:1" ht="19">
-      <c r="A855" s="65"/>
+      <c r="A855" s="45"/>
     </row>
     <row r="856" spans="1:1" ht="19">
-      <c r="A856" s="65"/>
+      <c r="A856" s="45"/>
     </row>
     <row r="857" spans="1:1" ht="19">
-      <c r="A857" s="65"/>
+      <c r="A857" s="45"/>
     </row>
     <row r="858" spans="1:1" ht="19">
-      <c r="A858" s="65"/>
+      <c r="A858" s="45"/>
     </row>
     <row r="859" spans="1:1" ht="19">
-      <c r="A859" s="65"/>
+      <c r="A859" s="45"/>
     </row>
     <row r="860" spans="1:1" ht="19">
-      <c r="A860" s="65"/>
+      <c r="A860" s="45"/>
     </row>
     <row r="861" spans="1:1" ht="19">
-      <c r="A861" s="65"/>
+      <c r="A861" s="45"/>
     </row>
     <row r="862" spans="1:1" ht="19">
-      <c r="A862" s="65"/>
+      <c r="A862" s="45"/>
     </row>
     <row r="863" spans="1:1" ht="19">
-      <c r="A863" s="65"/>
+      <c r="A863" s="45"/>
     </row>
     <row r="864" spans="1:1" ht="19">
-      <c r="A864" s="65"/>
+      <c r="A864" s="45"/>
     </row>
     <row r="865" spans="1:1" ht="19">
-      <c r="A865" s="65"/>
+      <c r="A865" s="45"/>
     </row>
     <row r="866" spans="1:1" ht="19">
-      <c r="A866" s="65"/>
+      <c r="A866" s="45"/>
     </row>
     <row r="867" spans="1:1" ht="19">
-      <c r="A867" s="65"/>
+      <c r="A867" s="45"/>
     </row>
     <row r="868" spans="1:1" ht="19">
-      <c r="A868" s="65"/>
+      <c r="A868" s="45"/>
     </row>
     <row r="869" spans="1:1" ht="19">
-      <c r="A869" s="65"/>
+      <c r="A869" s="45"/>
     </row>
     <row r="870" spans="1:1" ht="19">
-      <c r="A870" s="65"/>
+      <c r="A870" s="45"/>
     </row>
     <row r="871" spans="1:1" ht="19">
-      <c r="A871" s="65"/>
+      <c r="A871" s="45"/>
     </row>
     <row r="872" spans="1:1" ht="19">
-      <c r="A872" s="65"/>
+      <c r="A872" s="45"/>
     </row>
     <row r="873" spans="1:1" ht="19">
-      <c r="A873" s="65"/>
+      <c r="A873" s="45"/>
     </row>
     <row r="874" spans="1:1" ht="19">
-      <c r="A874" s="65"/>
+      <c r="A874" s="45"/>
     </row>
     <row r="875" spans="1:1" ht="19">
-      <c r="A875" s="65"/>
+      <c r="A875" s="45"/>
     </row>
     <row r="876" spans="1:1" ht="19">
-      <c r="A876" s="65"/>
+      <c r="A876" s="45"/>
     </row>
     <row r="877" spans="1:1" ht="19">
-      <c r="A877" s="65"/>
+      <c r="A877" s="45"/>
     </row>
     <row r="878" spans="1:1" ht="19">
-      <c r="A878" s="65"/>
+      <c r="A878" s="45"/>
     </row>
     <row r="879" spans="1:1" ht="19">
-      <c r="A879" s="65"/>
+      <c r="A879" s="45"/>
     </row>
     <row r="880" spans="1:1" ht="19">
-      <c r="A880" s="65"/>
+      <c r="A880" s="45"/>
     </row>
     <row r="881" spans="1:1" ht="19">
-      <c r="A881" s="65"/>
+      <c r="A881" s="45"/>
     </row>
     <row r="882" spans="1:1" ht="19">
-      <c r="A882" s="65"/>
+      <c r="A882" s="45"/>
     </row>
     <row r="883" spans="1:1" ht="19">
-      <c r="A883" s="65"/>
+      <c r="A883" s="45"/>
     </row>
     <row r="884" spans="1:1" ht="19">
-      <c r="A884" s="65"/>
+      <c r="A884" s="45"/>
     </row>
     <row r="885" spans="1:1" ht="19">
-      <c r="A885" s="65"/>
+      <c r="A885" s="45"/>
     </row>
     <row r="886" spans="1:1" ht="19">
-      <c r="A886" s="65"/>
+      <c r="A886" s="45"/>
     </row>
     <row r="887" spans="1:1" ht="19">
-      <c r="A887" s="65"/>
+      <c r="A887" s="45"/>
     </row>
     <row r="888" spans="1:1" ht="19">
-      <c r="A888" s="65"/>
+      <c r="A888" s="45"/>
     </row>
     <row r="889" spans="1:1" ht="19">
-      <c r="A889" s="65"/>
+      <c r="A889" s="45"/>
     </row>
     <row r="890" spans="1:1" ht="19">
-      <c r="A890" s="65"/>
+      <c r="A890" s="45"/>
     </row>
     <row r="891" spans="1:1" ht="19">
-      <c r="A891" s="65"/>
+      <c r="A891" s="45"/>
     </row>
     <row r="892" spans="1:1" ht="19">
-      <c r="A892" s="65"/>
+      <c r="A892" s="45"/>
     </row>
     <row r="893" spans="1:1" ht="19">
-      <c r="A893" s="65"/>
+      <c r="A893" s="45"/>
     </row>
     <row r="894" spans="1:1" ht="19">
-      <c r="A894" s="65"/>
+      <c r="A894" s="45"/>
     </row>
     <row r="895" spans="1:1" ht="19">
-      <c r="A895" s="65"/>
+      <c r="A895" s="45"/>
     </row>
     <row r="896" spans="1:1" ht="19">
-      <c r="A896" s="65"/>
+      <c r="A896" s="45"/>
     </row>
     <row r="897" spans="1:1" ht="19">
-      <c r="A897" s="65"/>
+      <c r="A897" s="45"/>
     </row>
     <row r="898" spans="1:1" ht="19">
-      <c r="A898" s="65"/>
+      <c r="A898" s="45"/>
     </row>
     <row r="899" spans="1:1" ht="19">
-      <c r="A899" s="65"/>
+      <c r="A899" s="45"/>
     </row>
     <row r="900" spans="1:1" ht="19">
-      <c r="A900" s="65"/>
+      <c r="A900" s="45"/>
     </row>
     <row r="901" spans="1:1" ht="19">
-      <c r="A901" s="65"/>
+      <c r="A901" s="45"/>
     </row>
     <row r="902" spans="1:1" ht="19">
-      <c r="A902" s="65"/>
+      <c r="A902" s="45"/>
     </row>
     <row r="903" spans="1:1" ht="19">
-      <c r="A903" s="65"/>
+      <c r="A903" s="45"/>
     </row>
     <row r="904" spans="1:1" ht="19">
-      <c r="A904" s="65"/>
+      <c r="A904" s="45"/>
     </row>
     <row r="905" spans="1:1" ht="19">
-      <c r="A905" s="65"/>
+      <c r="A905" s="45"/>
     </row>
     <row r="906" spans="1:1" ht="19">
-      <c r="A906" s="65"/>
+      <c r="A906" s="45"/>
     </row>
     <row r="907" spans="1:1" ht="19">
-      <c r="A907" s="65"/>
+      <c r="A907" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15305,7 +15365,7 @@
   <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8" style="23" customWidth="1"/>
+    <col min="1" max="1" width="8" style="18" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="50" style="1" customWidth="1"/>
     <col min="4" max="5" width="15" style="1" customWidth="1"/>
@@ -15313,326 +15373,343 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="29">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
     </row>
     <row r="3" spans="1:5" ht="19">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
     </row>
     <row r="5" spans="1:5" ht="19">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
     </row>
     <row r="7" spans="1:5" ht="19">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
     </row>
     <row r="9" spans="1:5" ht="19">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
     </row>
     <row r="11" spans="1:5" ht="19">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
     </row>
     <row r="13" spans="1:5" ht="19">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
     </row>
     <row r="20" spans="1:5" ht="22">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="39"/>
-      <c r="B23" s="40" t="s">
+      <c r="A23" s="29"/>
+      <c r="B23" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="41"/>
-      <c r="B24" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="45"/>
-      <c r="B26" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="65" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="47"/>
-      <c r="B27" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
     </row>
     <row r="31" spans="1:5" ht="22">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
     </row>
     <row r="33" spans="1:5" ht="19">
-      <c r="A33" s="51">
+      <c r="A33" s="35">
         <v>1</v>
       </c>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="36" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
     </row>
     <row r="34" spans="1:5" ht="19">
-      <c r="A34" s="54">
+      <c r="A34" s="37">
         <v>2</v>
       </c>
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="38" t="s">
         <v>50</v>
       </c>
       <c r="C34" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
     </row>
     <row r="35" spans="1:5" ht="19">
-      <c r="A35" s="56">
+      <c r="A35" s="39">
         <v>3</v>
       </c>
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="40" t="s">
         <v>52</v>
       </c>
       <c r="C35" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
     </row>
     <row r="36" spans="1:5" ht="19">
-      <c r="A36" s="58">
+      <c r="A36" s="41">
         <v>4</v>
       </c>
-      <c r="B36" s="59" t="s">
+      <c r="B36" s="42" t="s">
         <v>54</v>
       </c>
       <c r="C36" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
     </row>
     <row r="39" spans="1:5" ht="22">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
     </row>
     <row r="40" spans="1:5" ht="19">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
     </row>
     <row r="41" spans="1:5" ht="19">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="61" t="s">
+      <c r="B41" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
     </row>
     <row r="42" spans="1:5" ht="19">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="62" t="s">
+      <c r="B42" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="C33:E33"/>
@@ -15649,23 +15726,6 @@
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
